--- a/relatorios_internos/sel_var.xlsx
+++ b/relatorios_internos/sel_var.xlsx
@@ -16,7 +16,7 @@
     <sheet name="old" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$20:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$20:$L$40</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="95">
   <si>
     <t>poco</t>
   </si>
@@ -470,6 +470,12 @@
   </si>
   <si>
     <t>piora muito com outras variáveis</t>
+  </si>
+  <si>
+    <t>PIORA</t>
+  </si>
+  <si>
+    <t>modelo COMPLETO (9 var)</t>
   </si>
 </sst>
 </file>
@@ -544,7 +550,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,6 +593,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -601,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -633,6 +645,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -645,25 +678,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -673,6 +692,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1368,19 +1392,24 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="N19" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="O19" s="29"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1416,12 +1445,24 @@
       <c r="K20" t="s">
         <v>28</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>84</v>
       </c>
+      <c r="M20" t="s">
+        <v>93</v>
+      </c>
+      <c r="N20" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1448,9 +1489,19 @@
       <c r="K21">
         <v>0.49597882999999998</v>
       </c>
-      <c r="M21">
+      <c r="L21">
         <f>COUNTIF(B21:J21,"X")</f>
         <v>6</v>
+      </c>
+      <c r="N21">
+        <v>0.51397371000000003</v>
+      </c>
+      <c r="O21">
+        <v>0.48746318</v>
+      </c>
+      <c r="P21" s="5">
+        <f>(K21-O21)/K21</f>
+        <v>1.7169382007695744E-2</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -1477,49 +1528,63 @@
       <c r="K22">
         <v>0.14905921999999999</v>
       </c>
-      <c r="M22" s="8">
-        <f t="shared" ref="M22:M40" si="0">COUNTIF(B22:J22,"X")</f>
+      <c r="L22" s="8">
+        <f>COUNTIF(B22:J22,"X")</f>
         <v>4</v>
       </c>
+      <c r="N22" s="8">
+        <v>0.17091360999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.12541496999999999</v>
+      </c>
+      <c r="P22" s="5"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="22">
+      <c r="B23" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="18"/>
+      <c r="J23" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="17">
         <v>0.31476583000000002</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22">
-        <f t="shared" si="0"/>
+      <c r="L23" s="17">
+        <f>COUNTIF(B23:J23,"X")</f>
         <v>6</v>
       </c>
-      <c r="N23" s="22" t="s">
+      <c r="M23" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
+      <c r="N23">
+        <v>0.34280981999999999</v>
+      </c>
+      <c r="O23">
+        <v>0.30584286999999999</v>
+      </c>
+      <c r="P23" s="5">
+        <f t="shared" ref="P22:P40" si="0">(K23-O23)/K23</f>
+        <v>2.8347930904698376E-2</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
@@ -1545,10 +1610,17 @@
       <c r="K24">
         <v>0.13768622999999999</v>
       </c>
-      <c r="M24" s="8">
-        <f t="shared" si="0"/>
+      <c r="L24" s="8">
+        <f>COUNTIF(B24:J24,"X")</f>
         <v>4</v>
       </c>
+      <c r="N24" s="8">
+        <v>0.16446412999999999</v>
+      </c>
+      <c r="O24">
+        <v>0.11687031000000001</v>
+      </c>
+      <c r="P24" s="5"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
@@ -1572,13 +1644,20 @@
       <c r="K25">
         <v>8.1635509999999994E-2</v>
       </c>
-      <c r="M25" s="8">
-        <f t="shared" si="0"/>
+      <c r="L25" s="8">
+        <f>COUNTIF(B25:J25,"X")</f>
         <v>3</v>
       </c>
+      <c r="N25" s="8">
+        <v>0.10433932999999999</v>
+      </c>
+      <c r="O25">
+        <v>5.0955590000000002E-2</v>
+      </c>
+      <c r="P25" s="5"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -1607,13 +1686,23 @@
       <c r="K26">
         <v>0.64882229000000002</v>
       </c>
-      <c r="M26">
+      <c r="L26">
+        <f>COUNTIF(B26:J26,"X")</f>
+        <v>7</v>
+      </c>
+      <c r="N26">
+        <v>0.66490075000000004</v>
+      </c>
+      <c r="O26">
+        <v>0.64492793999999998</v>
+      </c>
+      <c r="P26" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6.002182816499794E-3</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="16" t="s">
         <v>16</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -1640,9 +1729,19 @@
       <c r="K27">
         <v>0.65250063000000003</v>
       </c>
-      <c r="M27">
+      <c r="L27">
+        <f>COUNTIF(B27:J27,"X")</f>
+        <v>6</v>
+      </c>
+      <c r="N27">
+        <v>0.66618730000000004</v>
+      </c>
+      <c r="O27">
+        <v>0.64602411999999998</v>
+      </c>
+      <c r="P27" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9.9256762403433178E-3</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -1665,13 +1764,20 @@
       <c r="K28">
         <v>3.1221499999999999E-2</v>
       </c>
-      <c r="M28" s="8">
-        <f t="shared" si="0"/>
+      <c r="L28" s="8">
+        <f>COUNTIF(B28:J28,"X")</f>
         <v>2</v>
       </c>
+      <c r="N28" s="8">
+        <v>4.7853470000000002E-2</v>
+      </c>
+      <c r="O28">
+        <v>-1.0441209999999999E-2</v>
+      </c>
+      <c r="P28" s="5"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="16" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -1698,13 +1804,23 @@
       <c r="K29">
         <v>0.78485329999999998</v>
       </c>
-      <c r="M29">
+      <c r="L29">
+        <f>COUNTIF(B29:J29,"X")</f>
+        <v>6</v>
+      </c>
+      <c r="N29">
+        <v>0.79482841999999998</v>
+      </c>
+      <c r="O29">
+        <v>0.78134999999999999</v>
+      </c>
+      <c r="P29" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4.463636707649681E-3</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -1733,13 +1849,23 @@
       <c r="K30">
         <v>0.66794257999999995</v>
       </c>
-      <c r="M30">
+      <c r="L30">
+        <f>COUNTIF(B30:J30,"X")</f>
+        <v>7</v>
+      </c>
+      <c r="N30">
+        <v>0.68572575000000002</v>
+      </c>
+      <c r="O30">
+        <v>0.66461778000000005</v>
+      </c>
+      <c r="P30" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4.9776733802476044E-3</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -1766,13 +1892,23 @@
       <c r="K31">
         <v>0.84131948999999995</v>
       </c>
-      <c r="M31">
+      <c r="L31">
+        <f>COUNTIF(B31:J31,"X")</f>
+        <v>6</v>
+      </c>
+      <c r="N31">
+        <v>0.84867088999999996</v>
+      </c>
+      <c r="O31">
+        <v>0.83843056999999999</v>
+      </c>
+      <c r="P31" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3.433796594917778E-3</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="16" t="s">
         <v>21</v>
       </c>
       <c r="B32" s="3"/>
@@ -1793,52 +1929,69 @@
       <c r="K32">
         <v>0.50225642000000004</v>
       </c>
-      <c r="M32">
+      <c r="L32">
+        <f>COUNTIF(B32:J32,"X")</f>
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <v>0.52779662999999999</v>
+      </c>
+      <c r="O32">
+        <v>0.49485221000000001</v>
+      </c>
+      <c r="P32" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1.4741892199207771E-2</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="22">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="17">
         <v>0.61341528999999995</v>
       </c>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22">
+      <c r="L33" s="17">
+        <f>COUNTIF(B33:J33,"X")</f>
+        <v>6</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N33">
+        <v>0.63360444999999999</v>
+      </c>
+      <c r="O33">
+        <v>0.60635189</v>
+      </c>
+      <c r="P33" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N33" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
+        <v>1.1514874368390691E-2</v>
+      </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -1865,13 +2018,23 @@
       <c r="K34">
         <v>0.71935037000000002</v>
       </c>
-      <c r="M34">
+      <c r="L34">
+        <f>COUNTIF(B34:J34,"X")</f>
+        <v>6</v>
+      </c>
+      <c r="N34">
+        <v>0.73493489999999995</v>
+      </c>
+      <c r="O34">
+        <v>0.71382352000000004</v>
+      </c>
+      <c r="P34" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.6831127507447751E-3</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -1896,13 +2059,23 @@
       <c r="K35">
         <v>0.79495139000000004</v>
       </c>
-      <c r="M35">
+      <c r="L35">
+        <f>COUNTIF(B35:J35,"X")</f>
+        <v>5</v>
+      </c>
+      <c r="N35">
+        <v>0.80657162000000004</v>
+      </c>
+      <c r="O35">
+        <v>0.79088824000000002</v>
+      </c>
+      <c r="P35" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>5.1111930252741812E-3</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -1927,52 +2100,69 @@
       <c r="K36">
         <v>0.35120868999999999</v>
       </c>
-      <c r="M36">
+      <c r="L36">
+        <f>COUNTIF(B36:J36,"X")</f>
+        <v>5</v>
+      </c>
+      <c r="N36">
+        <v>0.38350821000000002</v>
+      </c>
+      <c r="O36">
+        <v>0.33306796999999999</v>
+      </c>
+      <c r="P36" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>5.1652252682016495E-2</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="22">
+      <c r="B37" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="18"/>
+      <c r="H37" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="18"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="17">
         <v>0.40059250000000002</v>
       </c>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22">
+      <c r="L37" s="17">
+        <f>COUNTIF(B37:J37,"X")</f>
+        <v>6</v>
+      </c>
+      <c r="M37" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N37">
+        <v>0.43373413</v>
+      </c>
+      <c r="O37">
+        <v>0.38565495</v>
+      </c>
+      <c r="P37" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N37" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
+        <v>3.7288641200222225E-2</v>
+      </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="16" t="s">
         <v>15</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -1995,54 +2185,71 @@
       <c r="K38">
         <v>0.68871134000000001</v>
       </c>
-      <c r="M38">
+      <c r="L38">
+        <f>COUNTIF(B38:J38,"X")</f>
+        <v>4</v>
+      </c>
+      <c r="N38">
+        <v>0.70724472999999999</v>
+      </c>
+      <c r="O38">
+        <v>0.68035904000000003</v>
+      </c>
+      <c r="P38" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1.2127432082067909E-2</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I39" s="23"/>
-      <c r="J39" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K39" s="22">
+      <c r="B39" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" s="18"/>
+      <c r="J39" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="17">
         <v>0.74122326999999999</v>
       </c>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22">
+      <c r="L39" s="17">
+        <f>COUNTIF(B39:J39,"X")</f>
+        <v>7</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N39">
+        <v>0.75927568999999995</v>
+      </c>
+      <c r="O39">
+        <v>0.73572656999999997</v>
+      </c>
+      <c r="P39" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N39" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
+        <v>7.4157142961796402E-3</v>
+      </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
+      <c r="A40" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -2071,25 +2278,40 @@
       <c r="K40">
         <v>0.70402909000000002</v>
       </c>
-      <c r="M40">
+      <c r="L40">
+        <f>COUNTIF(B40:J40,"X")</f>
+        <v>7</v>
+      </c>
+      <c r="N40">
+        <v>0.72547457000000004</v>
+      </c>
+      <c r="O40">
+        <v>0.69802202999999996</v>
+      </c>
+      <c r="P40" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
+        <v>8.5324031141952722E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -2855,19 +3077,19 @@
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="24"/>
+      <c r="K67" s="24"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -3633,24 +3855,24 @@
       </c>
     </row>
     <row r="91" spans="1:13" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="17" t="s">
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F91" s="17"/>
-      <c r="G91" s="17"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="18" t="s">
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
+      <c r="H91" s="26"/>
+      <c r="I91" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="J91" s="18"/>
-      <c r="K91" s="18"/>
-      <c r="L91" s="18"/>
+      <c r="J91" s="27"/>
+      <c r="K91" s="27"/>
+      <c r="L91" s="27"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
@@ -4450,22 +4672,22 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="19" t="s">
+      <c r="A114" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
+      <c r="B114" s="22"/>
+      <c r="C114" s="22"/>
       <c r="D114" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E114" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H114" s="25" t="s">
+      <c r="H114" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="I114" s="25"/>
-      <c r="J114" s="25"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23"/>
       <c r="K114" s="10" t="s">
         <v>32</v>
       </c>
@@ -4473,15 +4695,15 @@
         <v>28</v>
       </c>
       <c r="N114" s="9"/>
-      <c r="O114" s="26" t="s">
+      <c r="O114" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="P114" s="26"/>
-      <c r="Q114" s="26"/>
-      <c r="R114" s="27" t="s">
+      <c r="P114" s="21"/>
+      <c r="Q114" s="21"/>
+      <c r="R114" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="S114" s="27" t="s">
+      <c r="S114" s="20" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6740,23 +6962,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7b5dc55a-e723-417d-bbd9-2b7384a51092" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008ECFF652E2B7794693435CC41F5B4CA1" ma:contentTypeVersion="18" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="2753c092c6e3650bfb39a0d5920becdb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7b5dc55a-e723-417d-bbd9-2b7384a51092" xmlns:ns4="53b96b38-2798-47b2-a685-55ac0f3a25a3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc10ce64d22c41095b2c63fe6f6b3f8" ns3:_="" ns4:_="">
     <xsd:import namespace="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
@@ -7009,32 +7214,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98708EEF-3554-4A3F-B1A7-CCD4F989B1B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7b5dc55a-e723-417d-bbd9-2b7384a51092" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8394E3-3502-4278-897E-CA609F09FC7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="53b96b38-2798-47b2-a685-55ac0f3a25a3"/>
-    <ds:schemaRef ds:uri="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A63570-DE3B-4061-A252-6F16027443E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7051,4 +7248,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8394E3-3502-4278-897E-CA609F09FC7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="53b96b38-2798-47b2-a685-55ac0f3a25a3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98708EEF-3554-4A3F-B1A7-CCD4F989B1B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/relatorios_internos/sel_var.xlsx
+++ b/relatorios_internos/sel_var.xlsx
@@ -12,11 +12,13 @@
     <workbookView xWindow="1176" yWindow="1116" windowWidth="23748" windowHeight="14496"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="old" sheetId="1" r:id="rId2"/>
+    <sheet name="16Out" sheetId="3" r:id="rId1"/>
+    <sheet name="12Out" sheetId="2" r:id="rId2"/>
+    <sheet name="old" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$20:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'12Out'!$A$20:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'16Out'!$A$54:$K$82</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="127">
   <si>
     <t>poco</t>
   </si>
@@ -477,12 +479,181 @@
   <si>
     <t>modelo COMPLETO (9 var)</t>
   </si>
+  <si>
+    <t>365/71</t>
+  </si>
+  <si>
+    <t>390/110</t>
+  </si>
+  <si>
+    <t>392/29</t>
+  </si>
+  <si>
+    <t>404/51</t>
+  </si>
+  <si>
+    <t>404/53</t>
+  </si>
+  <si>
+    <t>404/61</t>
+  </si>
+  <si>
+    <t>404/62</t>
+  </si>
+  <si>
+    <t>405/11</t>
+  </si>
+  <si>
+    <t>405/12</t>
+  </si>
+  <si>
+    <t>405/13</t>
+  </si>
+  <si>
+    <t>405/18</t>
+  </si>
+  <si>
+    <t>405/51</t>
+  </si>
+  <si>
+    <t>405/68</t>
+  </si>
+  <si>
+    <t>405/69</t>
+  </si>
+  <si>
+    <t>405/7</t>
+  </si>
+  <si>
+    <t>405/70</t>
+  </si>
+  <si>
+    <t>432/73</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CORRELACAO DE   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PEARSON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   DE GWD COM CADA UMA DAS VARIAVEIS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CORRELACAO DE    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPEARMAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">      DE GWD COM CADA UMA DAS VARIAVEIS</t>
+    </r>
+  </si>
+  <si>
+    <t>TODAS (9)  VARIAVEIS</t>
+  </si>
+  <si>
+    <t>6 VARIAVEIS COM 
+LAG 1 OU 2</t>
+  </si>
+  <si>
+    <t>3 VARIAVEIS COM 
+LAG 1</t>
+  </si>
+  <si>
+    <t>3 VARIAVEIS COM 
+LAG 2</t>
+  </si>
+  <si>
+    <t>3 VARIAVEIS
+rr_lag1 + eto_2 + caudal_2</t>
+  </si>
+  <si>
+    <t>2º melhor</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VERMELHO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  estão os poços em que a GWD não se relaciona minimamente com as restantes variáveis (R2 abaixo de 0.1)</t>
+    </r>
+  </si>
+  <si>
+    <t>melhor R2_adj</t>
+  </si>
+  <si>
+    <t>dif relativa</t>
+  </si>
+  <si>
+    <t>6 variaveis</t>
+  </si>
+  <si>
+    <t>OK?</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,8 +720,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -599,6 +777,42 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80DC8D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -613,7 +827,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -658,6 +872,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -678,22 +899,200 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF80DC8D"/>
       <color rgb="FFFF99FF"/>
     </mruColors>
   </colors>
@@ -1005,6 +1404,5305 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:P146"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>221</v>
+      </c>
+      <c r="B5" s="3">
+        <v>219</v>
+      </c>
+      <c r="C5" s="3">
+        <v>218</v>
+      </c>
+      <c r="D5" s="3">
+        <v>217</v>
+      </c>
+      <c r="E5" s="3">
+        <v>211</v>
+      </c>
+      <c r="F5" s="3">
+        <v>207</v>
+      </c>
+      <c r="G5" s="3">
+        <v>207</v>
+      </c>
+      <c r="H5" s="3">
+        <v>201</v>
+      </c>
+      <c r="I5" s="3">
+        <v>193</v>
+      </c>
+      <c r="J5" s="3">
+        <v>190</v>
+      </c>
+      <c r="K5" s="3">
+        <v>187</v>
+      </c>
+      <c r="L5" s="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>184</v>
+      </c>
+      <c r="B7" s="3">
+        <v>179</v>
+      </c>
+      <c r="C7" s="3">
+        <v>178</v>
+      </c>
+      <c r="D7" s="3">
+        <v>176</v>
+      </c>
+      <c r="E7" s="3">
+        <v>169</v>
+      </c>
+      <c r="F7" s="3">
+        <v>168</v>
+      </c>
+      <c r="G7" s="3">
+        <v>165</v>
+      </c>
+      <c r="H7" s="3">
+        <v>164</v>
+      </c>
+      <c r="I7" s="3">
+        <v>164</v>
+      </c>
+      <c r="J7" s="3">
+        <v>153</v>
+      </c>
+      <c r="K7" s="3">
+        <v>141</v>
+      </c>
+      <c r="L7" s="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>126</v>
+      </c>
+      <c r="B9" s="3">
+        <v>116</v>
+      </c>
+      <c r="C9" s="3">
+        <v>109</v>
+      </c>
+      <c r="D9" s="3">
+        <v>102</v>
+      </c>
+      <c r="E9" s="3">
+        <v>93</v>
+      </c>
+      <c r="F9" s="3">
+        <v>88</v>
+      </c>
+      <c r="G9" s="3">
+        <v>85</v>
+      </c>
+      <c r="H9" s="3">
+        <v>80</v>
+      </c>
+      <c r="I9" s="3">
+        <v>79</v>
+      </c>
+      <c r="J9" s="3">
+        <v>75</v>
+      </c>
+      <c r="K9" s="3">
+        <v>75</v>
+      </c>
+      <c r="L9" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>69</v>
+      </c>
+      <c r="B11" s="3">
+        <v>57</v>
+      </c>
+      <c r="C11" s="3">
+        <v>56</v>
+      </c>
+      <c r="D11" s="3">
+        <v>55</v>
+      </c>
+      <c r="E11" s="3">
+        <v>48</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3">
+        <v>39</v>
+      </c>
+      <c r="H11" s="3">
+        <v>39</v>
+      </c>
+      <c r="I11" s="3">
+        <v>34</v>
+      </c>
+      <c r="J11" s="3">
+        <v>26</v>
+      </c>
+      <c r="K11" s="3">
+        <v>21</v>
+      </c>
+      <c r="L11" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>221</v>
+      </c>
+      <c r="C23">
+        <v>-0.39458687999999997</v>
+      </c>
+      <c r="D23">
+        <v>0.34561998599999999</v>
+      </c>
+      <c r="E23">
+        <v>-0.53317963999999995</v>
+      </c>
+      <c r="F23">
+        <v>-0.57551123000000004</v>
+      </c>
+      <c r="G23">
+        <v>-0.55507233</v>
+      </c>
+      <c r="H23">
+        <v>0.52976942000000005</v>
+      </c>
+      <c r="I23">
+        <v>0.57711133999999997</v>
+      </c>
+      <c r="J23">
+        <v>-0.50537834000000004</v>
+      </c>
+      <c r="K23">
+        <v>-0.37731388999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>219</v>
+      </c>
+      <c r="C24" s="8">
+        <v>7.9875169999999995E-2</v>
+      </c>
+      <c r="D24" s="8">
+        <v>-0.14286073399999999</v>
+      </c>
+      <c r="E24">
+        <v>-0.39288687</v>
+      </c>
+      <c r="F24">
+        <v>-0.15650553</v>
+      </c>
+      <c r="G24">
+        <v>-0.32031092999999999</v>
+      </c>
+      <c r="H24">
+        <v>3.9914100000000001E-2</v>
+      </c>
+      <c r="I24">
+        <v>0.22057470000000001</v>
+      </c>
+      <c r="J24">
+        <v>-0.50981571999999997</v>
+      </c>
+      <c r="K24">
+        <v>-0.52520323999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>218</v>
+      </c>
+      <c r="C25">
+        <v>-0.14187472000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.166767781</v>
+      </c>
+      <c r="E25">
+        <v>-0.11114055</v>
+      </c>
+      <c r="F25">
+        <v>-0.17382102999999999</v>
+      </c>
+      <c r="G25">
+        <v>-0.14085897999999999</v>
+      </c>
+      <c r="H25">
+        <v>0.25538820000000001</v>
+      </c>
+      <c r="I25">
+        <v>0.27621805999999999</v>
+      </c>
+      <c r="J25">
+        <v>-0.14714894000000001</v>
+      </c>
+      <c r="K25">
+        <v>-0.11812886</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26">
+        <v>217</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3.0432020000000001E-2</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-3.6058869E-2</v>
+      </c>
+      <c r="E26">
+        <v>-0.31565985000000002</v>
+      </c>
+      <c r="F26">
+        <v>-0.20056399</v>
+      </c>
+      <c r="G26">
+        <v>-0.30683873</v>
+      </c>
+      <c r="H26">
+        <v>0.13347524999999999</v>
+      </c>
+      <c r="I26">
+        <v>0.26110295</v>
+      </c>
+      <c r="J26">
+        <v>-0.39783902999999998</v>
+      </c>
+      <c r="K26">
+        <v>-0.42251403999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>211</v>
+      </c>
+      <c r="C27">
+        <v>-0.41398369000000002</v>
+      </c>
+      <c r="D27">
+        <v>0.38107204099999997</v>
+      </c>
+      <c r="E27">
+        <v>-0.39063674999999998</v>
+      </c>
+      <c r="F27">
+        <v>-0.42380198000000002</v>
+      </c>
+      <c r="G27">
+        <v>-0.28641104000000001</v>
+      </c>
+      <c r="H27">
+        <v>0.41457790999999999</v>
+      </c>
+      <c r="I27">
+        <v>0.31321267000000003</v>
+      </c>
+      <c r="J27">
+        <v>-0.36381544999999998</v>
+      </c>
+      <c r="K27">
+        <v>-0.21829884999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>207</v>
+      </c>
+      <c r="C28">
+        <v>-0.52451448000000001</v>
+      </c>
+      <c r="D28">
+        <v>0.58519388299999997</v>
+      </c>
+      <c r="E28">
+        <v>-0.49207939000000001</v>
+      </c>
+      <c r="F28">
+        <v>-0.64855598999999997</v>
+      </c>
+      <c r="G28">
+        <v>-0.49896692999999998</v>
+      </c>
+      <c r="H28">
+        <v>0.75207740999999995</v>
+      </c>
+      <c r="I28">
+        <v>0.70956215</v>
+      </c>
+      <c r="J28">
+        <v>-0.38542390999999998</v>
+      </c>
+      <c r="K28">
+        <v>-0.23998971999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29">
+        <v>207</v>
+      </c>
+      <c r="C29" s="8">
+        <v>6.2406580000000003E-2</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-6.9735064999999999E-2</v>
+      </c>
+      <c r="E29">
+        <v>-5.818388E-2</v>
+      </c>
+      <c r="F29">
+        <v>-1.783823E-2</v>
+      </c>
+      <c r="G29">
+        <v>-0.14293507</v>
+      </c>
+      <c r="H29">
+        <v>1.632043E-2</v>
+      </c>
+      <c r="I29">
+        <v>0.12642423</v>
+      </c>
+      <c r="J29">
+        <v>-0.13944703</v>
+      </c>
+      <c r="K29">
+        <v>-0.12029346</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30">
+        <v>201</v>
+      </c>
+      <c r="C30">
+        <v>-0.44739691999999998</v>
+      </c>
+      <c r="D30">
+        <v>0.53306262500000001</v>
+      </c>
+      <c r="E30">
+        <v>-0.30108407999999998</v>
+      </c>
+      <c r="F30">
+        <v>-0.54107185999999996</v>
+      </c>
+      <c r="G30">
+        <v>-0.46381512000000003</v>
+      </c>
+      <c r="H30">
+        <v>0.68416098000000003</v>
+      </c>
+      <c r="I30">
+        <v>0.66261133000000005</v>
+      </c>
+      <c r="J30">
+        <v>-0.28678589999999998</v>
+      </c>
+      <c r="K30">
+        <v>-0.16855542000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31">
+        <v>193</v>
+      </c>
+      <c r="C31">
+        <v>-0.60008320000000004</v>
+      </c>
+      <c r="D31">
+        <v>0.77851369800000003</v>
+      </c>
+      <c r="E31">
+        <v>-0.43510695999999999</v>
+      </c>
+      <c r="F31">
+        <v>-0.61422284999999999</v>
+      </c>
+      <c r="G31">
+        <v>-0.43667555000000002</v>
+      </c>
+      <c r="H31">
+        <v>0.87526848999999995</v>
+      </c>
+      <c r="I31">
+        <v>0.75027867000000004</v>
+      </c>
+      <c r="J31">
+        <v>-0.37806767000000002</v>
+      </c>
+      <c r="K31">
+        <v>-0.19968509000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32">
+        <v>190</v>
+      </c>
+      <c r="C32">
+        <v>-5.3601099999999999E-2</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-3.6138160000000002E-3</v>
+      </c>
+      <c r="E32">
+        <v>-0.39707010999999998</v>
+      </c>
+      <c r="F32">
+        <v>-0.29767758</v>
+      </c>
+      <c r="G32">
+        <v>-0.44108568999999997</v>
+      </c>
+      <c r="H32">
+        <v>0.31723548000000001</v>
+      </c>
+      <c r="I32">
+        <v>0.55162962999999998</v>
+      </c>
+      <c r="J32">
+        <v>-0.52899057000000005</v>
+      </c>
+      <c r="K32">
+        <v>-0.53322287000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33">
+        <v>187</v>
+      </c>
+      <c r="C33">
+        <v>-0.49478717</v>
+      </c>
+      <c r="D33">
+        <v>0.54169289399999998</v>
+      </c>
+      <c r="E33">
+        <v>-0.43345319999999998</v>
+      </c>
+      <c r="F33">
+        <v>-0.67119393999999999</v>
+      </c>
+      <c r="G33">
+        <v>-0.58927786999999998</v>
+      </c>
+      <c r="H33">
+        <v>0.81895412999999995</v>
+      </c>
+      <c r="I33">
+        <v>0.87874589000000003</v>
+      </c>
+      <c r="J33">
+        <v>-0.41790302000000001</v>
+      </c>
+      <c r="K33">
+        <v>-0.27933607999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>186</v>
+      </c>
+      <c r="C34">
+        <v>-0.25139260000000002</v>
+      </c>
+      <c r="D34">
+        <v>0.19880864300000001</v>
+      </c>
+      <c r="E34">
+        <v>-0.40797710999999998</v>
+      </c>
+      <c r="F34">
+        <v>-0.39853670000000002</v>
+      </c>
+      <c r="G34">
+        <v>-0.41028664999999997</v>
+      </c>
+      <c r="H34">
+        <v>0.36513152999999998</v>
+      </c>
+      <c r="I34">
+        <v>0.44138545000000001</v>
+      </c>
+      <c r="J34">
+        <v>-0.47259343999999998</v>
+      </c>
+      <c r="K34">
+        <v>-0.40545997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>184</v>
+      </c>
+      <c r="C35">
+        <v>-0.23888380000000001</v>
+      </c>
+      <c r="D35">
+        <v>0.22880948200000001</v>
+      </c>
+      <c r="E35">
+        <v>-0.27433808999999998</v>
+      </c>
+      <c r="F35">
+        <v>-0.50920405000000002</v>
+      </c>
+      <c r="G35">
+        <v>-0.62400948999999994</v>
+      </c>
+      <c r="H35">
+        <v>0.59508804999999998</v>
+      </c>
+      <c r="I35">
+        <v>0.79768393000000004</v>
+      </c>
+      <c r="J35">
+        <v>-0.38260306999999999</v>
+      </c>
+      <c r="K35">
+        <v>-0.36582375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36">
+        <v>179</v>
+      </c>
+      <c r="C36">
+        <v>-8.1680530000000001E-2</v>
+      </c>
+      <c r="D36">
+        <v>0.14475380800000001</v>
+      </c>
+      <c r="E36">
+        <v>-0.26458649000000001</v>
+      </c>
+      <c r="F36">
+        <v>-0.39247356</v>
+      </c>
+      <c r="G36">
+        <v>-0.48241063000000001</v>
+      </c>
+      <c r="H36">
+        <v>0.48955040999999999</v>
+      </c>
+      <c r="I36">
+        <v>0.68802496000000002</v>
+      </c>
+      <c r="J36">
+        <v>-0.36134729999999998</v>
+      </c>
+      <c r="K36">
+        <v>-0.31865862</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37">
+        <v>178</v>
+      </c>
+      <c r="C37">
+        <v>-0.19285870999999999</v>
+      </c>
+      <c r="D37">
+        <v>0.121830444</v>
+      </c>
+      <c r="E37">
+        <v>-0.45133105000000001</v>
+      </c>
+      <c r="F37">
+        <v>-0.52641267000000003</v>
+      </c>
+      <c r="G37">
+        <v>-0.63243316000000005</v>
+      </c>
+      <c r="H37">
+        <v>0.47159467999999999</v>
+      </c>
+      <c r="I37">
+        <v>0.68404746000000005</v>
+      </c>
+      <c r="J37">
+        <v>-0.51930712999999995</v>
+      </c>
+      <c r="K37">
+        <v>-0.40867044000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>176</v>
+      </c>
+      <c r="C38">
+        <v>-0.23590469</v>
+      </c>
+      <c r="D38">
+        <v>0.133251226</v>
+      </c>
+      <c r="E38">
+        <v>-0.28225688999999998</v>
+      </c>
+      <c r="F38">
+        <v>-0.49087762000000001</v>
+      </c>
+      <c r="G38">
+        <v>-0.51188433</v>
+      </c>
+      <c r="H38">
+        <v>0.455067</v>
+      </c>
+      <c r="I38">
+        <v>0.61557645999999999</v>
+      </c>
+      <c r="J38">
+        <v>-0.31376576</v>
+      </c>
+      <c r="K38">
+        <v>-0.30362233999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>169</v>
+      </c>
+      <c r="C39">
+        <v>-0.47065642000000002</v>
+      </c>
+      <c r="D39">
+        <v>0.54734344700000004</v>
+      </c>
+      <c r="E39">
+        <v>-0.29277767999999998</v>
+      </c>
+      <c r="F39">
+        <v>-0.54729570000000005</v>
+      </c>
+      <c r="G39">
+        <v>-0.45577378000000002</v>
+      </c>
+      <c r="H39">
+        <v>0.67097801999999995</v>
+      </c>
+      <c r="I39">
+        <v>0.61094683999999999</v>
+      </c>
+      <c r="J39">
+        <v>-0.28407027000000001</v>
+      </c>
+      <c r="K39">
+        <v>-0.17981847000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40">
+        <v>168</v>
+      </c>
+      <c r="C40">
+        <v>-0.27276265999999999</v>
+      </c>
+      <c r="D40">
+        <v>0.29299586300000002</v>
+      </c>
+      <c r="E40">
+        <v>-0.22360747</v>
+      </c>
+      <c r="F40">
+        <v>-0.48349587999999999</v>
+      </c>
+      <c r="G40">
+        <v>-0.54452009999999995</v>
+      </c>
+      <c r="H40">
+        <v>0.62581732000000001</v>
+      </c>
+      <c r="I40">
+        <v>0.77693745000000003</v>
+      </c>
+      <c r="J40">
+        <v>-0.32045085000000001</v>
+      </c>
+      <c r="K40">
+        <v>-0.33731802</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41">
+        <v>165</v>
+      </c>
+      <c r="C41">
+        <v>-0.42041221000000001</v>
+      </c>
+      <c r="D41">
+        <v>0.50901479500000002</v>
+      </c>
+      <c r="E41">
+        <v>-0.54336552000000005</v>
+      </c>
+      <c r="F41">
+        <v>-0.58711413999999995</v>
+      </c>
+      <c r="G41">
+        <v>-0.55609843000000003</v>
+      </c>
+      <c r="H41">
+        <v>0.75117697999999999</v>
+      </c>
+      <c r="I41">
+        <v>0.80226359999999997</v>
+      </c>
+      <c r="J41">
+        <v>-0.57245997999999998</v>
+      </c>
+      <c r="K41">
+        <v>-0.47081036999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>164</v>
+      </c>
+      <c r="C42">
+        <v>-0.33811763</v>
+      </c>
+      <c r="D42">
+        <v>0.32246312999999999</v>
+      </c>
+      <c r="E42">
+        <v>-0.35129881000000002</v>
+      </c>
+      <c r="F42">
+        <v>-0.52194185000000004</v>
+      </c>
+      <c r="G42">
+        <v>-0.55865067999999996</v>
+      </c>
+      <c r="H42">
+        <v>0.62259432999999997</v>
+      </c>
+      <c r="I42">
+        <v>0.77511107000000001</v>
+      </c>
+      <c r="J42">
+        <v>-0.41474112000000002</v>
+      </c>
+      <c r="K42">
+        <v>-0.40899371000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43">
+        <v>164</v>
+      </c>
+      <c r="C43">
+        <v>-0.25153153</v>
+      </c>
+      <c r="D43">
+        <v>0.247014714</v>
+      </c>
+      <c r="E43">
+        <v>-0.15310583999999999</v>
+      </c>
+      <c r="F43">
+        <v>-0.38376339999999998</v>
+      </c>
+      <c r="G43">
+        <v>-0.27204358000000001</v>
+      </c>
+      <c r="H43">
+        <v>0.38045194999999998</v>
+      </c>
+      <c r="I43">
+        <v>0.41453430000000002</v>
+      </c>
+      <c r="J43">
+        <v>-0.12863361000000001</v>
+      </c>
+      <c r="K43">
+        <v>-8.0471689999999998E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44">
+        <v>153</v>
+      </c>
+      <c r="C44">
+        <v>-5.251186E-2</v>
+      </c>
+      <c r="D44">
+        <v>0.129927984</v>
+      </c>
+      <c r="E44">
+        <v>-5.9149680000000003E-2</v>
+      </c>
+      <c r="F44">
+        <v>-5.5312769999999997E-2</v>
+      </c>
+      <c r="G44">
+        <v>-1.1874010000000001E-2</v>
+      </c>
+      <c r="H44">
+        <v>0.14427247000000001</v>
+      </c>
+      <c r="I44">
+        <v>0.12649526999999999</v>
+      </c>
+      <c r="J44">
+        <v>-4.2286240000000003E-2</v>
+      </c>
+      <c r="K44">
+        <v>-0.10100948999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>141</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0.11798425999999999</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-0.27095891700000002</v>
+      </c>
+      <c r="E45">
+        <v>-0.25147515999999998</v>
+      </c>
+      <c r="F45">
+        <v>-8.7577940000000007E-2</v>
+      </c>
+      <c r="G45">
+        <v>-0.19012733000000001</v>
+      </c>
+      <c r="H45">
+        <v>-0.11067074</v>
+      </c>
+      <c r="I45">
+        <v>7.7916819999999998E-2</v>
+      </c>
+      <c r="J45">
+        <v>-0.39284429999999998</v>
+      </c>
+      <c r="K45">
+        <v>-0.52793952</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46">
+        <v>136</v>
+      </c>
+      <c r="C46">
+        <v>-0.43785541</v>
+      </c>
+      <c r="D46">
+        <v>0.32800259599999998</v>
+      </c>
+      <c r="E46">
+        <v>-0.49999939999999998</v>
+      </c>
+      <c r="F46">
+        <v>-0.63529961000000001</v>
+      </c>
+      <c r="G46">
+        <v>-0.61011711999999996</v>
+      </c>
+      <c r="H46">
+        <v>0.61579804000000005</v>
+      </c>
+      <c r="I46">
+        <v>0.73315021000000002</v>
+      </c>
+      <c r="J46">
+        <v>-0.41786527000000001</v>
+      </c>
+      <c r="K46">
+        <v>-0.32749887</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47">
+        <v>126</v>
+      </c>
+      <c r="C47">
+        <v>-0.42484855999999999</v>
+      </c>
+      <c r="D47">
+        <v>0.49169702999999998</v>
+      </c>
+      <c r="E47">
+        <v>-0.29436514000000003</v>
+      </c>
+      <c r="F47">
+        <v>-0.51338351000000004</v>
+      </c>
+      <c r="G47">
+        <v>-0.47391349999999999</v>
+      </c>
+      <c r="H47">
+        <v>0.67719132000000004</v>
+      </c>
+      <c r="I47">
+        <v>0.70394036000000004</v>
+      </c>
+      <c r="J47">
+        <v>-0.32134875000000002</v>
+      </c>
+      <c r="K47">
+        <v>-0.26213983000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>116</v>
+      </c>
+      <c r="C48">
+        <v>-1.9060460000000001E-2</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-0.137761149</v>
+      </c>
+      <c r="E48">
+        <v>-6.6652550000000005E-2</v>
+      </c>
+      <c r="F48">
+        <v>-9.3559950000000003E-2</v>
+      </c>
+      <c r="G48">
+        <v>-0.15671098</v>
+      </c>
+      <c r="H48">
+        <v>-1.224922E-2</v>
+      </c>
+      <c r="I48">
+        <v>8.9261809999999997E-2</v>
+      </c>
+      <c r="J48">
+        <v>-4.474848E-2</v>
+      </c>
+      <c r="K48">
+        <v>-4.8502990000000003E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49">
+        <v>109</v>
+      </c>
+      <c r="C49">
+        <v>-8.3949629999999997E-2</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-6.6324982000000005E-2</v>
+      </c>
+      <c r="E49">
+        <v>-0.17146948000000001</v>
+      </c>
+      <c r="F49">
+        <v>-0.27118482999999999</v>
+      </c>
+      <c r="G49">
+        <v>-0.36937745</v>
+      </c>
+      <c r="H49">
+        <v>0.25981089000000002</v>
+      </c>
+      <c r="I49">
+        <v>0.49563123999999997</v>
+      </c>
+      <c r="J49">
+        <v>-0.24419121999999999</v>
+      </c>
+      <c r="K49">
+        <v>-0.30018444</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50">
+        <v>102</v>
+      </c>
+      <c r="C50">
+        <v>-0.25717851000000003</v>
+      </c>
+      <c r="D50">
+        <v>0.28671358400000002</v>
+      </c>
+      <c r="E50">
+        <v>-0.42654739000000003</v>
+      </c>
+      <c r="F50">
+        <v>-0.35425664000000001</v>
+      </c>
+      <c r="G50">
+        <v>-0.3773108</v>
+      </c>
+      <c r="H50">
+        <v>0.38669181000000002</v>
+      </c>
+      <c r="I50">
+        <v>0.37155936000000001</v>
+      </c>
+      <c r="J50">
+        <v>-0.49380649999999998</v>
+      </c>
+      <c r="K50">
+        <v>-0.37539337</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>221</v>
+      </c>
+      <c r="C55">
+        <v>-0.36435182300000002</v>
+      </c>
+      <c r="D55">
+        <v>0.29172956</v>
+      </c>
+      <c r="E55">
+        <v>-0.39830015000000002</v>
+      </c>
+      <c r="F55">
+        <v>-0.52896979740000005</v>
+      </c>
+      <c r="G55">
+        <v>-0.51165773000000003</v>
+      </c>
+      <c r="H55">
+        <v>0.47403530999999999</v>
+      </c>
+      <c r="I55">
+        <v>0.53216317000000002</v>
+      </c>
+      <c r="J55">
+        <v>-0.36940603</v>
+      </c>
+      <c r="K55">
+        <v>-0.29667490000000002</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>219</v>
+      </c>
+      <c r="C56" s="8">
+        <v>5.6098033999999998E-2</v>
+      </c>
+      <c r="D56" s="8">
+        <v>-0.13325564000000001</v>
+      </c>
+      <c r="E56">
+        <v>-0.37649744000000002</v>
+      </c>
+      <c r="F56">
+        <v>-0.19580443489999999</v>
+      </c>
+      <c r="G56">
+        <v>-0.36313083000000002</v>
+      </c>
+      <c r="H56">
+        <v>5.402067E-2</v>
+      </c>
+      <c r="I56">
+        <v>0.23631163999999999</v>
+      </c>
+      <c r="J56">
+        <v>-0.49020229999999998</v>
+      </c>
+      <c r="K56">
+        <v>-0.49377889000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <v>218</v>
+      </c>
+      <c r="C57">
+        <v>-9.0192495999999997E-2</v>
+      </c>
+      <c r="D57">
+        <v>0.16562938999999999</v>
+      </c>
+      <c r="E57">
+        <v>-4.4093790000000001E-2</v>
+      </c>
+      <c r="F57">
+        <v>-0.1013160382</v>
+      </c>
+      <c r="G57">
+        <v>-8.3104670000000005E-2</v>
+      </c>
+      <c r="H57">
+        <v>0.25799896</v>
+      </c>
+      <c r="I57">
+        <v>0.27798666</v>
+      </c>
+      <c r="J57">
+        <v>-6.6132590000000005E-2</v>
+      </c>
+      <c r="K57">
+        <v>-8.8600830000000005E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58">
+        <v>217</v>
+      </c>
+      <c r="C58" s="8">
+        <v>4.0933009999999999E-2</v>
+      </c>
+      <c r="D58" s="8">
+        <v>-5.2060389999999998E-2</v>
+      </c>
+      <c r="E58">
+        <v>-0.14769689999999999</v>
+      </c>
+      <c r="F58">
+        <v>-0.17437424309999999</v>
+      </c>
+      <c r="G58">
+        <v>-0.28289120000000001</v>
+      </c>
+      <c r="H58">
+        <v>9.0150969999999997E-2</v>
+      </c>
+      <c r="I58">
+        <v>0.20498458</v>
+      </c>
+      <c r="J58">
+        <v>-0.28074811999999999</v>
+      </c>
+      <c r="K58">
+        <v>-0.29853575999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59">
+        <v>211</v>
+      </c>
+      <c r="C59">
+        <v>-0.19987545300000001</v>
+      </c>
+      <c r="D59">
+        <v>0.25616371999999998</v>
+      </c>
+      <c r="E59">
+        <v>-0.22787468</v>
+      </c>
+      <c r="F59">
+        <v>-0.26005808819999998</v>
+      </c>
+      <c r="G59">
+        <v>-0.20942970999999999</v>
+      </c>
+      <c r="H59">
+        <v>0.28973631999999999</v>
+      </c>
+      <c r="I59">
+        <v>0.23133161999999999</v>
+      </c>
+      <c r="J59">
+        <v>-0.23886262</v>
+      </c>
+      <c r="K59">
+        <v>-0.19403914</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60">
+        <v>207</v>
+      </c>
+      <c r="C60">
+        <v>-0.41422975299999998</v>
+      </c>
+      <c r="D60">
+        <v>0.55260595000000001</v>
+      </c>
+      <c r="E60">
+        <v>-0.29670447999999999</v>
+      </c>
+      <c r="F60">
+        <v>-0.56113465169999999</v>
+      </c>
+      <c r="G60">
+        <v>-0.43867666999999999</v>
+      </c>
+      <c r="H60">
+        <v>0.73726440999999998</v>
+      </c>
+      <c r="I60">
+        <v>0.71037371000000005</v>
+      </c>
+      <c r="J60">
+        <v>-0.29718340999999998</v>
+      </c>
+      <c r="K60">
+        <v>-0.10106234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61">
+        <v>207</v>
+      </c>
+      <c r="C61" s="8">
+        <v>4.3213599999999998E-2</v>
+      </c>
+      <c r="D61" s="8">
+        <v>-7.6378039999999994E-2</v>
+      </c>
+      <c r="E61">
+        <v>-8.6502010000000004E-2</v>
+      </c>
+      <c r="F61">
+        <v>-1.0381050500000001E-2</v>
+      </c>
+      <c r="G61">
+        <v>-0.12306350000000001</v>
+      </c>
+      <c r="H61">
+        <v>1.7955180000000001E-2</v>
+      </c>
+      <c r="I61">
+        <v>0.12178288</v>
+      </c>
+      <c r="J61">
+        <v>-9.1271099999999994E-2</v>
+      </c>
+      <c r="K61">
+        <v>-0.13352046000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62">
+        <v>201</v>
+      </c>
+      <c r="C62">
+        <v>-0.361885238</v>
+      </c>
+      <c r="D62">
+        <v>0.51963011000000003</v>
+      </c>
+      <c r="E62">
+        <v>-0.3229224</v>
+      </c>
+      <c r="F62">
+        <v>-0.46415588070000002</v>
+      </c>
+      <c r="G62">
+        <v>-0.40125624999999998</v>
+      </c>
+      <c r="H62">
+        <v>0.67475735999999997</v>
+      </c>
+      <c r="I62">
+        <v>0.65782647999999999</v>
+      </c>
+      <c r="J62">
+        <v>-0.31465558999999999</v>
+      </c>
+      <c r="K62">
+        <v>-0.25998426000000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63">
+        <v>193</v>
+      </c>
+      <c r="C63">
+        <v>-0.52272753900000002</v>
+      </c>
+      <c r="D63">
+        <v>0.78680019999999995</v>
+      </c>
+      <c r="E63">
+        <v>-0.36561581999999998</v>
+      </c>
+      <c r="F63">
+        <v>-0.52134895270000003</v>
+      </c>
+      <c r="G63">
+        <v>-0.34999578999999997</v>
+      </c>
+      <c r="H63">
+        <v>0.83951507999999997</v>
+      </c>
+      <c r="I63">
+        <v>0.68520517999999997</v>
+      </c>
+      <c r="J63">
+        <v>-0.33384204000000001</v>
+      </c>
+      <c r="K63">
+        <v>-0.19977111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64">
+        <v>190</v>
+      </c>
+      <c r="C64">
+        <v>-6.3993869999999994E-2</v>
+      </c>
+      <c r="D64">
+        <v>7.4269760000000004E-2</v>
+      </c>
+      <c r="E64">
+        <v>-0.47170472000000002</v>
+      </c>
+      <c r="F64">
+        <v>-0.30205633009999999</v>
+      </c>
+      <c r="G64">
+        <v>-0.48890909999999999</v>
+      </c>
+      <c r="H64">
+        <v>0.34341697999999998</v>
+      </c>
+      <c r="I64">
+        <v>0.54311708000000003</v>
+      </c>
+      <c r="J64">
+        <v>-0.60839962000000003</v>
+      </c>
+      <c r="K64">
+        <v>-0.61509577000000004</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65">
+        <v>187</v>
+      </c>
+      <c r="C65">
+        <v>-0.40635138100000001</v>
+      </c>
+      <c r="D65">
+        <v>0.57476439000000001</v>
+      </c>
+      <c r="E65">
+        <v>-0.31324200000000002</v>
+      </c>
+      <c r="F65">
+        <v>-0.58746543819999997</v>
+      </c>
+      <c r="G65">
+        <v>-0.52532062000000002</v>
+      </c>
+      <c r="H65">
+        <v>0.84558688999999998</v>
+      </c>
+      <c r="I65">
+        <v>0.87783133000000002</v>
+      </c>
+      <c r="J65">
+        <v>-0.31158659999999999</v>
+      </c>
+      <c r="K65">
+        <v>-0.27158058000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66">
+        <v>186</v>
+      </c>
+      <c r="C66">
+        <v>-0.243052663</v>
+      </c>
+      <c r="D66">
+        <v>0.23803381000000001</v>
+      </c>
+      <c r="E66">
+        <v>-0.40065052000000001</v>
+      </c>
+      <c r="F66">
+        <v>-0.44403506999999998</v>
+      </c>
+      <c r="G66">
+        <v>-0.44178971</v>
+      </c>
+      <c r="H66">
+        <v>0.41125590000000001</v>
+      </c>
+      <c r="I66">
+        <v>0.47322899000000002</v>
+      </c>
+      <c r="J66">
+        <v>-0.45572425999999999</v>
+      </c>
+      <c r="K66">
+        <v>-0.32496051999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67">
+        <v>184</v>
+      </c>
+      <c r="C67">
+        <v>-0.144857031</v>
+      </c>
+      <c r="D67">
+        <v>0.23187806999999999</v>
+      </c>
+      <c r="E67">
+        <v>-0.20598859999999999</v>
+      </c>
+      <c r="F67">
+        <v>-0.42051961300000001</v>
+      </c>
+      <c r="G67">
+        <v>-0.53593942999999999</v>
+      </c>
+      <c r="H67">
+        <v>0.60874550999999999</v>
+      </c>
+      <c r="I67">
+        <v>0.81121617999999995</v>
+      </c>
+      <c r="J67">
+        <v>-0.28805876000000002</v>
+      </c>
+      <c r="K67">
+        <v>-0.28540455999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68">
+        <v>179</v>
+      </c>
+      <c r="C68">
+        <v>-4.5199683999999997E-2</v>
+      </c>
+      <c r="D68">
+        <v>0.15518918000000001</v>
+      </c>
+      <c r="E68">
+        <v>-8.4982870000000002E-2</v>
+      </c>
+      <c r="F68">
+        <v>-0.34281244960000001</v>
+      </c>
+      <c r="G68">
+        <v>-0.40859791000000001</v>
+      </c>
+      <c r="H68">
+        <v>0.50282550000000004</v>
+      </c>
+      <c r="I68">
+        <v>0.69294306999999999</v>
+      </c>
+      <c r="J68">
+        <v>-0.15289484</v>
+      </c>
+      <c r="K68">
+        <v>-0.15150158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69">
+        <v>178</v>
+      </c>
+      <c r="C69">
+        <v>-0.16460925600000001</v>
+      </c>
+      <c r="D69">
+        <v>0.12048082</v>
+      </c>
+      <c r="E69">
+        <v>-0.35642966999999998</v>
+      </c>
+      <c r="F69">
+        <v>-0.53262511909999999</v>
+      </c>
+      <c r="G69">
+        <v>-0.56787860999999995</v>
+      </c>
+      <c r="H69">
+        <v>0.45060103000000001</v>
+      </c>
+      <c r="I69">
+        <v>0.65674513000000001</v>
+      </c>
+      <c r="J69">
+        <v>-0.39277610000000002</v>
+      </c>
+      <c r="K69">
+        <v>-0.30873846999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70">
+        <v>176</v>
+      </c>
+      <c r="C70">
+        <v>-0.16835282600000001</v>
+      </c>
+      <c r="D70">
+        <v>6.7553199999999994E-2</v>
+      </c>
+      <c r="E70">
+        <v>-0.20508636</v>
+      </c>
+      <c r="F70">
+        <v>-0.36738109320000001</v>
+      </c>
+      <c r="G70">
+        <v>-0.36834045999999998</v>
+      </c>
+      <c r="H70">
+        <v>0.35794619</v>
+      </c>
+      <c r="I70">
+        <v>0.52991896000000005</v>
+      </c>
+      <c r="J70">
+        <v>-0.25766166000000001</v>
+      </c>
+      <c r="K70">
+        <v>-0.27381527999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>36</v>
+      </c>
+      <c r="B71">
+        <v>169</v>
+      </c>
+      <c r="C71">
+        <v>-0.418335607</v>
+      </c>
+      <c r="D71">
+        <v>0.53778408</v>
+      </c>
+      <c r="E71">
+        <v>-0.20986504</v>
+      </c>
+      <c r="F71">
+        <v>-0.38533529119999999</v>
+      </c>
+      <c r="G71">
+        <v>-0.32338802999999999</v>
+      </c>
+      <c r="H71">
+        <v>0.62776865999999998</v>
+      </c>
+      <c r="I71">
+        <v>0.53623005000000001</v>
+      </c>
+      <c r="J71">
+        <v>-0.22904638999999999</v>
+      </c>
+      <c r="K71">
+        <v>-0.19590138000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72">
+        <v>168</v>
+      </c>
+      <c r="C72">
+        <v>-0.215465084</v>
+      </c>
+      <c r="D72">
+        <v>0.34564039000000002</v>
+      </c>
+      <c r="E72">
+        <v>-0.15014406999999999</v>
+      </c>
+      <c r="F72">
+        <v>-0.37930182690000003</v>
+      </c>
+      <c r="G72">
+        <v>-0.44989315000000002</v>
+      </c>
+      <c r="H72">
+        <v>0.68545705999999995</v>
+      </c>
+      <c r="I72">
+        <v>0.81670657000000002</v>
+      </c>
+      <c r="J72">
+        <v>-0.22816137</v>
+      </c>
+      <c r="K72">
+        <v>-0.27790225000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73">
+        <v>165</v>
+      </c>
+      <c r="C73">
+        <v>-0.33413345999999999</v>
+      </c>
+      <c r="D73">
+        <v>0.50191156000000003</v>
+      </c>
+      <c r="E73">
+        <v>-0.46423903999999999</v>
+      </c>
+      <c r="F73">
+        <v>-0.51945576910000002</v>
+      </c>
+      <c r="G73">
+        <v>-0.51135001000000002</v>
+      </c>
+      <c r="H73">
+        <v>0.74879222000000001</v>
+      </c>
+      <c r="I73">
+        <v>0.79710197999999999</v>
+      </c>
+      <c r="J73">
+        <v>-0.50357711999999999</v>
+      </c>
+      <c r="K73">
+        <v>-0.43384430000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74">
+        <v>164</v>
+      </c>
+      <c r="C74">
+        <v>-0.265511575</v>
+      </c>
+      <c r="D74">
+        <v>0.39197029999999999</v>
+      </c>
+      <c r="E74">
+        <v>-0.25678978000000002</v>
+      </c>
+      <c r="F74">
+        <v>-0.43193091649999998</v>
+      </c>
+      <c r="G74">
+        <v>-0.48160887000000002</v>
+      </c>
+      <c r="H74">
+        <v>0.69732804999999998</v>
+      </c>
+      <c r="I74">
+        <v>0.82664101000000001</v>
+      </c>
+      <c r="J74">
+        <v>-0.30784981</v>
+      </c>
+      <c r="K74">
+        <v>-0.34555212000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75">
+        <v>164</v>
+      </c>
+      <c r="C75">
+        <v>-0.134174034</v>
+      </c>
+      <c r="D75">
+        <v>0.11582452</v>
+      </c>
+      <c r="E75">
+        <v>-8.9531830000000007E-2</v>
+      </c>
+      <c r="F75">
+        <v>-0.19188983909999999</v>
+      </c>
+      <c r="G75">
+        <v>-0.13164243</v>
+      </c>
+      <c r="H75">
+        <v>0.19651515999999999</v>
+      </c>
+      <c r="I75">
+        <v>0.21217986</v>
+      </c>
+      <c r="J75">
+        <v>-0.10189548</v>
+      </c>
+      <c r="K75">
+        <v>-5.756443E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76">
+        <v>153</v>
+      </c>
+      <c r="C76">
+        <v>-4.8392010999999999E-2</v>
+      </c>
+      <c r="D76">
+        <v>7.2019399999999997E-2</v>
+      </c>
+      <c r="E76">
+        <v>-0.13065542999999999</v>
+      </c>
+      <c r="F76" s="8">
+        <v>2.4272209999999999E-4</v>
+      </c>
+      <c r="G76" s="8">
+        <v>1.152182E-2</v>
+      </c>
+      <c r="H76">
+        <v>9.0351909999999994E-2</v>
+      </c>
+      <c r="I76">
+        <v>7.0549490000000006E-2</v>
+      </c>
+      <c r="J76">
+        <v>-5.3442379999999998E-2</v>
+      </c>
+      <c r="K76">
+        <v>-0.11587117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77">
+        <v>141</v>
+      </c>
+      <c r="C77" s="8">
+        <v>0.15400786499999999</v>
+      </c>
+      <c r="D77" s="8">
+        <v>-0.30637198999999998</v>
+      </c>
+      <c r="E77">
+        <v>-0.12254540999999999</v>
+      </c>
+      <c r="F77">
+        <v>-0.1263218002</v>
+      </c>
+      <c r="G77">
+        <v>-0.18087613999999999</v>
+      </c>
+      <c r="H77" s="8">
+        <v>-0.14950622999999999</v>
+      </c>
+      <c r="I77">
+        <v>4.4304129999999997E-2</v>
+      </c>
+      <c r="J77">
+        <v>-0.26415529999999998</v>
+      </c>
+      <c r="K77">
+        <v>-0.3751138</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78">
+        <v>136</v>
+      </c>
+      <c r="C78">
+        <v>-0.38434974799999999</v>
+      </c>
+      <c r="D78">
+        <v>0.29518195000000003</v>
+      </c>
+      <c r="E78">
+        <v>-0.40052589999999999</v>
+      </c>
+      <c r="F78">
+        <v>-0.57233660340000003</v>
+      </c>
+      <c r="G78">
+        <v>-0.50029904000000003</v>
+      </c>
+      <c r="H78">
+        <v>0.59020983999999999</v>
+      </c>
+      <c r="I78">
+        <v>0.71157645999999997</v>
+      </c>
+      <c r="J78">
+        <v>-0.32443589</v>
+      </c>
+      <c r="K78">
+        <v>-0.28790270000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79">
+        <v>126</v>
+      </c>
+      <c r="C79">
+        <v>-0.220541074</v>
+      </c>
+      <c r="D79">
+        <v>0.39742590999999999</v>
+      </c>
+      <c r="E79">
+        <v>-0.22814966</v>
+      </c>
+      <c r="F79">
+        <v>-0.42316161790000001</v>
+      </c>
+      <c r="G79">
+        <v>-0.36022224000000003</v>
+      </c>
+      <c r="H79">
+        <v>0.61000544000000001</v>
+      </c>
+      <c r="I79">
+        <v>0.64898670999999997</v>
+      </c>
+      <c r="J79">
+        <v>-0.25679487000000001</v>
+      </c>
+      <c r="K79">
+        <v>-0.18746915</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B80">
+        <v>116</v>
+      </c>
+      <c r="C80">
+        <v>-6.4095978999999997E-2</v>
+      </c>
+      <c r="D80">
+        <v>4.6417409999999999E-2</v>
+      </c>
+      <c r="E80">
+        <v>-8.6299920000000002E-2</v>
+      </c>
+      <c r="F80">
+        <v>-0.12659677580000001</v>
+      </c>
+      <c r="G80">
+        <v>-0.10278866</v>
+      </c>
+      <c r="H80">
+        <v>7.5476760000000004E-2</v>
+      </c>
+      <c r="I80">
+        <v>0.12260842</v>
+      </c>
+      <c r="J80">
+        <v>-8.2395899999999994E-2</v>
+      </c>
+      <c r="K80">
+        <v>-9.8696329999999999E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81">
+        <v>109</v>
+      </c>
+      <c r="C81">
+        <v>-4.563391E-3</v>
+      </c>
+      <c r="D81" s="8">
+        <v>-8.1266669999999999E-2</v>
+      </c>
+      <c r="E81">
+        <v>-4.221258E-2</v>
+      </c>
+      <c r="F81">
+        <v>-0.15097140449999999</v>
+      </c>
+      <c r="G81">
+        <v>-0.23268876999999999</v>
+      </c>
+      <c r="H81">
+        <v>0.24919537999999999</v>
+      </c>
+      <c r="I81">
+        <v>0.48752168000000001</v>
+      </c>
+      <c r="J81">
+        <v>-0.10110238000000001</v>
+      </c>
+      <c r="K81">
+        <v>-0.19477189</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82">
+        <v>102</v>
+      </c>
+      <c r="C82">
+        <v>-0.177978465</v>
+      </c>
+      <c r="D82">
+        <v>0.26211591000000001</v>
+      </c>
+      <c r="E82">
+        <v>-0.33019575000000001</v>
+      </c>
+      <c r="F82">
+        <v>-0.35953330449999998</v>
+      </c>
+      <c r="G82">
+        <v>-0.32322324000000002</v>
+      </c>
+      <c r="H82">
+        <v>0.33164979999999999</v>
+      </c>
+      <c r="I82">
+        <v>0.30671292999999999</v>
+      </c>
+      <c r="J82">
+        <v>-0.33314336</v>
+      </c>
+      <c r="K82">
+        <v>-0.33717796</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="27"/>
+      <c r="J85" s="27"/>
+      <c r="K85" s="27"/>
+      <c r="L85" s="4"/>
+      <c r="N85" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="O85" s="22"/>
+      <c r="P85" s="33"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H86" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J86" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="K86" t="s">
+        <v>28</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N86" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="O86" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="P86" s="34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K87">
+        <v>0.46636547</v>
+      </c>
+      <c r="L87">
+        <f t="shared" ref="L87:L114" si="0">COUNTIF(B87:J87,"X")</f>
+        <v>8</v>
+      </c>
+      <c r="N87">
+        <v>0.48632123999999999</v>
+      </c>
+      <c r="O87">
+        <v>0.46441076799999997</v>
+      </c>
+      <c r="P87" s="5">
+        <f>(K87-O87)/K87</f>
+        <v>4.1913523314666291E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88">
+        <v>0.36250254999999998</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N88">
+        <v>0.38446709000000001</v>
+      </c>
+      <c r="O88">
+        <v>0.35796089199999997</v>
+      </c>
+      <c r="P88" s="5">
+        <f t="shared" ref="P88:P114" si="1">(K88-O88)/K88</f>
+        <v>1.2528623591751298E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89">
+        <v>7.7085600000000004E-2</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N89">
+        <v>9.8033839999999997E-2</v>
+      </c>
+      <c r="O89">
+        <v>5.9006458999999997E-2</v>
+      </c>
+      <c r="P89" s="5">
+        <f t="shared" si="1"/>
+        <v>0.234533311020476</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K90">
+        <v>0.13342445999999999</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N90">
+        <v>0.16082083999999999</v>
+      </c>
+      <c r="O90">
+        <v>0.124334789</v>
+      </c>
+      <c r="P90" s="5">
+        <f t="shared" si="1"/>
+        <v>6.8125971804570126E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K91">
+        <v>0.10259366</v>
+      </c>
+      <c r="L91">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N91">
+        <v>0.12217499</v>
+      </c>
+      <c r="O91">
+        <v>8.2869395999999998E-2</v>
+      </c>
+      <c r="P91" s="5">
+        <f t="shared" si="1"/>
+        <v>0.1922561686560359</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92">
+        <v>0.60131108</v>
+      </c>
+      <c r="L92">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N92">
+        <v>0.61718419999999996</v>
+      </c>
+      <c r="O92">
+        <v>0.59969515399999995</v>
+      </c>
+      <c r="P92" s="5">
+        <f t="shared" si="1"/>
+        <v>2.6873378085766277E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K93">
+        <v>3.0828129999999999E-2</v>
+      </c>
+      <c r="L93">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N93">
+        <v>5.0162119999999998E-2</v>
+      </c>
+      <c r="O93">
+        <v>6.7685059999999997E-3</v>
+      </c>
+      <c r="P93" s="5">
+        <f t="shared" si="1"/>
+        <v>0.78044383490013824</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K94">
+        <v>0.48895614999999998</v>
+      </c>
+      <c r="L94">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N94">
+        <v>0.50542485000000004</v>
+      </c>
+      <c r="O94">
+        <v>0.48212026400000002</v>
+      </c>
+      <c r="P94" s="5">
+        <f t="shared" si="1"/>
+        <v>1.3980570650353734E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K95">
+        <v>0.75203165999999999</v>
+      </c>
+      <c r="L95">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N95">
+        <v>0.76254906</v>
+      </c>
+      <c r="O95">
+        <v>0.75087114200000005</v>
+      </c>
+      <c r="P95" s="5">
+        <f t="shared" si="1"/>
+        <v>1.5431770518809591E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>23</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K96">
+        <v>0.60331820999999997</v>
+      </c>
+      <c r="L96">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N96">
+        <v>0.61981344000000005</v>
+      </c>
+      <c r="O96">
+        <v>0.60080411300000003</v>
+      </c>
+      <c r="P96" s="5">
+        <f t="shared" si="1"/>
+        <v>4.1671160563841389E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K97">
+        <v>0.83276503000000002</v>
+      </c>
+      <c r="L97">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N97">
+        <v>0.84003415999999997</v>
+      </c>
+      <c r="O97">
+        <v>0.83190030800000003</v>
+      </c>
+      <c r="P97" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0383745340507206E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K98">
+        <v>0.33841201999999998</v>
+      </c>
+      <c r="L98">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N98">
+        <v>0.36286309</v>
+      </c>
+      <c r="O98">
+        <v>0.33028222899999998</v>
+      </c>
+      <c r="P98" s="5">
+        <f t="shared" si="1"/>
+        <v>2.4023351771015691E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>34</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K99">
+        <v>0.70574183000000001</v>
+      </c>
+      <c r="L99">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N99">
+        <v>0.71722540000000001</v>
+      </c>
+      <c r="O99">
+        <v>0.70259912599999996</v>
+      </c>
+      <c r="P99" s="5">
+        <f t="shared" si="1"/>
+        <v>4.4530504873149601E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>16</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100">
+        <v>0.53543954000000005</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N100">
+        <v>0.55194767</v>
+      </c>
+      <c r="O100">
+        <v>0.528086893</v>
+      </c>
+      <c r="P100" s="5">
+        <f t="shared" si="1"/>
+        <v>1.3731983633483708E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101">
+        <v>0.59891158</v>
+      </c>
+      <c r="L101">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N101">
+        <v>0.61717664000000005</v>
+      </c>
+      <c r="O101">
+        <v>0.59666824600000001</v>
+      </c>
+      <c r="P101" s="5">
+        <f t="shared" si="1"/>
+        <v>3.7456847970780355E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>35</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K102">
+        <v>0.38804843</v>
+      </c>
+      <c r="L102">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N102">
+        <v>0.41024153000000002</v>
+      </c>
+      <c r="O102">
+        <v>0.37826667200000003</v>
+      </c>
+      <c r="P102" s="5">
+        <f t="shared" si="1"/>
+        <v>2.5207570096340743E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>36</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K103">
+        <v>0.41566608999999999</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N103">
+        <v>0.43657800000000002</v>
+      </c>
+      <c r="O103">
+        <v>0.40468619300000003</v>
+      </c>
+      <c r="P103" s="5">
+        <f t="shared" si="1"/>
+        <v>2.6415185804547974E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104">
+        <v>0.70053087999999997</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N104">
+        <v>0.71430020000000005</v>
+      </c>
+      <c r="O104">
+        <v>0.69802616500000003</v>
+      </c>
+      <c r="P104" s="5">
+        <f t="shared" si="1"/>
+        <v>3.5754526624150176E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K105">
+        <v>0.70071728</v>
+      </c>
+      <c r="L105">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N105">
+        <v>0.71469822000000005</v>
+      </c>
+      <c r="O105">
+        <v>0.69813231099999995</v>
+      </c>
+      <c r="P105" s="5">
+        <f t="shared" si="1"/>
+        <v>3.6890327579762955E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>10</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K106">
+        <v>0.70135199000000004</v>
+      </c>
+      <c r="L106">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N106">
+        <v>0.71510189999999996</v>
+      </c>
+      <c r="O106">
+        <v>0.69845201099999998</v>
+      </c>
+      <c r="P106" s="5">
+        <f t="shared" si="1"/>
+        <v>4.1348410517806503E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107">
+        <v>4.0649699999999997E-2</v>
+      </c>
+      <c r="L107">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N107">
+        <v>6.7793010000000001E-2</v>
+      </c>
+      <c r="O107">
+        <v>1.3313380999999999E-2</v>
+      </c>
+      <c r="P107" s="5">
+        <f t="shared" si="1"/>
+        <v>0.67248513519164965</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A108" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K108">
+        <v>2.9247840000000001E-2</v>
+      </c>
+      <c r="L108">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N108">
+        <v>7.7483960000000004E-2</v>
+      </c>
+      <c r="O108">
+        <v>1.9423513999999999E-2</v>
+      </c>
+      <c r="P108" s="5">
+        <f t="shared" si="1"/>
+        <v>0.33589919802624746</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>39</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K109">
+        <v>0.28817354000000001</v>
+      </c>
+      <c r="L109">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N109">
+        <v>0.32211118999999999</v>
+      </c>
+      <c r="O109">
+        <v>0.27553867799999998</v>
+      </c>
+      <c r="P109" s="5">
+        <f t="shared" si="1"/>
+        <v>4.3844629177265976E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110">
+        <v>0.63677879999999998</v>
+      </c>
+      <c r="L110">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N110">
+        <v>0.65507234999999997</v>
+      </c>
+      <c r="O110">
+        <v>0.63043465700000001</v>
+      </c>
+      <c r="P110" s="5">
+        <f t="shared" si="1"/>
+        <v>9.9628677964781007E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K111">
+        <v>0.42966169999999998</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N111">
+        <v>0.45279754999999999</v>
+      </c>
+      <c r="O111">
+        <v>0.41034219199999999</v>
+      </c>
+      <c r="P111" s="5">
+        <f t="shared" si="1"/>
+        <v>4.4964463902647099E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A112" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112">
+        <v>1.00173E-2</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N112">
+        <v>5.7508160000000003E-2</v>
+      </c>
+      <c r="O112">
+        <v>-2.251473E-2</v>
+      </c>
+      <c r="P112" s="5">
+        <f t="shared" si="1"/>
+        <v>3.2475846785061848</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113">
+        <v>0.34594143999999999</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N113">
+        <v>0.38952782000000002</v>
+      </c>
+      <c r="O113">
+        <v>0.33403035199999997</v>
+      </c>
+      <c r="P113" s="5">
+        <f t="shared" si="1"/>
+        <v>3.4430937212957244E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K114">
+        <v>0.20566113999999999</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N114">
+        <v>0.23535848000000001</v>
+      </c>
+      <c r="O114">
+        <v>0.160556595</v>
+      </c>
+      <c r="P114" s="5">
+        <f t="shared" si="1"/>
+        <v>0.21931486424708138</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="37"/>
+      <c r="B117" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C117" s="39"/>
+      <c r="D117" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E117" s="40"/>
+      <c r="F117" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="G117" s="42"/>
+      <c r="H117" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="I117" s="44"/>
+      <c r="J117" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="K117" s="46"/>
+      <c r="L117" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="O117" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A118" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D118" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E118" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F118" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G118" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="H118" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I118" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="J118" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K118" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="L118" s="38"/>
+      <c r="M118" t="s">
+        <v>119</v>
+      </c>
+      <c r="N118" t="s">
+        <v>122</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119">
+        <v>0.48632123999999999</v>
+      </c>
+      <c r="C119">
+        <v>0.46441076799999997</v>
+      </c>
+      <c r="D119">
+        <v>0.42868437999999998</v>
+      </c>
+      <c r="E119">
+        <v>0.41266618300000002</v>
+      </c>
+      <c r="F119">
+        <v>0.33269620500000002</v>
+      </c>
+      <c r="G119">
+        <v>0.32347080700000003</v>
+      </c>
+      <c r="H119">
+        <v>0.34112587</v>
+      </c>
+      <c r="I119">
+        <v>0.332017014</v>
+      </c>
+      <c r="J119">
+        <v>0.39900403000000001</v>
+      </c>
+      <c r="K119">
+        <v>0.39069533169999998</v>
+      </c>
+      <c r="L119" s="50">
+        <f>MAX(C119,E119,G119,I119,K119)</f>
+        <v>0.46441076799999997</v>
+      </c>
+      <c r="M119" s="48">
+        <f>LARGE((C119,E119,G119,I119,K119),2)</f>
+        <v>0.41266618300000002</v>
+      </c>
+      <c r="N119" s="52">
+        <f>(L119-M119)/L119</f>
+        <v>0.11141986483827601</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120">
+        <v>0.38446709000000001</v>
+      </c>
+      <c r="C120">
+        <v>0.35796089199999997</v>
+      </c>
+      <c r="D120">
+        <v>0.37153828</v>
+      </c>
+      <c r="E120">
+        <v>0.35375162700000001</v>
+      </c>
+      <c r="F120">
+        <v>0.25565581100000001</v>
+      </c>
+      <c r="G120">
+        <v>0.245269613</v>
+      </c>
+      <c r="H120">
+        <v>0.26458098000000002</v>
+      </c>
+      <c r="I120">
+        <v>0.25431931899999999</v>
+      </c>
+      <c r="J120">
+        <v>0.26804155000000002</v>
+      </c>
+      <c r="K120">
+        <v>0.2578281738</v>
+      </c>
+      <c r="L120" s="50">
+        <f t="shared" ref="L120:L146" si="2">MAX(C120,E120,G120,I120,K120)</f>
+        <v>0.35796089199999997</v>
+      </c>
+      <c r="M120" s="48">
+        <f>LARGE((C120,E120,G120,I120,K120),2)</f>
+        <v>0.35375162700000001</v>
+      </c>
+      <c r="N120" s="52">
+        <f t="shared" ref="N120:N146" si="3">(L120-M120)/L120</f>
+        <v>1.1759008020350899E-2</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A121" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B121">
+        <v>9.8033839999999997E-2</v>
+      </c>
+      <c r="C121">
+        <v>5.9006458999999997E-2</v>
+      </c>
+      <c r="D121">
+        <v>9.5352510000000001E-2</v>
+      </c>
+      <c r="E121">
+        <v>6.9627941999999998E-2</v>
+      </c>
+      <c r="F121">
+        <v>7.2671319999999998E-2</v>
+      </c>
+      <c r="G121">
+        <v>5.9671385E-2</v>
+      </c>
+      <c r="H121">
+        <v>9.1051960000000001E-2</v>
+      </c>
+      <c r="I121">
+        <v>7.8309699999999996E-2</v>
+      </c>
+      <c r="J121">
+        <v>7.9238160000000002E-2</v>
+      </c>
+      <c r="K121">
+        <v>6.6330281599999999E-2</v>
+      </c>
+      <c r="L121" s="51">
+        <f t="shared" si="2"/>
+        <v>7.8309699999999996E-2</v>
+      </c>
+      <c r="M121" s="49">
+        <f>LARGE((C121,E121,G121,I121,K121),2)</f>
+        <v>6.9627941999999998E-2</v>
+      </c>
+      <c r="N121" s="53">
+        <f t="shared" si="3"/>
+        <v>0.11086440121721827</v>
+      </c>
+      <c r="O121" s="3"/>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122">
+        <v>0.16082083999999999</v>
+      </c>
+      <c r="C122">
+        <v>0.124334789</v>
+      </c>
+      <c r="D122">
+        <v>0.15159197999999999</v>
+      </c>
+      <c r="E122">
+        <v>0.12735175300000001</v>
+      </c>
+      <c r="F122">
+        <v>8.2844328999999994E-2</v>
+      </c>
+      <c r="G122">
+        <v>6.9926642999999997E-2</v>
+      </c>
+      <c r="H122">
+        <v>0.11627782</v>
+      </c>
+      <c r="I122">
+        <v>0.10383102800000001</v>
+      </c>
+      <c r="J122">
+        <v>0.11466874000000001</v>
+      </c>
+      <c r="K122">
+        <v>0.1021992808</v>
+      </c>
+      <c r="L122" s="50">
+        <f t="shared" si="2"/>
+        <v>0.12735175300000001</v>
+      </c>
+      <c r="M122" s="48">
+        <f>LARGE((C122,E122,G122,I122,K122),2)</f>
+        <v>0.124334789</v>
+      </c>
+      <c r="N122" s="52">
+        <f t="shared" si="3"/>
+        <v>2.3690007627928063E-2</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A123" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123">
+        <v>0.12217499</v>
+      </c>
+      <c r="C123">
+        <v>8.2869395999999998E-2</v>
+      </c>
+      <c r="D123">
+        <v>0.1204264</v>
+      </c>
+      <c r="E123">
+        <v>9.4556583999999999E-2</v>
+      </c>
+      <c r="F123">
+        <v>0.10967413600000001</v>
+      </c>
+      <c r="G123">
+        <v>9.6770861999999999E-2</v>
+      </c>
+      <c r="H123">
+        <v>7.1952669999999996E-2</v>
+      </c>
+      <c r="I123">
+        <v>5.8502712999999998E-2</v>
+      </c>
+      <c r="J123">
+        <v>0.10220356</v>
+      </c>
+      <c r="K123">
+        <v>8.9192018200000001E-2</v>
+      </c>
+      <c r="L123" s="51">
+        <f t="shared" si="2"/>
+        <v>9.6770861999999999E-2</v>
+      </c>
+      <c r="M123" s="49">
+        <f>LARGE((C123,E123,G123,I123,K123),2)</f>
+        <v>9.4556583999999999E-2</v>
+      </c>
+      <c r="N123" s="53">
+        <f t="shared" si="3"/>
+        <v>2.2881660390707277E-2</v>
+      </c>
+      <c r="O123" s="3"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124">
+        <v>0.61718419999999996</v>
+      </c>
+      <c r="C124">
+        <v>0.59969515399999995</v>
+      </c>
+      <c r="D124">
+        <v>0.59521329000000001</v>
+      </c>
+      <c r="E124">
+        <v>0.58306969399999997</v>
+      </c>
+      <c r="F124">
+        <v>0.56159143300000003</v>
+      </c>
+      <c r="G124">
+        <v>0.55511248899999999</v>
+      </c>
+      <c r="H124">
+        <v>0.51957317000000003</v>
+      </c>
+      <c r="I124">
+        <v>0.51247326699999995</v>
+      </c>
+      <c r="J124">
+        <v>0.56815760000000004</v>
+      </c>
+      <c r="K124">
+        <v>0.56177568830000002</v>
+      </c>
+      <c r="L124" s="50">
+        <f t="shared" si="2"/>
+        <v>0.59969515399999995</v>
+      </c>
+      <c r="M124" s="48">
+        <f>LARGE((C124,E124,G124,I124,K124),2)</f>
+        <v>0.58306969399999997</v>
+      </c>
+      <c r="N124" s="52">
+        <f t="shared" si="3"/>
+        <v>2.772318550368006E-2</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A125" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B125">
+        <v>5.0162119999999998E-2</v>
+      </c>
+      <c r="C125">
+        <v>6.7685059999999997E-3</v>
+      </c>
+      <c r="D125">
+        <v>4.6368109999999997E-2</v>
+      </c>
+      <c r="E125">
+        <v>1.7759153999999999E-2</v>
+      </c>
+      <c r="F125">
+        <v>9.3881620000000002E-3</v>
+      </c>
+      <c r="G125">
+        <v>-5.2514220000000004E-3</v>
+      </c>
+      <c r="H125">
+        <v>2.5481790000000001E-2</v>
+      </c>
+      <c r="I125">
+        <v>1.1080042E-2</v>
+      </c>
+      <c r="J125">
+        <v>2.7406059999999999E-2</v>
+      </c>
+      <c r="K125">
+        <v>1.30327494E-2</v>
+      </c>
+      <c r="L125" s="51">
+        <f t="shared" si="2"/>
+        <v>1.7759153999999999E-2</v>
+      </c>
+      <c r="M125" s="49">
+        <f>LARGE((C125,E125,G125,I125,K125),2)</f>
+        <v>1.30327494E-2</v>
+      </c>
+      <c r="N125" s="53">
+        <f t="shared" si="3"/>
+        <v>0.26613906270535181</v>
+      </c>
+      <c r="O125" s="3"/>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>21</v>
+      </c>
+      <c r="B126">
+        <v>0.50542485000000004</v>
+      </c>
+      <c r="C126">
+        <v>0.48212026400000002</v>
+      </c>
+      <c r="D126">
+        <v>0.49188352000000002</v>
+      </c>
+      <c r="E126">
+        <v>0.47616857800000001</v>
+      </c>
+      <c r="F126">
+        <v>0.46518301299999998</v>
+      </c>
+      <c r="G126">
+        <v>0.45703859200000002</v>
+      </c>
+      <c r="H126">
+        <v>0.43467914000000002</v>
+      </c>
+      <c r="I126">
+        <v>0.42607019299999999</v>
+      </c>
+      <c r="J126">
+        <v>0.4549281</v>
+      </c>
+      <c r="K126">
+        <v>0.44662750839999998</v>
+      </c>
+      <c r="L126" s="50">
+        <f t="shared" si="2"/>
+        <v>0.48212026400000002</v>
+      </c>
+      <c r="M126" s="48">
+        <f>LARGE((C126,E126,G126,I126,K126),2)</f>
+        <v>0.47616857800000001</v>
+      </c>
+      <c r="N126" s="52">
+        <f t="shared" si="3"/>
+        <v>1.2344816105883514E-2</v>
+      </c>
+      <c r="O126" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127">
+        <v>0.76254906</v>
+      </c>
+      <c r="C127">
+        <v>0.75087114200000005</v>
+      </c>
+      <c r="D127">
+        <v>0.72381843999999995</v>
+      </c>
+      <c r="E127">
+        <v>0.71490936100000002</v>
+      </c>
+      <c r="F127">
+        <v>0.70571984700000001</v>
+      </c>
+      <c r="G127">
+        <v>0.70104873400000001</v>
+      </c>
+      <c r="H127">
+        <v>0.47619928</v>
+      </c>
+      <c r="I127">
+        <v>0.46788497800000001</v>
+      </c>
+      <c r="J127">
+        <v>0.51590638</v>
+      </c>
+      <c r="K127">
+        <v>0.50822235770000002</v>
+      </c>
+      <c r="L127" s="50">
+        <f t="shared" si="2"/>
+        <v>0.75087114200000005</v>
+      </c>
+      <c r="M127" s="48">
+        <f>LARGE((C127,E127,G127,I127,K127),2)</f>
+        <v>0.71490936100000002</v>
+      </c>
+      <c r="N127" s="52">
+        <f t="shared" si="3"/>
+        <v>4.7893412049653687E-2</v>
+      </c>
+      <c r="O127" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>23</v>
+      </c>
+      <c r="B128">
+        <v>0.61981344000000005</v>
+      </c>
+      <c r="C128">
+        <v>0.60080411300000003</v>
+      </c>
+      <c r="D128">
+        <v>0.61245490000000002</v>
+      </c>
+      <c r="E128">
+        <v>0.59974849900000005</v>
+      </c>
+      <c r="F128">
+        <v>0.39891268099999999</v>
+      </c>
+      <c r="G128">
+        <v>0.38921772399999999</v>
+      </c>
+      <c r="H128">
+        <v>0.52564348000000005</v>
+      </c>
+      <c r="I128">
+        <v>0.51799256900000001</v>
+      </c>
+      <c r="J128">
+        <v>0.53271469999999999</v>
+      </c>
+      <c r="K128">
+        <v>0.5251778412</v>
+      </c>
+      <c r="L128" s="50">
+        <f t="shared" si="2"/>
+        <v>0.60080411300000003</v>
+      </c>
+      <c r="M128" s="48">
+        <f>LARGE((C128,E128,G128,I128,K128),2)</f>
+        <v>0.59974849900000005</v>
+      </c>
+      <c r="N128" s="52">
+        <f t="shared" si="3"/>
+        <v>1.7570019531473855E-3</v>
+      </c>
+      <c r="O128" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>24</v>
+      </c>
+      <c r="B129">
+        <v>0.84003415999999997</v>
+      </c>
+      <c r="C129">
+        <v>0.83190030800000003</v>
+      </c>
+      <c r="D129">
+        <v>0.82599412999999999</v>
+      </c>
+      <c r="E129">
+        <v>0.82019393500000004</v>
+      </c>
+      <c r="F129">
+        <v>0.72265386300000001</v>
+      </c>
+      <c r="G129">
+        <v>0.71810720500000003</v>
+      </c>
+      <c r="H129">
+        <v>0.77186893000000001</v>
+      </c>
+      <c r="I129">
+        <v>0.76812907699999999</v>
+      </c>
+      <c r="J129">
+        <v>0.79916218999999999</v>
+      </c>
+      <c r="K129">
+        <v>0.79586976549999999</v>
+      </c>
+      <c r="L129" s="50">
+        <f t="shared" si="2"/>
+        <v>0.83190030800000003</v>
+      </c>
+      <c r="M129" s="48">
+        <f>LARGE((C129,E129,G129,I129,K129),2)</f>
+        <v>0.82019393500000004</v>
+      </c>
+      <c r="N129" s="52">
+        <f t="shared" si="3"/>
+        <v>1.4071845974121207E-2</v>
+      </c>
+      <c r="O129" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>17</v>
+      </c>
+      <c r="B130">
+        <v>0.36286309</v>
+      </c>
+      <c r="C130">
+        <v>0.33028222899999998</v>
+      </c>
+      <c r="D130">
+        <v>0.33925566000000001</v>
+      </c>
+      <c r="E130">
+        <v>0.31710780599999999</v>
+      </c>
+      <c r="F130">
+        <v>0.295427944</v>
+      </c>
+      <c r="G130">
+        <v>0.28381411899999998</v>
+      </c>
+      <c r="H130">
+        <v>0.27131018000000001</v>
+      </c>
+      <c r="I130">
+        <v>0.25929880500000002</v>
+      </c>
+      <c r="J130">
+        <v>0.31736007999999999</v>
+      </c>
+      <c r="K130">
+        <v>0.30610777420000002</v>
+      </c>
+      <c r="L130" s="50">
+        <f t="shared" si="2"/>
+        <v>0.33028222899999998</v>
+      </c>
+      <c r="M130" s="48">
+        <f>LARGE((C130,E130,G130,I130,K130),2)</f>
+        <v>0.31710780599999999</v>
+      </c>
+      <c r="N130" s="52">
+        <f t="shared" si="3"/>
+        <v>3.988837982560664E-2</v>
+      </c>
+      <c r="O130" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>34</v>
+      </c>
+      <c r="B131">
+        <v>0.71722540000000001</v>
+      </c>
+      <c r="C131">
+        <v>0.70259912599999996</v>
+      </c>
+      <c r="D131">
+        <v>0.69617678999999999</v>
+      </c>
+      <c r="E131">
+        <v>0.68587769600000004</v>
+      </c>
+      <c r="F131">
+        <v>0.37880096000000002</v>
+      </c>
+      <c r="G131">
+        <v>0.36844764200000002</v>
+      </c>
+      <c r="H131">
+        <v>0.65928545999999999</v>
+      </c>
+      <c r="I131">
+        <v>0.65360688499999997</v>
+      </c>
+      <c r="J131">
+        <v>0.65945233000000003</v>
+      </c>
+      <c r="K131">
+        <v>0.65377653840000005</v>
+      </c>
+      <c r="L131" s="50">
+        <f t="shared" si="2"/>
+        <v>0.70259912599999996</v>
+      </c>
+      <c r="M131" s="48">
+        <f>LARGE((C131,E131,G131,I131,K131),2)</f>
+        <v>0.68587769600000004</v>
+      </c>
+      <c r="N131" s="52">
+        <f t="shared" si="3"/>
+        <v>2.3799389127050988E-2</v>
+      </c>
+      <c r="O131" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>16</v>
+      </c>
+      <c r="B132">
+        <v>0.55194767</v>
+      </c>
+      <c r="C132">
+        <v>0.528086893</v>
+      </c>
+      <c r="D132">
+        <v>0.52890780999999998</v>
+      </c>
+      <c r="E132">
+        <v>0.51247436599999996</v>
+      </c>
+      <c r="F132">
+        <v>0.25502070500000001</v>
+      </c>
+      <c r="G132">
+        <v>0.24224963099999999</v>
+      </c>
+      <c r="H132">
+        <v>0.48395324000000001</v>
+      </c>
+      <c r="I132">
+        <v>0.47510672199999998</v>
+      </c>
+      <c r="J132">
+        <v>0.48457781</v>
+      </c>
+      <c r="K132">
+        <v>0.4757420054</v>
+      </c>
+      <c r="L132" s="50">
+        <f t="shared" si="2"/>
+        <v>0.528086893</v>
+      </c>
+      <c r="M132" s="48">
+        <f>LARGE((C132,E132,G132,I132,K132),2)</f>
+        <v>0.51247436599999996</v>
+      </c>
+      <c r="N132" s="52">
+        <f t="shared" si="3"/>
+        <v>2.9564314522761773E-2</v>
+      </c>
+      <c r="O132" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>12</v>
+      </c>
+      <c r="B133">
+        <v>0.61717664000000005</v>
+      </c>
+      <c r="C133">
+        <v>0.59666824600000001</v>
+      </c>
+      <c r="D133">
+        <v>0.60873421000000005</v>
+      </c>
+      <c r="E133">
+        <v>0.59500559099999994</v>
+      </c>
+      <c r="F133">
+        <v>0.33779865100000001</v>
+      </c>
+      <c r="G133">
+        <v>0.32638138700000002</v>
+      </c>
+      <c r="H133">
+        <v>0.47851841000000001</v>
+      </c>
+      <c r="I133">
+        <v>0.46952735299999998</v>
+      </c>
+      <c r="J133">
+        <v>0.50586355000000005</v>
+      </c>
+      <c r="K133">
+        <v>0.497343959</v>
+      </c>
+      <c r="L133" s="50">
+        <f t="shared" si="2"/>
+        <v>0.59666824600000001</v>
+      </c>
+      <c r="M133" s="48">
+        <f>LARGE((C133,E133,G133,I133,K133),2)</f>
+        <v>0.59500559099999994</v>
+      </c>
+      <c r="N133" s="52">
+        <f t="shared" si="3"/>
+        <v>2.7865652498625985E-3</v>
+      </c>
+      <c r="O133" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>35</v>
+      </c>
+      <c r="B134">
+        <v>0.41024153000000002</v>
+      </c>
+      <c r="C134">
+        <v>0.37826667200000003</v>
+      </c>
+      <c r="D134">
+        <v>0.36256860000000002</v>
+      </c>
+      <c r="E134">
+        <v>0.33993789400000002</v>
+      </c>
+      <c r="F134">
+        <v>0.16855131200000001</v>
+      </c>
+      <c r="G134">
+        <v>0.1540493</v>
+      </c>
+      <c r="H134">
+        <v>0.28704786999999998</v>
+      </c>
+      <c r="I134">
+        <v>0.27461266000000001</v>
+      </c>
+      <c r="J134">
+        <v>0.29911357999999999</v>
+      </c>
+      <c r="K134">
+        <v>0.28688881960000001</v>
+      </c>
+      <c r="L134" s="50">
+        <f t="shared" si="2"/>
+        <v>0.37826667200000003</v>
+      </c>
+      <c r="M134" s="48">
+        <f>LARGE((C134,E134,G134,I134,K134),2)</f>
+        <v>0.33993789400000002</v>
+      </c>
+      <c r="N134" s="52">
+        <f t="shared" si="3"/>
+        <v>0.10132739899432643</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>36</v>
+      </c>
+      <c r="B135">
+        <v>0.43657800000000002</v>
+      </c>
+      <c r="C135">
+        <v>0.40468619300000003</v>
+      </c>
+      <c r="D135">
+        <v>0.40713695</v>
+      </c>
+      <c r="E135">
+        <v>0.38517905899999999</v>
+      </c>
+      <c r="F135">
+        <v>0.39421784599999998</v>
+      </c>
+      <c r="G135">
+        <v>0.38320362499999999</v>
+      </c>
+      <c r="H135">
+        <v>0.28813079000000003</v>
+      </c>
+      <c r="I135">
+        <v>0.27518771800000003</v>
+      </c>
+      <c r="J135">
+        <v>0.30599106999999998</v>
+      </c>
+      <c r="K135">
+        <v>0.29337272479999998</v>
+      </c>
+      <c r="L135" s="50">
+        <f t="shared" si="2"/>
+        <v>0.40468619300000003</v>
+      </c>
+      <c r="M135" s="48">
+        <f>LARGE((C135,E135,G135,I135,K135),2)</f>
+        <v>0.38517905899999999</v>
+      </c>
+      <c r="N135" s="52">
+        <f t="shared" si="3"/>
+        <v>4.8203112281619241E-2</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136">
+        <v>0.71430020000000005</v>
+      </c>
+      <c r="C136">
+        <v>0.69802616500000003</v>
+      </c>
+      <c r="D136">
+        <v>0.68523352000000004</v>
+      </c>
+      <c r="E136">
+        <v>0.673503089</v>
+      </c>
+      <c r="F136">
+        <v>0.47026952900000002</v>
+      </c>
+      <c r="G136">
+        <v>0.460579338</v>
+      </c>
+      <c r="H136">
+        <v>0.67012532999999996</v>
+      </c>
+      <c r="I136">
+        <v>0.66409103800000002</v>
+      </c>
+      <c r="J136">
+        <v>0.66744360000000003</v>
+      </c>
+      <c r="K136">
+        <v>0.66136024869999999</v>
+      </c>
+      <c r="L136" s="50">
+        <f t="shared" si="2"/>
+        <v>0.69802616500000003</v>
+      </c>
+      <c r="M136" s="48">
+        <f>LARGE((C136,E136,G136,I136,K136),2)</f>
+        <v>0.673503089</v>
+      </c>
+      <c r="N136" s="52">
+        <f t="shared" si="3"/>
+        <v>3.5132029757079422E-2</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>33</v>
+      </c>
+      <c r="B137">
+        <v>0.71469822000000005</v>
+      </c>
+      <c r="C137">
+        <v>0.69813231099999995</v>
+      </c>
+      <c r="D137">
+        <v>0.70621975999999997</v>
+      </c>
+      <c r="E137">
+        <v>0.69506355200000003</v>
+      </c>
+      <c r="F137">
+        <v>0.61443354299999997</v>
+      </c>
+      <c r="G137">
+        <v>0.60724907500000003</v>
+      </c>
+      <c r="H137">
+        <v>0.66164445000000005</v>
+      </c>
+      <c r="I137">
+        <v>0.65533968600000003</v>
+      </c>
+      <c r="J137">
+        <v>0.68345933999999997</v>
+      </c>
+      <c r="K137">
+        <v>0.67756106920000003</v>
+      </c>
+      <c r="L137" s="50">
+        <f t="shared" si="2"/>
+        <v>0.69813231099999995</v>
+      </c>
+      <c r="M137" s="48">
+        <f>LARGE((C137,E137,G137,I137,K137),2)</f>
+        <v>0.69506355200000003</v>
+      </c>
+      <c r="N137" s="52">
+        <f t="shared" si="3"/>
+        <v>4.3956696340329117E-3</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>10</v>
+      </c>
+      <c r="B138">
+        <v>0.71510189999999996</v>
+      </c>
+      <c r="C138">
+        <v>0.69845201099999998</v>
+      </c>
+      <c r="D138">
+        <v>0.70495101000000004</v>
+      </c>
+      <c r="E138">
+        <v>0.69367525200000002</v>
+      </c>
+      <c r="F138">
+        <v>0.48970665099999999</v>
+      </c>
+      <c r="G138">
+        <v>0.48013865100000003</v>
+      </c>
+      <c r="H138">
+        <v>0.68973994000000005</v>
+      </c>
+      <c r="I138">
+        <v>0.68392256299999998</v>
+      </c>
+      <c r="J138">
+        <v>0.68945732000000004</v>
+      </c>
+      <c r="K138">
+        <v>0.68363464689999998</v>
+      </c>
+      <c r="L138" s="50">
+        <f t="shared" si="2"/>
+        <v>0.69845201099999998</v>
+      </c>
+      <c r="M138" s="48">
+        <f>LARGE((C138,E138,G138,I138,K138),2)</f>
+        <v>0.69367525200000002</v>
+      </c>
+      <c r="N138" s="52">
+        <f t="shared" si="3"/>
+        <v>6.839065425784799E-3</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B139">
+        <v>6.7793010000000001E-2</v>
+      </c>
+      <c r="C139">
+        <v>1.3313380999999999E-2</v>
+      </c>
+      <c r="D139">
+        <v>5.6186439999999997E-2</v>
+      </c>
+      <c r="E139">
+        <v>2.0117126999999999E-2</v>
+      </c>
+      <c r="F139">
+        <v>4.7529810999999998E-2</v>
+      </c>
+      <c r="G139">
+        <v>2.9670994999999999E-2</v>
+      </c>
+      <c r="H139">
+        <v>4.5046049999999997E-2</v>
+      </c>
+      <c r="I139">
+        <v>2.7140666000000001E-2</v>
+      </c>
+      <c r="J139">
+        <v>5.5453240000000001E-2</v>
+      </c>
+      <c r="K139">
+        <v>3.7742985600000001E-2</v>
+      </c>
+      <c r="L139" s="51">
+        <f t="shared" si="2"/>
+        <v>3.7742985600000001E-2</v>
+      </c>
+      <c r="M139" s="49">
+        <f>LARGE((C139,E139,G139,I139,K139),2)</f>
+        <v>2.9670994999999999E-2</v>
+      </c>
+      <c r="N139" s="53">
+        <f t="shared" si="3"/>
+        <v>0.2138673046575309</v>
+      </c>
+      <c r="O139" s="3"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A140" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140">
+        <v>7.7483960000000004E-2</v>
+      </c>
+      <c r="C140">
+        <v>1.9423513999999999E-2</v>
+      </c>
+      <c r="D140">
+        <v>4.2191029999999997E-2</v>
+      </c>
+      <c r="E140">
+        <v>2.829022E-3</v>
+      </c>
+      <c r="F140">
+        <v>1.5197781E-2</v>
+      </c>
+      <c r="G140">
+        <v>-4.6304520000000002E-3</v>
+      </c>
+      <c r="H140">
+        <v>2.8869369999999998E-2</v>
+      </c>
+      <c r="I140">
+        <v>9.3164089999999995E-3</v>
+      </c>
+      <c r="J140">
+        <v>1.5891010000000001E-2</v>
+      </c>
+      <c r="K140">
+        <v>-3.9232681000000002E-3</v>
+      </c>
+      <c r="L140" s="51">
+        <f t="shared" si="2"/>
+        <v>1.9423513999999999E-2</v>
+      </c>
+      <c r="M140" s="49">
+        <f>LARGE((C140,E140,G140,I140,K140),2)</f>
+        <v>9.3164089999999995E-3</v>
+      </c>
+      <c r="N140" s="53">
+        <f t="shared" si="3"/>
+        <v>0.5203540924675113</v>
+      </c>
+      <c r="O140" s="3"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>39</v>
+      </c>
+      <c r="B141">
+        <v>0.32211118999999999</v>
+      </c>
+      <c r="C141">
+        <v>0.27553867799999998</v>
+      </c>
+      <c r="D141">
+        <v>0.31435220000000003</v>
+      </c>
+      <c r="E141">
+        <v>0.283651553</v>
+      </c>
+      <c r="F141">
+        <v>0.15599575600000001</v>
+      </c>
+      <c r="G141">
+        <v>0.13751391099999999</v>
+      </c>
+      <c r="H141">
+        <v>0.15041676000000001</v>
+      </c>
+      <c r="I141">
+        <v>0.13181275200000001</v>
+      </c>
+      <c r="J141">
+        <v>0.16556546999999999</v>
+      </c>
+      <c r="K141">
+        <v>0.14729318450000001</v>
+      </c>
+      <c r="L141" s="50">
+        <f t="shared" si="2"/>
+        <v>0.283651553</v>
+      </c>
+      <c r="M141" s="48">
+        <f>LARGE((C141,E141,G141,I141,K141),2)</f>
+        <v>0.27553867799999998</v>
+      </c>
+      <c r="N141" s="52">
+        <f t="shared" si="3"/>
+        <v>2.8601553258550357E-2</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142">
+        <v>0.65507234999999997</v>
+      </c>
+      <c r="C142">
+        <v>0.63043465700000001</v>
+      </c>
+      <c r="D142">
+        <v>0.60880564000000004</v>
+      </c>
+      <c r="E142">
+        <v>0.59061055399999995</v>
+      </c>
+      <c r="F142">
+        <v>0.41884480299999999</v>
+      </c>
+      <c r="G142">
+        <v>0.40563673</v>
+      </c>
+      <c r="H142">
+        <v>0.51386726999999999</v>
+      </c>
+      <c r="I142">
+        <v>0.50281879799999996</v>
+      </c>
+      <c r="J142">
+        <v>0.57802350999999996</v>
+      </c>
+      <c r="K142">
+        <v>0.56843313360000003</v>
+      </c>
+      <c r="L142" s="50">
+        <f t="shared" si="2"/>
+        <v>0.63043465700000001</v>
+      </c>
+      <c r="M142" s="48">
+        <f>LARGE((C142,E142,G142,I142,K142),2)</f>
+        <v>0.59061055399999995</v>
+      </c>
+      <c r="N142" s="52">
+        <f t="shared" si="3"/>
+        <v>6.3169279413520657E-2</v>
+      </c>
+      <c r="O142" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>42</v>
+      </c>
+      <c r="B143">
+        <v>0.45279754999999999</v>
+      </c>
+      <c r="C143">
+        <v>0.41034219199999999</v>
+      </c>
+      <c r="D143">
+        <v>0.45250631000000002</v>
+      </c>
+      <c r="E143">
+        <v>0.424901588</v>
+      </c>
+      <c r="F143">
+        <v>0.38007155599999998</v>
+      </c>
+      <c r="G143">
+        <v>0.36482741400000002</v>
+      </c>
+      <c r="H143">
+        <v>0.42393012000000002</v>
+      </c>
+      <c r="I143">
+        <v>0.40976446500000002</v>
+      </c>
+      <c r="J143">
+        <v>0.44030248999999999</v>
+      </c>
+      <c r="K143">
+        <v>0.42653943480000001</v>
+      </c>
+      <c r="L143" s="50">
+        <f t="shared" si="2"/>
+        <v>0.42653943480000001</v>
+      </c>
+      <c r="M143" s="48">
+        <f>LARGE((C143,E143,G143,I143,K143),2)</f>
+        <v>0.424901588</v>
+      </c>
+      <c r="N143" s="52">
+        <f t="shared" si="3"/>
+        <v>3.839848479116541E-3</v>
+      </c>
+      <c r="O143" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A144" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B144">
+        <v>5.7508160000000003E-2</v>
+      </c>
+      <c r="C144">
+        <v>-2.251473E-2</v>
+      </c>
+      <c r="D144">
+        <v>3.8341010000000002E-2</v>
+      </c>
+      <c r="E144">
+        <v>-1.4594351E-2</v>
+      </c>
+      <c r="F144">
+        <v>1.6856495999999999E-2</v>
+      </c>
+      <c r="G144">
+        <v>-9.4777049999999995E-3</v>
+      </c>
+      <c r="H144">
+        <v>1.9170130000000001E-2</v>
+      </c>
+      <c r="I144">
+        <v>-7.1020980000000003E-3</v>
+      </c>
+      <c r="J144">
+        <v>2.650054E-2</v>
+      </c>
+      <c r="K144">
+        <v>4.246664E-4</v>
+      </c>
+      <c r="L144" s="51">
+        <f t="shared" si="2"/>
+        <v>4.246664E-4</v>
+      </c>
+      <c r="M144" s="49">
+        <f>LARGE((C144,E144,G144,I144,K144),2)</f>
+        <v>-7.1020980000000003E-3</v>
+      </c>
+      <c r="N144" s="53">
+        <f t="shared" si="3"/>
+        <v>17.7239461374858</v>
+      </c>
+      <c r="O144" s="3"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>40</v>
+      </c>
+      <c r="B145">
+        <v>0.38952782000000002</v>
+      </c>
+      <c r="C145">
+        <v>0.33403035199999997</v>
+      </c>
+      <c r="D145">
+        <v>0.34272408999999998</v>
+      </c>
+      <c r="E145">
+        <v>0.30406079899999999</v>
+      </c>
+      <c r="F145">
+        <v>6.3055400999999997E-2</v>
+      </c>
+      <c r="G145">
+        <v>3.6285554999999997E-2</v>
+      </c>
+      <c r="H145">
+        <v>0.24671897000000001</v>
+      </c>
+      <c r="I145">
+        <v>0.22519665699999999</v>
+      </c>
+      <c r="J145">
+        <v>0.24152883</v>
+      </c>
+      <c r="K145">
+        <v>0.21985822839999999</v>
+      </c>
+      <c r="L145" s="50">
+        <f t="shared" si="2"/>
+        <v>0.33403035199999997</v>
+      </c>
+      <c r="M145" s="48">
+        <f>LARGE((C145,E145,G145,I145,K145),2)</f>
+        <v>0.30406079899999999</v>
+      </c>
+      <c r="N145" s="52">
+        <f t="shared" si="3"/>
+        <v>8.9721047265788542E-2</v>
+      </c>
+      <c r="O145" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>38</v>
+      </c>
+      <c r="B146">
+        <v>0.23535848000000001</v>
+      </c>
+      <c r="C146">
+        <v>0.160556595</v>
+      </c>
+      <c r="D146">
+        <v>0.22927212999999999</v>
+      </c>
+      <c r="E146">
+        <v>0.18059457800000001</v>
+      </c>
+      <c r="F146">
+        <v>0.183947796</v>
+      </c>
+      <c r="G146">
+        <v>0.15896660600000001</v>
+      </c>
+      <c r="H146">
+        <v>0.16232949999999999</v>
+      </c>
+      <c r="I146">
+        <v>0.136686522</v>
+      </c>
+      <c r="J146">
+        <v>0.22609920999999999</v>
+      </c>
+      <c r="K146">
+        <v>0.20240836940000001</v>
+      </c>
+      <c r="L146" s="50">
+        <f t="shared" si="2"/>
+        <v>0.20240836940000001</v>
+      </c>
+      <c r="M146" s="48">
+        <f>LARGE((C146,E146,G146,I146,K146),2)</f>
+        <v>0.18059457800000001</v>
+      </c>
+      <c r="N146" s="52">
+        <f t="shared" si="3"/>
+        <v>0.10777119278546989</v>
+      </c>
+      <c r="O146" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A54:K82"/>
+  <mergeCells count="7">
+    <mergeCell ref="L117:L118"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:E117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="H117:I117"/>
+    <mergeCell ref="J117:K117"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B119:K119">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>$L$119</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120:K146">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>$L$119</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B119:K146">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>$L119</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B119:K146">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>$M119</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:S122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1392,23 +7090,23 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="N19" s="29" t="s">
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="N19" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="O19" s="29"/>
+      <c r="O19" s="22"/>
       <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -1451,10 +7149,10 @@
       <c r="M20" t="s">
         <v>93</v>
       </c>
-      <c r="N20" s="30" t="s">
+      <c r="N20" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="O20" s="30" t="s">
+      <c r="O20" s="23" t="s">
         <v>28</v>
       </c>
       <c r="P20" s="3" t="s">
@@ -1490,7 +7188,7 @@
         <v>0.49597882999999998</v>
       </c>
       <c r="L21">
-        <f>COUNTIF(B21:J21,"X")</f>
+        <f t="shared" ref="L21:L40" si="0">COUNTIF(B21:J21,"X")</f>
         <v>6</v>
       </c>
       <c r="N21">
@@ -1529,7 +7227,7 @@
         <v>0.14905921999999999</v>
       </c>
       <c r="L22" s="8">
-        <f>COUNTIF(B22:J22,"X")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N22" s="8">
@@ -1569,10 +7267,10 @@
         <v>0.31476583000000002</v>
       </c>
       <c r="L23" s="17">
-        <f>COUNTIF(B23:J23,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M23" s="28" t="s">
+      <c r="M23" s="21" t="s">
         <v>92</v>
       </c>
       <c r="N23">
@@ -1582,7 +7280,7 @@
         <v>0.30584286999999999</v>
       </c>
       <c r="P23" s="5">
-        <f t="shared" ref="P22:P40" si="0">(K23-O23)/K23</f>
+        <f t="shared" ref="P23:P40" si="1">(K23-O23)/K23</f>
         <v>2.8347930904698376E-2</v>
       </c>
     </row>
@@ -1611,7 +7309,7 @@
         <v>0.13768622999999999</v>
       </c>
       <c r="L24" s="8">
-        <f>COUNTIF(B24:J24,"X")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N24" s="8">
@@ -1645,7 +7343,7 @@
         <v>8.1635509999999994E-2</v>
       </c>
       <c r="L25" s="8">
-        <f>COUNTIF(B25:J25,"X")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N25" s="8">
@@ -1687,7 +7385,7 @@
         <v>0.64882229000000002</v>
       </c>
       <c r="L26">
-        <f>COUNTIF(B26:J26,"X")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N26">
@@ -1697,7 +7395,7 @@
         <v>0.64492793999999998</v>
       </c>
       <c r="P26" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.002182816499794E-3</v>
       </c>
     </row>
@@ -1730,7 +7428,7 @@
         <v>0.65250063000000003</v>
       </c>
       <c r="L27">
-        <f>COUNTIF(B27:J27,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N27">
@@ -1740,7 +7438,7 @@
         <v>0.64602411999999998</v>
       </c>
       <c r="P27" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.9256762403433178E-3</v>
       </c>
     </row>
@@ -1765,7 +7463,7 @@
         <v>3.1221499999999999E-2</v>
       </c>
       <c r="L28" s="8">
-        <f>COUNTIF(B28:J28,"X")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N28" s="8">
@@ -1805,7 +7503,7 @@
         <v>0.78485329999999998</v>
       </c>
       <c r="L29">
-        <f>COUNTIF(B29:J29,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N29">
@@ -1815,7 +7513,7 @@
         <v>0.78134999999999999</v>
       </c>
       <c r="P29" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.463636707649681E-3</v>
       </c>
     </row>
@@ -1850,7 +7548,7 @@
         <v>0.66794257999999995</v>
       </c>
       <c r="L30">
-        <f>COUNTIF(B30:J30,"X")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N30">
@@ -1860,7 +7558,7 @@
         <v>0.66461778000000005</v>
       </c>
       <c r="P30" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.9776733802476044E-3</v>
       </c>
     </row>
@@ -1893,7 +7591,7 @@
         <v>0.84131948999999995</v>
       </c>
       <c r="L31">
-        <f>COUNTIF(B31:J31,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N31">
@@ -1903,7 +7601,7 @@
         <v>0.83843056999999999</v>
       </c>
       <c r="P31" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.433796594917778E-3</v>
       </c>
     </row>
@@ -1930,7 +7628,7 @@
         <v>0.50225642000000004</v>
       </c>
       <c r="L32">
-        <f>COUNTIF(B32:J32,"X")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N32">
@@ -1940,7 +7638,7 @@
         <v>0.49485221000000001</v>
       </c>
       <c r="P32" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.4741892199207771E-2</v>
       </c>
     </row>
@@ -1973,10 +7671,10 @@
         <v>0.61341528999999995</v>
       </c>
       <c r="L33" s="17">
-        <f>COUNTIF(B33:J33,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M33" s="28" t="s">
+      <c r="M33" s="21" t="s">
         <v>92</v>
       </c>
       <c r="N33">
@@ -1986,7 +7684,7 @@
         <v>0.60635189</v>
       </c>
       <c r="P33" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1514874368390691E-2</v>
       </c>
     </row>
@@ -2019,7 +7717,7 @@
         <v>0.71935037000000002</v>
       </c>
       <c r="L34">
-        <f>COUNTIF(B34:J34,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N34">
@@ -2029,7 +7727,7 @@
         <v>0.71382352000000004</v>
       </c>
       <c r="P34" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.6831127507447751E-3</v>
       </c>
     </row>
@@ -2060,7 +7758,7 @@
         <v>0.79495139000000004</v>
       </c>
       <c r="L35">
-        <f>COUNTIF(B35:J35,"X")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N35">
@@ -2070,7 +7768,7 @@
         <v>0.79088824000000002</v>
       </c>
       <c r="P35" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.1111930252741812E-3</v>
       </c>
     </row>
@@ -2101,7 +7799,7 @@
         <v>0.35120868999999999</v>
       </c>
       <c r="L36">
-        <f>COUNTIF(B36:J36,"X")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N36">
@@ -2111,7 +7809,7 @@
         <v>0.33306796999999999</v>
       </c>
       <c r="P36" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.1652252682016495E-2</v>
       </c>
     </row>
@@ -2144,10 +7842,10 @@
         <v>0.40059250000000002</v>
       </c>
       <c r="L37" s="17">
-        <f>COUNTIF(B37:J37,"X")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M37" s="28" t="s">
+      <c r="M37" s="21" t="s">
         <v>92</v>
       </c>
       <c r="N37">
@@ -2157,7 +7855,7 @@
         <v>0.38565495</v>
       </c>
       <c r="P37" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.7288641200222225E-2</v>
       </c>
     </row>
@@ -2186,7 +7884,7 @@
         <v>0.68871134000000001</v>
       </c>
       <c r="L38">
-        <f>COUNTIF(B38:J38,"X")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N38">
@@ -2196,7 +7894,7 @@
         <v>0.68035904000000003</v>
       </c>
       <c r="P38" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2127432082067909E-2</v>
       </c>
     </row>
@@ -2231,10 +7929,10 @@
         <v>0.74122326999999999</v>
       </c>
       <c r="L39" s="17">
-        <f>COUNTIF(B39:J39,"X")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="M39" s="28" t="s">
+      <c r="M39" s="21" t="s">
         <v>92</v>
       </c>
       <c r="N39">
@@ -2244,7 +7942,7 @@
         <v>0.73572656999999997</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.4157142961796402E-3</v>
       </c>
     </row>
@@ -2279,7 +7977,7 @@
         <v>0.70402909000000002</v>
       </c>
       <c r="L40">
-        <f>COUNTIF(B40:J40,"X")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N40">
@@ -2289,7 +7987,7 @@
         <v>0.69802202999999996</v>
       </c>
       <c r="P40" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5324031141952722E-3</v>
       </c>
     </row>
@@ -2299,19 +7997,19 @@
       <c r="P41" s="14"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -2414,11 +8112,11 @@
         <v>0.14702638000000001</v>
       </c>
       <c r="L46" s="5">
-        <f t="shared" ref="L46:L64" si="1">(K22-K46)/K22</f>
+        <f t="shared" ref="L46:L64" si="2">(K22-K46)/K22</f>
         <v>1.3637801137024468E-2</v>
       </c>
       <c r="M46">
-        <f t="shared" ref="M46:M64" si="2">COUNTIF(B46:J46,"X")</f>
+        <f t="shared" ref="M46:M64" si="3">COUNTIF(B46:J46,"X")</f>
         <v>3</v>
       </c>
     </row>
@@ -2453,11 +8151,11 @@
         <v>0.31421829000000001</v>
       </c>
       <c r="L47" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7395153724278553E-3</v>
       </c>
       <c r="M47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -2488,11 +8186,11 @@
         <v>0.13643227999999999</v>
       </c>
       <c r="L48" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.107301434573405E-3</v>
       </c>
       <c r="M48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -2519,11 +8217,11 @@
         <v>8.1494460000000005E-2</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7278020312482866E-3</v>
       </c>
       <c r="M49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -2556,11 +8254,11 @@
         <v>0.64807557999999998</v>
       </c>
       <c r="L50" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1508698321693591E-3</v>
       </c>
       <c r="M50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -2595,11 +8293,11 @@
         <v>0.65066784</v>
       </c>
       <c r="L51" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.808870851205199E-3</v>
       </c>
       <c r="M51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -2624,11 +8322,11 @@
         <v>3.0166599999999998E-2</v>
       </c>
       <c r="L52" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.3787614304245504E-2</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -2663,11 +8361,11 @@
         <v>0.78436099999999997</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.2725097798531403E-4</v>
       </c>
       <c r="M53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -2698,11 +8396,11 @@
         <v>0.66747504999999996</v>
       </c>
       <c r="L54" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.9995537640375283E-4</v>
       </c>
       <c r="M54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -2737,11 +8435,11 @@
         <v>0.84075907000000005</v>
       </c>
       <c r="L55" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6612031060863091E-4</v>
       </c>
       <c r="M55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -2774,11 +8472,11 @@
         <v>0.50187263999999998</v>
       </c>
       <c r="L56" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.6411168621807904E-4</v>
       </c>
       <c r="M56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -2813,11 +8511,11 @@
         <v>0.61236919999999995</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7053536438584693E-3</v>
       </c>
       <c r="M57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -2848,11 +8546,11 @@
         <v>0.71911272999999998</v>
       </c>
       <c r="L58" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.3035362169903234E-4</v>
       </c>
       <c r="M58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -2885,11 +8583,11 @@
         <v>0.79489098000000002</v>
       </c>
       <c r="L59" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.5992067892366005E-5</v>
       </c>
       <c r="M59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -2922,11 +8620,11 @@
         <v>0.35025242000000001</v>
       </c>
       <c r="L60" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.722797092520636E-3</v>
       </c>
       <c r="M60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -2959,11 +8657,11 @@
         <v>0.39921584999999998</v>
       </c>
       <c r="L61" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4365346330748449E-3</v>
       </c>
       <c r="M61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -2994,11 +8692,11 @@
         <v>0.68845029000000002</v>
       </c>
       <c r="L62" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.7904123954164151E-4</v>
       </c>
       <c r="M62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -3031,11 +8729,11 @@
         <v>0.74069196000000004</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.1680156506682741E-4</v>
       </c>
       <c r="M63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -3068,28 +8766,28 @@
         <v>0.70133303999999996</v>
       </c>
       <c r="L64" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.8294582401418396E-3</v>
       </c>
       <c r="M64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A67" s="24" t="s">
+      <c r="A67" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="24"/>
-      <c r="K67" s="24"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="27"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -3196,11 +8894,11 @@
         <v>0.14609643</v>
       </c>
       <c r="L70" s="5">
-        <f t="shared" ref="L70:L88" si="3">(K22-K70)/K22</f>
+        <f t="shared" ref="L70:L88" si="4">(K22-K70)/K22</f>
         <v>1.9876596697607791E-2</v>
       </c>
       <c r="M70">
-        <f t="shared" ref="M70:M88" si="4">COUNTIF(B70:J70,"X")</f>
+        <f t="shared" ref="M70:M88" si="5">COUNTIF(B70:J70,"X")</f>
         <v>4</v>
       </c>
     </row>
@@ -3233,11 +8931,11 @@
         <v>0.31147134999999998</v>
       </c>
       <c r="L71" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0466447390430034E-2</v>
       </c>
       <c r="M71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -3268,11 +8966,11 @@
         <v>0.13494734</v>
       </c>
       <c r="L72" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9892257925865166E-2</v>
       </c>
       <c r="M72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -3299,11 +8997,11 @@
         <v>7.9927860000000003E-2</v>
       </c>
       <c r="L73" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.0917980422980039E-2</v>
       </c>
       <c r="M73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -3334,11 +9032,11 @@
         <v>0.64793535999999996</v>
       </c>
       <c r="L74" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.3669844789087986E-3</v>
       </c>
       <c r="M74">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -3373,11 +9071,11 @@
         <v>0.65020880999999997</v>
       </c>
       <c r="L75" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.5123644248436286E-3</v>
       </c>
       <c r="M75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -3404,11 +9102,11 @@
         <v>2.5905569999999999E-2</v>
       </c>
       <c r="L76" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.17026504171804685</v>
       </c>
       <c r="M76" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -3439,11 +9137,11 @@
         <v>0.78396732000000002</v>
       </c>
       <c r="L77" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.128847900620349E-3</v>
       </c>
       <c r="M77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -3476,11 +9174,11 @@
         <v>0.66740323000000001</v>
       </c>
       <c r="L78" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.0747958903883404E-4</v>
       </c>
       <c r="M78">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -3515,11 +9213,11 @@
         <v>0.84023639999999999</v>
       </c>
       <c r="L79" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2873706277741804E-3</v>
       </c>
       <c r="M79">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -3550,11 +9248,11 @@
         <v>0.50180722</v>
       </c>
       <c r="L80" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.943638789127642E-4</v>
       </c>
       <c r="M80">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -3589,11 +9287,11 @@
         <v>0.61042788999999997</v>
       </c>
       <c r="L81" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8701101011029146E-3</v>
       </c>
       <c r="M81">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -3626,11 +9324,11 @@
         <v>0.71883783000000001</v>
       </c>
       <c r="L82" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.1250397772090637E-4</v>
       </c>
       <c r="M82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -3663,11 +9361,11 @@
         <v>0.79449654000000003</v>
       </c>
       <c r="L83" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.7217335012145411E-4</v>
       </c>
       <c r="M83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -3698,11 +9396,11 @@
         <v>0.34961182000000002</v>
       </c>
       <c r="L84" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.5467838509348178E-3</v>
       </c>
       <c r="M84">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -3733,11 +9431,11 @@
         <v>0.39826609000000002</v>
       </c>
       <c r="L85" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8074227550440928E-3</v>
       </c>
       <c r="M85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -3766,11 +9464,11 @@
         <v>0.68820766</v>
       </c>
       <c r="L86" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.3133687620129258E-4</v>
       </c>
       <c r="M86">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -3805,11 +9503,11 @@
         <v>0.73882338000000003</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2377423876613588E-3</v>
       </c>
       <c r="M87">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -3846,33 +9544,33 @@
         <v>0.70130506999999997</v>
       </c>
       <c r="L88" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.8691867121570917E-3</v>
       </c>
       <c r="M88">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="25" t="s">
+      <c r="A91" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="25"/>
-      <c r="E91" s="26" t="s">
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F91" s="26"/>
-      <c r="G91" s="26"/>
-      <c r="H91" s="26"/>
-      <c r="I91" s="27" t="s">
+      <c r="F91" s="29"/>
+      <c r="G91" s="29"/>
+      <c r="H91" s="29"/>
+      <c r="I91" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="J91" s="27"/>
-      <c r="K91" s="27"/>
-      <c r="L91" s="27"/>
+      <c r="J91" s="30"/>
+      <c r="K91" s="30"/>
+      <c r="L91" s="30"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
@@ -3960,7 +9658,7 @@
         <v>0.12258187</v>
       </c>
       <c r="D94" s="5">
-        <f t="shared" ref="D94:D112" si="5">($K22-C94)/$K22</f>
+        <f t="shared" ref="D94:D112" si="6">($K22-C94)/$K22</f>
         <v>0.17762973669122914</v>
       </c>
       <c r="F94">
@@ -3970,7 +9668,7 @@
         <v>0.114260429</v>
       </c>
       <c r="H94" s="5">
-        <f t="shared" ref="H94:H112" si="6">($K22-G94)/$K22</f>
+        <f t="shared" ref="H94:H112" si="7">($K22-G94)/$K22</f>
         <v>0.23345614581909122</v>
       </c>
       <c r="J94">
@@ -3980,7 +9678,7 @@
         <v>0.11799842000000001</v>
       </c>
       <c r="L94" s="5">
-        <f t="shared" ref="L94:L112" si="7">($K22-K94)/$K22</f>
+        <f t="shared" ref="L94:L112" si="8">($K22-K94)/$K22</f>
         <v>0.20837892483269393</v>
       </c>
       <c r="M94">
@@ -3998,7 +9696,7 @@
         <v>0.27990563000000002</v>
       </c>
       <c r="D95" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11074963251252529</v>
       </c>
       <c r="F95">
@@ -4008,7 +9706,7 @@
         <v>0.26613183099999999</v>
       </c>
       <c r="H95" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15450850875395222</v>
       </c>
       <c r="J95">
@@ -4018,7 +9716,7 @@
         <v>0.25940548000000002</v>
       </c>
       <c r="L95" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.17587788992216849</v>
       </c>
       <c r="M95">
@@ -4036,7 +9734,7 @@
         <v>0.13243809000000001</v>
       </c>
       <c r="D96" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.8116665697070687E-2</v>
       </c>
       <c r="F96">
@@ -4046,7 +9744,7 @@
         <v>0.11303724699999999</v>
       </c>
       <c r="H96" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17902286234433176</v>
       </c>
       <c r="J96">
@@ -4056,7 +9754,7 @@
         <v>0.12273924</v>
       </c>
       <c r="L96" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.1085583503884157</v>
       </c>
       <c r="M96">
@@ -4074,7 +9772,7 @@
         <v>7.2382210000000002E-2</v>
       </c>
       <c r="D97" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11334895806983986</v>
       </c>
       <c r="F97">
@@ -4084,7 +9782,7 @@
         <v>7.6581015000000002E-2</v>
       </c>
       <c r="H97" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.1915396865898094E-2</v>
       </c>
       <c r="J97">
@@ -4094,7 +9792,7 @@
         <v>7.2840150000000006E-2</v>
       </c>
       <c r="L97" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.10773938939071966</v>
       </c>
       <c r="M97">
@@ -4112,7 +9810,7 @@
         <v>0.64793535999999996</v>
       </c>
       <c r="D98" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3669844789087986E-3</v>
       </c>
       <c r="F98">
@@ -4122,7 +9820,7 @@
         <v>0.63312285499999998</v>
       </c>
       <c r="H98" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.4196818207340008E-2</v>
       </c>
       <c r="J98">
@@ -4132,7 +9830,7 @@
         <v>0.63037947999999999</v>
       </c>
       <c r="L98" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.8425056112051931E-2</v>
       </c>
       <c r="M98">
@@ -4150,7 +9848,7 @@
         <v>0.61992572999999995</v>
       </c>
       <c r="D99" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.9923170189123144E-2</v>
       </c>
       <c r="F99">
@@ -4160,7 +9858,7 @@
         <v>0.38677330700000001</v>
       </c>
       <c r="H99" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.40724454626197065</v>
       </c>
       <c r="J99">
@@ -4170,7 +9868,7 @@
         <v>0.59591439000000002</v>
       </c>
       <c r="L99" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.6722123164846607E-2</v>
       </c>
       <c r="M99">
@@ -4188,7 +9886,7 @@
         <v>1.3543589999999999E-2</v>
       </c>
       <c r="D100" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.56620950306679685</v>
       </c>
       <c r="F100">
@@ -4198,7 +9896,7 @@
         <v>-9.3062709999999996E-3</v>
       </c>
       <c r="H100" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.298072514132889</v>
       </c>
       <c r="J100">
@@ -4208,7 +9906,7 @@
         <v>1.140445E-2</v>
       </c>
       <c r="L100" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.6347244687154685</v>
       </c>
       <c r="M100">
@@ -4226,7 +9924,7 @@
         <v>0.74752903000000004</v>
       </c>
       <c r="D101" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.7555727930302313E-2</v>
       </c>
       <c r="F101">
@@ -4236,7 +9934,7 @@
         <v>0.74917542800000003</v>
       </c>
       <c r="H101" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5458013618595916E-2</v>
       </c>
       <c r="J101">
@@ -4246,7 +9944,7 @@
         <v>0.64573950000000002</v>
       </c>
       <c r="L101" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.17724815580185488</v>
       </c>
       <c r="M101">
@@ -4264,7 +9962,7 @@
         <v>0.66516726000000004</v>
       </c>
       <c r="D102" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.1550278169119187E-3</v>
       </c>
       <c r="F102">
@@ -4274,7 +9972,7 @@
         <v>0.47592249800000003</v>
       </c>
       <c r="H102" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.28747992379824017</v>
       </c>
       <c r="J102">
@@ -4284,7 +9982,7 @@
         <v>0.60201497999999998</v>
       </c>
       <c r="L102" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.8702496253495295E-2</v>
       </c>
       <c r="M102">
@@ -4302,7 +10000,7 @@
         <v>0.83524821999999999</v>
       </c>
       <c r="D103" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.2163667574133604E-3</v>
       </c>
       <c r="F103">
@@ -4312,7 +10010,7 @@
         <v>0.77147718099999996</v>
       </c>
       <c r="H103" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.3015203891211406E-2</v>
       </c>
       <c r="J103">
@@ -4322,7 +10020,7 @@
         <v>0.82296793000000001</v>
       </c>
       <c r="L103" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.1812831175466927E-2</v>
       </c>
       <c r="M103">
@@ -4340,7 +10038,7 @@
         <v>0.48807392999999999</v>
       </c>
       <c r="D104" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.8237548461799745E-2</v>
       </c>
       <c r="F104">
@@ -4350,7 +10048,7 @@
         <v>0.47176416100000002</v>
       </c>
       <c r="H104" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.0710541041964224E-2</v>
       </c>
       <c r="J104">
@@ -4360,7 +10058,7 @@
         <v>0.47022510000000001</v>
       </c>
       <c r="L104" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.3774834376432721E-2</v>
       </c>
       <c r="M104">
@@ -4378,7 +10076,7 @@
         <v>0.53694527999999997</v>
       </c>
       <c r="D105" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.12466270607633531</v>
       </c>
       <c r="F105">
@@ -4388,7 +10086,7 @@
         <v>0.456401153</v>
       </c>
       <c r="H105" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.25596710672145123</v>
       </c>
       <c r="J105">
@@ -4398,7 +10096,7 @@
         <v>0.51081695000000005</v>
       </c>
       <c r="L105" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.16725755238347564</v>
       </c>
       <c r="M105">
@@ -4416,7 +10114,7 @@
         <v>0.71595229999999999</v>
       </c>
       <c r="D106" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.7238037842394255E-3</v>
       </c>
       <c r="F106">
@@ -4426,7 +10124,7 @@
         <v>0.651378499</v>
       </c>
       <c r="H106" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.4490631873866998E-2</v>
       </c>
       <c r="J106">
@@ -4436,7 +10134,7 @@
         <v>0.71653913999999996</v>
       </c>
       <c r="L106" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.9080121693689449E-3</v>
       </c>
       <c r="M106">
@@ -4454,7 +10152,7 @@
         <v>0.75404590999999999</v>
       </c>
       <c r="D107" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.1456580257064587E-2</v>
       </c>
       <c r="F107">
@@ -4464,7 +10162,7 @@
         <v>0.43429089500000001</v>
       </c>
       <c r="H107" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.45368874064111014</v>
       </c>
       <c r="J107">
@@ -4474,7 +10172,7 @@
         <v>0.72608625999999998</v>
       </c>
       <c r="L107" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.6628101876770155E-2</v>
       </c>
       <c r="M107">
@@ -4492,7 +10190,7 @@
         <v>0.35120868999999999</v>
       </c>
       <c r="D108" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F108">
@@ -4502,7 +10200,7 @@
         <v>0.31615543299999999</v>
       </c>
       <c r="H108" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.9807487679191551E-2</v>
       </c>
       <c r="J108">
@@ -4512,7 +10210,7 @@
         <v>0.34289783000000001</v>
       </c>
       <c r="L108" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.3663594428714095E-2</v>
       </c>
       <c r="M108">
@@ -4530,7 +10228,7 @@
         <v>0.35721820999999998</v>
       </c>
       <c r="D109" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.10827534214944123</v>
       </c>
       <c r="F109">
@@ -4540,7 +10238,7 @@
         <v>0.139313826</v>
       </c>
       <c r="H109" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.65223056847045324</v>
       </c>
       <c r="J109">
@@ -4550,7 +10248,7 @@
         <v>0.25219128000000002</v>
       </c>
       <c r="L109" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.37045431454657785</v>
       </c>
       <c r="M109">
@@ -4568,7 +10266,7 @@
         <v>0.68597715000000004</v>
       </c>
       <c r="D110" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.9700086831733735E-3</v>
       </c>
       <c r="F110">
@@ -4578,7 +10276,7 @@
         <v>0.47226348299999998</v>
       </c>
       <c r="H110" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.31427950206250416</v>
       </c>
       <c r="J110">
@@ -4588,7 +10286,7 @@
         <v>0.63629595999999999</v>
       </c>
       <c r="L110" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.6106457024506108E-2</v>
       </c>
       <c r="M110">
@@ -4606,7 +10304,7 @@
         <v>0.67941757999999997</v>
       </c>
       <c r="D111" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.3383364367392326E-2</v>
       </c>
       <c r="F111">
@@ -4616,7 +10314,7 @@
         <v>0.50368180500000004</v>
       </c>
       <c r="H111" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.32047221750067284</v>
       </c>
       <c r="J111">
@@ -4626,7 +10324,7 @@
         <v>0.68198822999999997</v>
       </c>
       <c r="L111" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.991524604995201E-2</v>
       </c>
       <c r="M111">
@@ -4644,7 +10342,7 @@
         <v>0.68517501999999997</v>
       </c>
       <c r="D112" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.6780242844795028E-2</v>
       </c>
       <c r="F112">
@@ -4654,7 +10352,7 @@
         <v>0.473123132</v>
       </c>
       <c r="H112" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.32797786523281308</v>
       </c>
       <c r="J112">
@@ -4664,7 +10362,7 @@
         <v>0.67435314000000002</v>
       </c>
       <c r="L112" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.2151596321112247E-2</v>
       </c>
       <c r="M112">
@@ -4672,22 +10370,22 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="22" t="s">
+      <c r="A114" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B114" s="22"/>
-      <c r="C114" s="22"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25"/>
       <c r="D114" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E114" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H114" s="23" t="s">
+      <c r="H114" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="I114" s="23"/>
-      <c r="J114" s="23"/>
+      <c r="I114" s="26"/>
+      <c r="J114" s="26"/>
       <c r="K114" s="10" t="s">
         <v>32</v>
       </c>
@@ -4695,11 +10393,11 @@
         <v>28</v>
       </c>
       <c r="N114" s="9"/>
-      <c r="O114" s="21" t="s">
+      <c r="O114" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="P114" s="21"/>
-      <c r="Q114" s="21"/>
+      <c r="P114" s="24"/>
+      <c r="Q114" s="24"/>
       <c r="R114" s="20" t="s">
         <v>32</v>
       </c>
@@ -4747,33 +10445,33 @@
         <v>14</v>
       </c>
       <c r="D116">
-        <f t="shared" ref="D116:D120" si="8">VLOOKUP($B116,$A$93:$K$112,10,FALSE)</f>
+        <f t="shared" ref="D116:D120" si="9">VLOOKUP($B116,$A$93:$K$112,10,FALSE)</f>
         <v>0.63961999000000003</v>
       </c>
       <c r="E116">
-        <f t="shared" ref="E116:E120" si="9">VLOOKUP($B116,$A$93:$K$112,11,FALSE)</f>
+        <f t="shared" ref="E116:E120" si="10">VLOOKUP($B116,$A$93:$K$112,11,FALSE)</f>
         <v>0.63037947999999999</v>
       </c>
       <c r="I116" t="s">
         <v>22</v>
       </c>
       <c r="K116">
-        <f t="shared" ref="K116:K120" si="10">VLOOKUP($I116,$A$93:$K$112,2,FALSE)</f>
+        <f t="shared" ref="K116:K120" si="11">VLOOKUP($I116,$A$93:$K$112,2,FALSE)</f>
         <v>0.75617529000000006</v>
       </c>
       <c r="L116">
-        <f t="shared" ref="L116:L120" si="11">VLOOKUP($I116,$A$93:$K$112,3,FALSE)</f>
+        <f t="shared" ref="L116:L120" si="12">VLOOKUP($I116,$A$93:$K$112,3,FALSE)</f>
         <v>0.74752903000000004</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
       </c>
       <c r="R116">
-        <f t="shared" ref="R116:R122" si="12">VLOOKUP($P116,$A$93:$K$112,2,FALSE)</f>
+        <f t="shared" ref="R116:R122" si="13">VLOOKUP($P116,$A$93:$K$112,2,FALSE)</f>
         <v>0.30121018999999999</v>
       </c>
       <c r="S116">
-        <f t="shared" ref="S116:S122" si="13">VLOOKUP($P116,$A$93:$K$112,3,FALSE)</f>
+        <f t="shared" ref="S116:S122" si="14">VLOOKUP($P116,$A$93:$K$112,3,FALSE)</f>
         <v>0.27990563000000002</v>
       </c>
     </row>
@@ -4782,22 +10480,22 @@
         <v>24</v>
       </c>
       <c r="D117">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.82795474000000002</v>
       </c>
       <c r="E117">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.82296793000000001</v>
       </c>
       <c r="I117" t="s">
         <v>12</v>
       </c>
       <c r="K117">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.67687470000000005</v>
       </c>
       <c r="L117">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.66516726000000004</v>
       </c>
       <c r="P117" s="8" t="s">
@@ -4805,11 +10503,11 @@
       </c>
       <c r="Q117" s="8"/>
       <c r="R117" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.10137027</v>
       </c>
       <c r="S117" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.2382210000000002E-2</v>
       </c>
     </row>
@@ -4818,22 +10516,22 @@
         <v>33</v>
       </c>
       <c r="D118">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.72583293999999998</v>
       </c>
       <c r="E118">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.71653913999999996</v>
       </c>
       <c r="I118" t="s">
         <v>21</v>
       </c>
       <c r="K118">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.50662196999999998</v>
       </c>
       <c r="L118">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.48807392999999999</v>
       </c>
       <c r="P118" s="8" t="s">
@@ -4841,11 +10539,11 @@
       </c>
       <c r="Q118" s="8"/>
       <c r="R118" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.5160779999999998E-2</v>
       </c>
       <c r="S118" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.3543589999999999E-2</v>
       </c>
     </row>
@@ -4854,33 +10552,33 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.36498530000000001</v>
       </c>
       <c r="E119">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.34289783000000001</v>
       </c>
       <c r="I119" t="s">
         <v>34</v>
       </c>
       <c r="K119">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.76429400000000003</v>
       </c>
       <c r="L119">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.75404590999999999</v>
       </c>
       <c r="P119" t="s">
         <v>23</v>
       </c>
       <c r="R119">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.55475507999999996</v>
       </c>
       <c r="S119">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.53694527999999997</v>
       </c>
     </row>
@@ -4889,33 +10587,33 @@
         <v>10</v>
       </c>
       <c r="D120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.68751059000000003</v>
       </c>
       <c r="E120">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.67435314000000002</v>
       </c>
       <c r="I120" t="s">
         <v>15</v>
       </c>
       <c r="K120">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.70065111000000002</v>
       </c>
       <c r="L120">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.68597715000000004</v>
       </c>
       <c r="P120" t="s">
         <v>35</v>
       </c>
       <c r="R120">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.38516524000000002</v>
       </c>
       <c r="S120">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.35721820999999998</v>
       </c>
     </row>
@@ -4924,11 +10622,11 @@
         <v>11</v>
       </c>
       <c r="R121">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.69528800000000002</v>
       </c>
       <c r="S121">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.67941757999999997</v>
       </c>
     </row>
@@ -4938,11 +10636,11 @@
       </c>
       <c r="Q122" s="8"/>
       <c r="R122" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.158413</v>
       </c>
       <c r="S122" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.13243809000000001</v>
       </c>
     </row>
@@ -4964,7 +10662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:Q69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6962,6 +12660,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7b5dc55a-e723-417d-bbd9-2b7384a51092" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008ECFF652E2B7794693435CC41F5B4CA1" ma:contentTypeVersion="18" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="2753c092c6e3650bfb39a0d5920becdb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7b5dc55a-e723-417d-bbd9-2b7384a51092" xmlns:ns4="53b96b38-2798-47b2-a685-55ac0f3a25a3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc10ce64d22c41095b2c63fe6f6b3f8" ns3:_="" ns4:_="">
     <xsd:import namespace="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
@@ -7214,24 +12929,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7b5dc55a-e723-417d-bbd9-2b7384a51092" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98708EEF-3554-4A3F-B1A7-CCD4F989B1B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8394E3-3502-4278-897E-CA609F09FC7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="53b96b38-2798-47b2-a685-55ac0f3a25a3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A63570-DE3B-4061-A252-6F16027443E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7248,29 +12971,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8394E3-3502-4278-897E-CA609F09FC7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="53b96b38-2798-47b2-a685-55ac0f3a25a3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98708EEF-3554-4A3F-B1A7-CCD4F989B1B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/relatorios_internos/sel_var.xlsx
+++ b/relatorios_internos/sel_var.xlsx
@@ -12,13 +12,16 @@
     <workbookView xWindow="1176" yWindow="1116" windowWidth="23748" windowHeight="14496"/>
   </bookViews>
   <sheets>
-    <sheet name="16Out" sheetId="3" r:id="rId1"/>
-    <sheet name="12Out" sheetId="2" r:id="rId2"/>
-    <sheet name="old" sheetId="1" r:id="rId3"/>
+    <sheet name="17Out" sheetId="5" r:id="rId1"/>
+    <sheet name="16Out" sheetId="3" r:id="rId2"/>
+    <sheet name="12Out" sheetId="2" r:id="rId3"/>
+    <sheet name="old" sheetId="1" r:id="rId4"/>
+    <sheet name="aluvioes" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'12Out'!$A$20:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'16Out'!$A$54:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'12Out'!$A$20:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'16Out'!$A$54:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">aluvioes!$F$1:$H$74</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="143">
   <si>
     <t>poco</t>
   </si>
@@ -645,15 +648,64 @@
   <si>
     <t>S</t>
   </si>
+  <si>
+    <t xml:space="preserve">só interessam poços pouco profundos </t>
+  </si>
+  <si>
+    <t>que são usados para rega e não para consumo humano</t>
+  </si>
+  <si>
+    <t>Aluvião?</t>
+  </si>
+  <si>
+    <t>390/99</t>
+  </si>
+  <si>
+    <t>331/15</t>
+  </si>
+  <si>
+    <t>poço</t>
+  </si>
+  <si>
+    <t>aluviao</t>
+  </si>
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>n_obs_prof</t>
+  </si>
+  <si>
+    <t>DIOGO: Este ’n’ é referente à tabela exclusiva da ‘piezo_tejo_loc_zvt’, não é a tabela unificada com as outras variáveis por mês</t>
+  </si>
+  <si>
+    <t>Rosario?</t>
+  </si>
+  <si>
+    <t>n obs</t>
+  </si>
+  <si>
+    <t>precipitação</t>
+  </si>
+  <si>
+    <t>evapotrans</t>
+  </si>
+  <si>
+    <t>maior |r| entre lag=0,1,2</t>
+  </si>
+  <si>
+    <t>LAG do maior |r|</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,8 +779,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -813,8 +890,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -822,12 +917,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF8F5E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F5E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F5E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F5E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -878,26 +988,8 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -912,32 +1004,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -948,49 +1022,73 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill>
@@ -1030,61 +1128,71 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1092,6 +1200,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF3399"/>
       <color rgb="FF80DC8D"/>
       <color rgb="FFFF99FF"/>
     </mruColors>
@@ -1404,7 +1513,3897 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P146"/>
+  <dimension ref="A2:Q108"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <v>221</v>
+      </c>
+      <c r="C25">
+        <v>-0.39458687999999997</v>
+      </c>
+      <c r="D25">
+        <v>0.34561998599999999</v>
+      </c>
+      <c r="E25">
+        <v>-0.53317959999999998</v>
+      </c>
+      <c r="F25">
+        <v>-0.5755112</v>
+      </c>
+      <c r="G25">
+        <v>-0.55507229999999996</v>
+      </c>
+      <c r="H25">
+        <v>0.52976939999999995</v>
+      </c>
+      <c r="I25">
+        <v>0.57711129999999999</v>
+      </c>
+      <c r="J25">
+        <v>-0.50537829999999995</v>
+      </c>
+      <c r="K25">
+        <v>-0.37731389999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>219</v>
+      </c>
+      <c r="C26">
+        <v>7.9875169999999995E-2</v>
+      </c>
+      <c r="D26">
+        <v>-0.14286073399999999</v>
+      </c>
+      <c r="E26">
+        <v>-0.39288689999999998</v>
+      </c>
+      <c r="F26">
+        <v>-0.15650549999999999</v>
+      </c>
+      <c r="G26">
+        <v>-0.32031090000000001</v>
+      </c>
+      <c r="H26">
+        <v>3.9914100000000001E-2</v>
+      </c>
+      <c r="I26">
+        <v>0.22057470000000001</v>
+      </c>
+      <c r="J26">
+        <v>-0.50981569999999998</v>
+      </c>
+      <c r="K26">
+        <v>-0.52520319999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27">
+        <v>217</v>
+      </c>
+      <c r="C27">
+        <v>3.0432020000000001E-2</v>
+      </c>
+      <c r="D27">
+        <v>-3.6058869E-2</v>
+      </c>
+      <c r="E27">
+        <v>-0.31565989999999999</v>
+      </c>
+      <c r="F27">
+        <v>-0.20056399999999999</v>
+      </c>
+      <c r="G27">
+        <v>-0.30683870000000002</v>
+      </c>
+      <c r="H27">
+        <v>0.13347519999999999</v>
+      </c>
+      <c r="I27">
+        <v>0.26110290000000003</v>
+      </c>
+      <c r="J27">
+        <v>-0.397839</v>
+      </c>
+      <c r="K27">
+        <v>-0.422514</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>211</v>
+      </c>
+      <c r="C28">
+        <v>-0.41398369000000002</v>
+      </c>
+      <c r="D28">
+        <v>0.38107204099999997</v>
+      </c>
+      <c r="E28">
+        <v>-0.39063680000000001</v>
+      </c>
+      <c r="F28">
+        <v>-0.42380200000000001</v>
+      </c>
+      <c r="G28">
+        <v>-0.28641100000000003</v>
+      </c>
+      <c r="H28">
+        <v>0.4145779</v>
+      </c>
+      <c r="I28">
+        <v>0.31321270000000001</v>
+      </c>
+      <c r="J28">
+        <v>-0.36381540000000001</v>
+      </c>
+      <c r="K28">
+        <v>-0.21829879999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29">
+        <v>207</v>
+      </c>
+      <c r="C29">
+        <v>-0.52451448000000001</v>
+      </c>
+      <c r="D29">
+        <v>0.58519388299999997</v>
+      </c>
+      <c r="E29">
+        <v>-0.4920794</v>
+      </c>
+      <c r="F29">
+        <v>-0.64855600000000002</v>
+      </c>
+      <c r="G29">
+        <v>-0.49896689999999999</v>
+      </c>
+      <c r="H29">
+        <v>0.75207740000000001</v>
+      </c>
+      <c r="I29">
+        <v>0.70956209999999997</v>
+      </c>
+      <c r="J29">
+        <v>-0.38542389999999999</v>
+      </c>
+      <c r="K29">
+        <v>-0.2399897</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>193</v>
+      </c>
+      <c r="C30">
+        <v>-0.60008320000000004</v>
+      </c>
+      <c r="D30">
+        <v>0.77851369800000003</v>
+      </c>
+      <c r="E30">
+        <v>-0.43510700000000002</v>
+      </c>
+      <c r="F30">
+        <v>-0.61422279999999996</v>
+      </c>
+      <c r="G30">
+        <v>-0.4366756</v>
+      </c>
+      <c r="H30">
+        <v>0.8752685</v>
+      </c>
+      <c r="I30">
+        <v>0.75027869999999997</v>
+      </c>
+      <c r="J30">
+        <v>-0.37806770000000001</v>
+      </c>
+      <c r="K30">
+        <v>-0.1996851</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31">
+        <v>190</v>
+      </c>
+      <c r="C31">
+        <v>-5.3601099999999999E-2</v>
+      </c>
+      <c r="D31">
+        <v>-3.6138160000000002E-3</v>
+      </c>
+      <c r="E31">
+        <v>-0.39707009999999998</v>
+      </c>
+      <c r="F31">
+        <v>-0.29767759999999999</v>
+      </c>
+      <c r="G31">
+        <v>-0.44108570000000002</v>
+      </c>
+      <c r="H31">
+        <v>0.3172355</v>
+      </c>
+      <c r="I31">
+        <v>0.55162960000000005</v>
+      </c>
+      <c r="J31">
+        <v>-0.52899059999999998</v>
+      </c>
+      <c r="K31">
+        <v>-0.53322290000000006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32">
+        <v>178</v>
+      </c>
+      <c r="C32">
+        <v>-0.19285870999999999</v>
+      </c>
+      <c r="D32">
+        <v>0.121830444</v>
+      </c>
+      <c r="E32">
+        <v>-0.45133109999999999</v>
+      </c>
+      <c r="F32">
+        <v>-0.52641269999999996</v>
+      </c>
+      <c r="G32">
+        <v>-0.63243320000000003</v>
+      </c>
+      <c r="H32">
+        <v>0.47159469999999998</v>
+      </c>
+      <c r="I32">
+        <v>0.68404750000000003</v>
+      </c>
+      <c r="J32">
+        <v>-0.51930710000000002</v>
+      </c>
+      <c r="K32">
+        <v>-0.40867039999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>165</v>
+      </c>
+      <c r="C33">
+        <v>-0.42041221000000001</v>
+      </c>
+      <c r="D33">
+        <v>0.50901479500000002</v>
+      </c>
+      <c r="E33">
+        <v>-0.54336549999999995</v>
+      </c>
+      <c r="F33">
+        <v>-0.58711409999999997</v>
+      </c>
+      <c r="G33">
+        <v>-0.55609839999999999</v>
+      </c>
+      <c r="H33">
+        <v>0.75117699999999998</v>
+      </c>
+      <c r="I33">
+        <v>0.80226359999999997</v>
+      </c>
+      <c r="J33">
+        <v>-0.57245999999999997</v>
+      </c>
+      <c r="K33">
+        <v>-0.47081040000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34">
+        <v>136</v>
+      </c>
+      <c r="C34">
+        <v>-0.43785541</v>
+      </c>
+      <c r="D34">
+        <v>0.32800259599999998</v>
+      </c>
+      <c r="E34">
+        <v>-0.49999939999999998</v>
+      </c>
+      <c r="F34">
+        <v>-0.63529959999999996</v>
+      </c>
+      <c r="G34">
+        <v>-0.61011709999999997</v>
+      </c>
+      <c r="H34">
+        <v>0.61579799999999996</v>
+      </c>
+      <c r="I34">
+        <v>0.73315019999999997</v>
+      </c>
+      <c r="J34">
+        <v>-0.4178653</v>
+      </c>
+      <c r="K34">
+        <v>-0.32749889999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>-0.25717851000000003</v>
+      </c>
+      <c r="D35">
+        <v>0.28671358400000002</v>
+      </c>
+      <c r="E35">
+        <v>-0.42654740000000002</v>
+      </c>
+      <c r="F35">
+        <v>-0.35425659999999998</v>
+      </c>
+      <c r="G35">
+        <v>-0.3773108</v>
+      </c>
+      <c r="H35">
+        <v>0.38669179999999997</v>
+      </c>
+      <c r="I35">
+        <v>0.37155939999999998</v>
+      </c>
+      <c r="J35">
+        <v>-0.49380649999999998</v>
+      </c>
+      <c r="K35">
+        <v>-0.37539339999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
+        <v>93</v>
+      </c>
+      <c r="C36">
+        <v>-0.33825144000000001</v>
+      </c>
+      <c r="D36">
+        <v>0.39176819000000002</v>
+      </c>
+      <c r="E36">
+        <v>-0.41452990000000001</v>
+      </c>
+      <c r="F36">
+        <v>-0.4478026</v>
+      </c>
+      <c r="G36">
+        <v>-0.4431408</v>
+      </c>
+      <c r="H36">
+        <v>0.52581869999999997</v>
+      </c>
+      <c r="I36">
+        <v>0.51993789999999995</v>
+      </c>
+      <c r="J36">
+        <v>-0.46779720000000002</v>
+      </c>
+      <c r="K36">
+        <v>-0.2327497</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37">
+        <v>80</v>
+      </c>
+      <c r="C37">
+        <v>-0.13317688999999999</v>
+      </c>
+      <c r="D37">
+        <v>0.17318108900000001</v>
+      </c>
+      <c r="E37">
+        <v>-0.61748230000000004</v>
+      </c>
+      <c r="F37">
+        <v>-0.4163906</v>
+      </c>
+      <c r="G37">
+        <v>-0.48827769999999998</v>
+      </c>
+      <c r="H37">
+        <v>0.3622242</v>
+      </c>
+      <c r="I37">
+        <v>0.47948370000000001</v>
+      </c>
+      <c r="J37">
+        <v>-0.65271170000000001</v>
+      </c>
+      <c r="K37">
+        <v>-0.52450240000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38">
+        <v>79</v>
+      </c>
+      <c r="C38">
+        <v>-5.9588309999999999E-2</v>
+      </c>
+      <c r="D38">
+        <v>7.2607979999999997E-3</v>
+      </c>
+      <c r="E38">
+        <v>-0.57851109999999994</v>
+      </c>
+      <c r="F38">
+        <v>-0.42929719999999999</v>
+      </c>
+      <c r="G38">
+        <v>-0.48486089999999998</v>
+      </c>
+      <c r="H38">
+        <v>0.25145000000000001</v>
+      </c>
+      <c r="I38">
+        <v>0.3908354</v>
+      </c>
+      <c r="J38">
+        <v>-0.71715320000000005</v>
+      </c>
+      <c r="K38">
+        <v>-0.47323320000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39">
+        <v>75</v>
+      </c>
+      <c r="C39">
+        <v>-0.15781184000000001</v>
+      </c>
+      <c r="D39">
+        <v>8.0432884999999996E-2</v>
+      </c>
+      <c r="E39">
+        <v>-0.39785019999999999</v>
+      </c>
+      <c r="F39">
+        <v>-0.4436523</v>
+      </c>
+      <c r="G39">
+        <v>-0.51582320000000004</v>
+      </c>
+      <c r="H39">
+        <v>0.42440489999999997</v>
+      </c>
+      <c r="I39">
+        <v>0.63116110000000003</v>
+      </c>
+      <c r="J39">
+        <v>-0.47856779999999999</v>
+      </c>
+      <c r="K39">
+        <v>-0.42047499999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>74</v>
+      </c>
+      <c r="C40">
+        <v>-0.51675603999999997</v>
+      </c>
+      <c r="D40">
+        <v>0.64079225799999995</v>
+      </c>
+      <c r="E40">
+        <v>-0.42891319999999999</v>
+      </c>
+      <c r="F40">
+        <v>-0.55401840000000002</v>
+      </c>
+      <c r="G40">
+        <v>-0.43189870000000002</v>
+      </c>
+      <c r="H40">
+        <v>0.817326</v>
+      </c>
+      <c r="I40">
+        <v>0.78983199999999998</v>
+      </c>
+      <c r="J40">
+        <v>-0.4136552</v>
+      </c>
+      <c r="K40">
+        <v>-0.3314841</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41">
+        <v>57</v>
+      </c>
+      <c r="C41">
+        <v>-0.46012219999999998</v>
+      </c>
+      <c r="D41">
+        <v>0.30289279800000002</v>
+      </c>
+      <c r="E41">
+        <v>-0.74839960000000005</v>
+      </c>
+      <c r="F41">
+        <v>-0.36223080000000002</v>
+      </c>
+      <c r="G41">
+        <v>-0.13517019999999999</v>
+      </c>
+      <c r="H41">
+        <v>0.25433919999999999</v>
+      </c>
+      <c r="I41">
+        <v>6.2264E-2</v>
+      </c>
+      <c r="J41">
+        <v>-0.40914030000000001</v>
+      </c>
+      <c r="K41">
+        <v>-0.209513</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42">
+        <v>48</v>
+      </c>
+      <c r="C42">
+        <v>-0.64436782999999997</v>
+      </c>
+      <c r="D42">
+        <v>0.64777570299999998</v>
+      </c>
+      <c r="E42">
+        <v>-0.28135599999999999</v>
+      </c>
+      <c r="F42">
+        <v>-0.55861830000000001</v>
+      </c>
+      <c r="G42">
+        <v>-0.35293160000000001</v>
+      </c>
+      <c r="H42">
+        <v>0.84010530000000005</v>
+      </c>
+      <c r="I42">
+        <v>0.80856609999999995</v>
+      </c>
+      <c r="J42">
+        <v>-0.18548980000000001</v>
+      </c>
+      <c r="K42">
+        <v>-0.1113373</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="M45" s="60"/>
+      <c r="N45" s="60"/>
+      <c r="O45" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="P45" s="63"/>
+      <c r="Q45" s="63"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L46" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="M46" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="N46" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="O46" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="P46" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q46" s="64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47">
+        <v>221</v>
+      </c>
+      <c r="C47">
+        <v>-0.36435181999999999</v>
+      </c>
+      <c r="D47">
+        <v>0.29172956</v>
+      </c>
+      <c r="E47">
+        <v>-0.39830009999999999</v>
+      </c>
+      <c r="F47">
+        <v>-0.52896980000000005</v>
+      </c>
+      <c r="G47">
+        <v>-0.51165769999999999</v>
+      </c>
+      <c r="H47">
+        <v>0.47403530999999999</v>
+      </c>
+      <c r="I47">
+        <v>0.53216317000000002</v>
+      </c>
+      <c r="J47">
+        <v>-0.36940600000000001</v>
+      </c>
+      <c r="K47">
+        <v>-0.29667490000000002</v>
+      </c>
+      <c r="L47" s="62">
+        <f>MAX(ABS(C47),ABS(F47),ABS(G47))</f>
+        <v>0.52896980000000005</v>
+      </c>
+      <c r="M47" s="62">
+        <f>MAX(ABS(D47),ABS(H47),ABS(I47))</f>
+        <v>0.53216317000000002</v>
+      </c>
+      <c r="N47" s="62">
+        <f>MAX(ABS(E47),ABS(J47),ABS(K47))</f>
+        <v>0.39830009999999999</v>
+      </c>
+      <c r="O47" s="64" t="str">
+        <f>_xlfn.IFNA(INDEX($C$46:$K$46,1,MATCH(L47,$C47:$K47,0)),INDEX($C$46:$K$46,1,MATCH(-L47,$C47:$K47,0)))</f>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P47" s="64" t="str">
+        <f t="shared" ref="P47:Q47" si="0">_xlfn.IFNA(INDEX($C$46:$K$46,1,MATCH(M47,$C47:$K47,0)),INDEX($C$46:$K$46,1,MATCH(-M47,$C47:$K47,0)))</f>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q47" s="64" t="str">
+        <f t="shared" si="0"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48">
+        <v>219</v>
+      </c>
+      <c r="C48">
+        <v>5.609803E-2</v>
+      </c>
+      <c r="D48">
+        <v>-0.13325564000000001</v>
+      </c>
+      <c r="E48">
+        <v>-0.37649739999999998</v>
+      </c>
+      <c r="F48">
+        <v>-0.19580439999999999</v>
+      </c>
+      <c r="G48">
+        <v>-0.36313079999999998</v>
+      </c>
+      <c r="H48">
+        <v>5.402067E-2</v>
+      </c>
+      <c r="I48">
+        <v>0.23631163999999999</v>
+      </c>
+      <c r="J48">
+        <v>-0.49020229999999998</v>
+      </c>
+      <c r="K48">
+        <v>-0.49377890000000002</v>
+      </c>
+      <c r="L48" s="62">
+        <f t="shared" ref="L48:L64" si="1">MAX(ABS(C48),ABS(F48),ABS(G48))</f>
+        <v>0.36313079999999998</v>
+      </c>
+      <c r="M48" s="62">
+        <f t="shared" ref="M48:M64" si="2">MAX(ABS(D48),ABS(H48),ABS(I48))</f>
+        <v>0.23631163999999999</v>
+      </c>
+      <c r="N48" s="62">
+        <f t="shared" ref="N48:N64" si="3">MAX(ABS(E48),ABS(J48),ABS(K48))</f>
+        <v>0.49377890000000002</v>
+      </c>
+      <c r="O48" s="64" t="str">
+        <f t="shared" ref="O48:O64" si="4">_xlfn.IFNA(INDEX($C$46:$K$46,1,MATCH(L48,$C48:$K48,0)),INDEX($C$46:$K$46,1,MATCH(-L48,$C48:$K48,0)))</f>
+        <v>rr_lag2</v>
+      </c>
+      <c r="P48" s="64" t="str">
+        <f t="shared" ref="P48:P64" si="5">_xlfn.IFNA(INDEX($C$46:$K$46,1,MATCH(M48,$C48:$K48,0)),INDEX($C$46:$K$46,1,MATCH(-M48,$C48:$K48,0)))</f>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q48" s="64" t="str">
+        <f t="shared" ref="Q48:Q64" si="6">_xlfn.IFNA(INDEX($C$46:$K$46,1,MATCH(N48,$C48:$K48,0)),INDEX($C$46:$K$46,1,MATCH(-N48,$C48:$K48,0)))</f>
+        <v>caudal_lag2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49">
+        <v>217</v>
+      </c>
+      <c r="C49">
+        <v>4.0933009999999999E-2</v>
+      </c>
+      <c r="D49">
+        <v>-5.2060389999999998E-2</v>
+      </c>
+      <c r="E49">
+        <v>-0.14769689999999999</v>
+      </c>
+      <c r="F49">
+        <v>-0.17437420000000001</v>
+      </c>
+      <c r="G49">
+        <v>-0.28289120000000001</v>
+      </c>
+      <c r="H49">
+        <v>9.0150969999999997E-2</v>
+      </c>
+      <c r="I49">
+        <v>0.20498458</v>
+      </c>
+      <c r="J49">
+        <v>-0.2807481</v>
+      </c>
+      <c r="K49">
+        <v>-0.29853580000000002</v>
+      </c>
+      <c r="L49" s="62">
+        <f t="shared" si="1"/>
+        <v>0.28289120000000001</v>
+      </c>
+      <c r="M49" s="62">
+        <f t="shared" si="2"/>
+        <v>0.20498458</v>
+      </c>
+      <c r="N49" s="62">
+        <f t="shared" si="3"/>
+        <v>0.29853580000000002</v>
+      </c>
+      <c r="O49" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag2</v>
+      </c>
+      <c r="P49" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q49" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50">
+        <v>211</v>
+      </c>
+      <c r="C50">
+        <v>-0.19987545000000001</v>
+      </c>
+      <c r="D50">
+        <v>0.25616371999999998</v>
+      </c>
+      <c r="E50">
+        <v>-0.22787470000000001</v>
+      </c>
+      <c r="F50">
+        <v>-0.26005810000000001</v>
+      </c>
+      <c r="G50">
+        <v>-0.2094297</v>
+      </c>
+      <c r="H50">
+        <v>0.28973631999999999</v>
+      </c>
+      <c r="I50">
+        <v>0.23133161999999999</v>
+      </c>
+      <c r="J50">
+        <v>-0.23886260000000001</v>
+      </c>
+      <c r="K50">
+        <v>-0.19403909999999999</v>
+      </c>
+      <c r="L50" s="62">
+        <f t="shared" si="1"/>
+        <v>0.26005810000000001</v>
+      </c>
+      <c r="M50" s="62">
+        <f t="shared" si="2"/>
+        <v>0.28973631999999999</v>
+      </c>
+      <c r="N50" s="62">
+        <f t="shared" si="3"/>
+        <v>0.23886260000000001</v>
+      </c>
+      <c r="O50" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P50" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q50" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51">
+        <v>207</v>
+      </c>
+      <c r="C51">
+        <v>-0.41422975000000001</v>
+      </c>
+      <c r="D51">
+        <v>0.55260595000000001</v>
+      </c>
+      <c r="E51">
+        <v>-0.29670449999999998</v>
+      </c>
+      <c r="F51">
+        <v>-0.56113469999999999</v>
+      </c>
+      <c r="G51">
+        <v>-0.43867669999999997</v>
+      </c>
+      <c r="H51">
+        <v>0.73726440999999998</v>
+      </c>
+      <c r="I51">
+        <v>0.71037371000000005</v>
+      </c>
+      <c r="J51">
+        <v>-0.29718339999999999</v>
+      </c>
+      <c r="K51">
+        <v>-0.10106229999999999</v>
+      </c>
+      <c r="L51" s="62">
+        <f t="shared" si="1"/>
+        <v>0.56113469999999999</v>
+      </c>
+      <c r="M51" s="62">
+        <f t="shared" si="2"/>
+        <v>0.73726440999999998</v>
+      </c>
+      <c r="N51" s="62">
+        <f t="shared" si="3"/>
+        <v>0.29718339999999999</v>
+      </c>
+      <c r="O51" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P51" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q51" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52">
+        <v>193</v>
+      </c>
+      <c r="C52">
+        <v>-0.52272753999999999</v>
+      </c>
+      <c r="D52">
+        <v>0.78680019999999995</v>
+      </c>
+      <c r="E52">
+        <v>-0.36561579999999999</v>
+      </c>
+      <c r="F52">
+        <v>-0.52134899999999995</v>
+      </c>
+      <c r="G52">
+        <v>-0.34999580000000002</v>
+      </c>
+      <c r="H52">
+        <v>0.83951507999999997</v>
+      </c>
+      <c r="I52">
+        <v>0.68520517999999997</v>
+      </c>
+      <c r="J52">
+        <v>-0.33384200000000003</v>
+      </c>
+      <c r="K52">
+        <v>-0.19977110000000001</v>
+      </c>
+      <c r="L52" s="62">
+        <f t="shared" si="1"/>
+        <v>0.52272753999999999</v>
+      </c>
+      <c r="M52" s="62">
+        <f t="shared" si="2"/>
+        <v>0.83951507999999997</v>
+      </c>
+      <c r="N52" s="62">
+        <f t="shared" si="3"/>
+        <v>0.36561579999999999</v>
+      </c>
+      <c r="O52" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr</v>
+      </c>
+      <c r="P52" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q52" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53">
+        <v>190</v>
+      </c>
+      <c r="C53">
+        <v>-6.3993869999999994E-2</v>
+      </c>
+      <c r="D53">
+        <v>7.4269760000000004E-2</v>
+      </c>
+      <c r="E53">
+        <v>-0.47170469999999998</v>
+      </c>
+      <c r="F53">
+        <v>-0.3020563</v>
+      </c>
+      <c r="G53">
+        <v>-0.48890909999999999</v>
+      </c>
+      <c r="H53">
+        <v>0.34341697999999998</v>
+      </c>
+      <c r="I53">
+        <v>0.54311708000000003</v>
+      </c>
+      <c r="J53">
+        <v>-0.60839960000000004</v>
+      </c>
+      <c r="K53">
+        <v>-0.61509579999999997</v>
+      </c>
+      <c r="L53" s="62">
+        <f t="shared" si="1"/>
+        <v>0.48890909999999999</v>
+      </c>
+      <c r="M53" s="62">
+        <f t="shared" si="2"/>
+        <v>0.54311708000000003</v>
+      </c>
+      <c r="N53" s="62">
+        <f t="shared" si="3"/>
+        <v>0.61509579999999997</v>
+      </c>
+      <c r="O53" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag2</v>
+      </c>
+      <c r="P53" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q53" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54">
+        <v>178</v>
+      </c>
+      <c r="C54">
+        <v>-0.16460926000000001</v>
+      </c>
+      <c r="D54">
+        <v>0.12048082</v>
+      </c>
+      <c r="E54">
+        <v>-0.35642970000000002</v>
+      </c>
+      <c r="F54">
+        <v>-0.53262509999999996</v>
+      </c>
+      <c r="G54">
+        <v>-0.56787860000000001</v>
+      </c>
+      <c r="H54">
+        <v>0.45060103000000001</v>
+      </c>
+      <c r="I54">
+        <v>0.65674513000000001</v>
+      </c>
+      <c r="J54">
+        <v>-0.39277610000000002</v>
+      </c>
+      <c r="K54">
+        <v>-0.30873850000000003</v>
+      </c>
+      <c r="L54" s="62">
+        <f t="shared" si="1"/>
+        <v>0.56787860000000001</v>
+      </c>
+      <c r="M54" s="62">
+        <f t="shared" si="2"/>
+        <v>0.65674513000000001</v>
+      </c>
+      <c r="N54" s="62">
+        <f t="shared" si="3"/>
+        <v>0.39277610000000002</v>
+      </c>
+      <c r="O54" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag2</v>
+      </c>
+      <c r="P54" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q54" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55">
+        <v>165</v>
+      </c>
+      <c r="C55">
+        <v>-0.33413345999999999</v>
+      </c>
+      <c r="D55">
+        <v>0.50191156000000003</v>
+      </c>
+      <c r="E55">
+        <v>-0.46423900000000001</v>
+      </c>
+      <c r="F55">
+        <v>-0.51945580000000002</v>
+      </c>
+      <c r="G55">
+        <v>-0.51134999999999997</v>
+      </c>
+      <c r="H55">
+        <v>0.74879222000000001</v>
+      </c>
+      <c r="I55">
+        <v>0.79710197999999999</v>
+      </c>
+      <c r="J55">
+        <v>-0.5035771</v>
+      </c>
+      <c r="K55">
+        <v>-0.43384430000000002</v>
+      </c>
+      <c r="L55" s="62">
+        <f t="shared" si="1"/>
+        <v>0.51945580000000002</v>
+      </c>
+      <c r="M55" s="62">
+        <f t="shared" si="2"/>
+        <v>0.79710197999999999</v>
+      </c>
+      <c r="N55" s="62">
+        <f t="shared" si="3"/>
+        <v>0.5035771</v>
+      </c>
+      <c r="O55" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P55" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q55" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56">
+        <v>136</v>
+      </c>
+      <c r="C56">
+        <v>-0.38434974999999999</v>
+      </c>
+      <c r="D56">
+        <v>0.29518195000000003</v>
+      </c>
+      <c r="E56">
+        <v>-0.40052589999999999</v>
+      </c>
+      <c r="F56">
+        <v>-0.57233659999999997</v>
+      </c>
+      <c r="G56">
+        <v>-0.50029900000000005</v>
+      </c>
+      <c r="H56">
+        <v>0.59020983999999999</v>
+      </c>
+      <c r="I56">
+        <v>0.71157645999999997</v>
+      </c>
+      <c r="J56">
+        <v>-0.3244359</v>
+      </c>
+      <c r="K56">
+        <v>-0.28790270000000001</v>
+      </c>
+      <c r="L56" s="62">
+        <f t="shared" si="1"/>
+        <v>0.57233659999999997</v>
+      </c>
+      <c r="M56" s="62">
+        <f t="shared" si="2"/>
+        <v>0.71157645999999997</v>
+      </c>
+      <c r="N56" s="62">
+        <f t="shared" si="3"/>
+        <v>0.40052589999999999</v>
+      </c>
+      <c r="O56" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P56" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q56" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57">
+        <v>102</v>
+      </c>
+      <c r="C57">
+        <v>-0.17797846</v>
+      </c>
+      <c r="D57">
+        <v>0.26211591000000001</v>
+      </c>
+      <c r="E57">
+        <v>-0.33019579999999998</v>
+      </c>
+      <c r="F57">
+        <v>-0.3595333</v>
+      </c>
+      <c r="G57">
+        <v>-0.32322319999999999</v>
+      </c>
+      <c r="H57">
+        <v>0.33164979999999999</v>
+      </c>
+      <c r="I57">
+        <v>0.30671292999999999</v>
+      </c>
+      <c r="J57">
+        <v>-0.33314339999999998</v>
+      </c>
+      <c r="K57">
+        <v>-0.33717799999999998</v>
+      </c>
+      <c r="L57" s="62">
+        <f t="shared" si="1"/>
+        <v>0.3595333</v>
+      </c>
+      <c r="M57" s="62">
+        <f t="shared" si="2"/>
+        <v>0.33164979999999999</v>
+      </c>
+      <c r="N57" s="62">
+        <f t="shared" si="3"/>
+        <v>0.33717799999999998</v>
+      </c>
+      <c r="O57" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P57" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q57" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58">
+        <v>93</v>
+      </c>
+      <c r="C58">
+        <v>-0.23580766</v>
+      </c>
+      <c r="D58">
+        <v>0.32957871999999999</v>
+      </c>
+      <c r="E58">
+        <v>-0.35849379999999997</v>
+      </c>
+      <c r="F58">
+        <v>-0.39558149999999997</v>
+      </c>
+      <c r="G58">
+        <v>-0.35528530000000003</v>
+      </c>
+      <c r="H58">
+        <v>0.42080192</v>
+      </c>
+      <c r="I58">
+        <v>0.37690707000000001</v>
+      </c>
+      <c r="J58">
+        <v>-0.4495207</v>
+      </c>
+      <c r="K58">
+        <v>-0.26655990000000002</v>
+      </c>
+      <c r="L58" s="62">
+        <f t="shared" si="1"/>
+        <v>0.39558149999999997</v>
+      </c>
+      <c r="M58" s="62">
+        <f t="shared" si="2"/>
+        <v>0.42080192</v>
+      </c>
+      <c r="N58" s="62">
+        <f t="shared" si="3"/>
+        <v>0.4495207</v>
+      </c>
+      <c r="O58" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P58" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q58" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59">
+        <v>80</v>
+      </c>
+      <c r="C59">
+        <v>-0.15575865999999999</v>
+      </c>
+      <c r="D59">
+        <v>0.22685343999999999</v>
+      </c>
+      <c r="E59">
+        <v>-0.55763359999999995</v>
+      </c>
+      <c r="F59">
+        <v>-0.53431810000000002</v>
+      </c>
+      <c r="G59">
+        <v>-0.51823019999999997</v>
+      </c>
+      <c r="H59">
+        <v>0.38998465999999998</v>
+      </c>
+      <c r="I59">
+        <v>0.49313952999999999</v>
+      </c>
+      <c r="J59">
+        <v>-0.66520040000000003</v>
+      </c>
+      <c r="K59">
+        <v>-0.48176809999999998</v>
+      </c>
+      <c r="L59" s="62">
+        <f t="shared" si="1"/>
+        <v>0.53431810000000002</v>
+      </c>
+      <c r="M59" s="62">
+        <f t="shared" si="2"/>
+        <v>0.49313952999999999</v>
+      </c>
+      <c r="N59" s="62">
+        <f t="shared" si="3"/>
+        <v>0.66520040000000003</v>
+      </c>
+      <c r="O59" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P59" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q59" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60">
+        <v>79</v>
+      </c>
+      <c r="C60">
+        <v>-5.3824070000000002E-2</v>
+      </c>
+      <c r="D60">
+        <v>4.6321540000000001E-2</v>
+      </c>
+      <c r="E60">
+        <v>-0.51541599999999999</v>
+      </c>
+      <c r="F60">
+        <v>-0.49728050000000001</v>
+      </c>
+      <c r="G60">
+        <v>-0.56126290000000001</v>
+      </c>
+      <c r="H60">
+        <v>0.26659422999999999</v>
+      </c>
+      <c r="I60">
+        <v>0.38833285000000001</v>
+      </c>
+      <c r="J60">
+        <v>-0.63675749999999998</v>
+      </c>
+      <c r="K60">
+        <v>-0.40969729999999999</v>
+      </c>
+      <c r="L60" s="62">
+        <f t="shared" si="1"/>
+        <v>0.56126290000000001</v>
+      </c>
+      <c r="M60" s="62">
+        <f t="shared" si="2"/>
+        <v>0.38833285000000001</v>
+      </c>
+      <c r="N60" s="62">
+        <f t="shared" si="3"/>
+        <v>0.63675749999999998</v>
+      </c>
+      <c r="O60" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag2</v>
+      </c>
+      <c r="P60" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q60" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal_lag1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61">
+        <v>75</v>
+      </c>
+      <c r="C61">
+        <v>-0.25586168999999997</v>
+      </c>
+      <c r="D61">
+        <v>9.9384509999999995E-2</v>
+      </c>
+      <c r="E61">
+        <v>-0.51176980000000005</v>
+      </c>
+      <c r="F61">
+        <v>-0.2881591</v>
+      </c>
+      <c r="G61">
+        <v>-0.3684597</v>
+      </c>
+      <c r="H61">
+        <v>0.39431104</v>
+      </c>
+      <c r="I61">
+        <v>0.57917905999999997</v>
+      </c>
+      <c r="J61">
+        <v>-0.38255070000000002</v>
+      </c>
+      <c r="K61">
+        <v>-0.32899990000000001</v>
+      </c>
+      <c r="L61" s="62">
+        <f t="shared" si="1"/>
+        <v>0.3684597</v>
+      </c>
+      <c r="M61" s="62">
+        <f t="shared" si="2"/>
+        <v>0.57917905999999997</v>
+      </c>
+      <c r="N61" s="62">
+        <f t="shared" si="3"/>
+        <v>0.51176980000000005</v>
+      </c>
+      <c r="O61" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag2</v>
+      </c>
+      <c r="P61" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag2</v>
+      </c>
+      <c r="Q61" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62">
+        <v>74</v>
+      </c>
+      <c r="C62">
+        <v>-0.48196455999999999</v>
+      </c>
+      <c r="D62">
+        <v>0.73111265999999997</v>
+      </c>
+      <c r="E62">
+        <v>-0.38576490000000002</v>
+      </c>
+      <c r="F62">
+        <v>-0.48635129999999999</v>
+      </c>
+      <c r="G62">
+        <v>-0.32839420000000002</v>
+      </c>
+      <c r="H62">
+        <v>0.82478116999999995</v>
+      </c>
+      <c r="I62">
+        <v>0.70689833000000002</v>
+      </c>
+      <c r="J62">
+        <v>-0.37657239999999997</v>
+      </c>
+      <c r="K62">
+        <v>-0.2948595</v>
+      </c>
+      <c r="L62" s="62">
+        <f t="shared" si="1"/>
+        <v>0.48635129999999999</v>
+      </c>
+      <c r="M62" s="62">
+        <f t="shared" si="2"/>
+        <v>0.82478116999999995</v>
+      </c>
+      <c r="N62" s="62">
+        <f t="shared" si="3"/>
+        <v>0.38576490000000002</v>
+      </c>
+      <c r="O62" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr_lag1</v>
+      </c>
+      <c r="P62" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q62" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63">
+        <v>57</v>
+      </c>
+      <c r="C63">
+        <v>-0.67347791000000001</v>
+      </c>
+      <c r="D63">
+        <v>0.43382029999999999</v>
+      </c>
+      <c r="E63">
+        <v>-0.79059690000000005</v>
+      </c>
+      <c r="F63">
+        <v>-0.65063689999999996</v>
+      </c>
+      <c r="G63">
+        <v>-0.36047129999999999</v>
+      </c>
+      <c r="H63">
+        <v>0.32142976000000001</v>
+      </c>
+      <c r="I63">
+        <v>8.2628110000000005E-2</v>
+      </c>
+      <c r="J63">
+        <v>-0.5521279</v>
+      </c>
+      <c r="K63">
+        <v>-0.33569139999999997</v>
+      </c>
+      <c r="L63" s="62">
+        <f t="shared" si="1"/>
+        <v>0.67347791000000001</v>
+      </c>
+      <c r="M63" s="62">
+        <f t="shared" si="2"/>
+        <v>0.43382029999999999</v>
+      </c>
+      <c r="N63" s="62">
+        <f t="shared" si="3"/>
+        <v>0.79059690000000005</v>
+      </c>
+      <c r="O63" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr</v>
+      </c>
+      <c r="P63" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto</v>
+      </c>
+      <c r="Q63" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64">
+        <v>48</v>
+      </c>
+      <c r="C64">
+        <v>-0.62369774</v>
+      </c>
+      <c r="D64">
+        <v>0.78738111</v>
+      </c>
+      <c r="E64">
+        <v>-0.2802171</v>
+      </c>
+      <c r="F64">
+        <v>-0.52550719999999995</v>
+      </c>
+      <c r="G64">
+        <v>-0.24776519999999999</v>
+      </c>
+      <c r="H64">
+        <v>0.86709314999999998</v>
+      </c>
+      <c r="I64">
+        <v>0.71664963000000004</v>
+      </c>
+      <c r="J64">
+        <v>-0.234735</v>
+      </c>
+      <c r="K64">
+        <v>-0.1227898</v>
+      </c>
+      <c r="L64" s="62">
+        <f t="shared" si="1"/>
+        <v>0.62369774</v>
+      </c>
+      <c r="M64" s="62">
+        <f t="shared" si="2"/>
+        <v>0.86709314999999998</v>
+      </c>
+      <c r="N64" s="62">
+        <f t="shared" si="3"/>
+        <v>0.2802171</v>
+      </c>
+      <c r="O64" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>rr</v>
+      </c>
+      <c r="P64" s="64" t="str">
+        <f t="shared" si="5"/>
+        <v>eto_lag1</v>
+      </c>
+      <c r="Q64" s="64" t="str">
+        <f t="shared" si="6"/>
+        <v>caudal</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+      <c r="L67" s="43"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="O67" s="22"/>
+      <c r="P67" s="27"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H68" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J68" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="K68" t="s">
+        <v>28</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N68" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="O68" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="P68" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K69">
+        <v>0.46636549999999999</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ref="L69:L86" si="7">COUNTIF(B69:J69,"X")</f>
+        <v>8</v>
+      </c>
+      <c r="N69">
+        <v>0.48632120000000001</v>
+      </c>
+      <c r="O69">
+        <v>0.46441080000000001</v>
+      </c>
+      <c r="P69" s="5">
+        <f>(K69-O69)/K69</f>
+        <v>4.1913477733665459E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K70">
+        <v>0.36250260000000001</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="N70">
+        <v>0.38446710000000001</v>
+      </c>
+      <c r="O70">
+        <v>0.35796090000000003</v>
+      </c>
+      <c r="P70" s="5">
+        <f t="shared" ref="P70:P86" si="8">(K70-O70)/K70</f>
+        <v>1.2528737724915577E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71">
+        <v>0.1334245</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="N71">
+        <v>0.16082080000000001</v>
+      </c>
+      <c r="O71">
+        <v>0.1243348</v>
+      </c>
+      <c r="P71" s="5">
+        <f t="shared" si="8"/>
+        <v>6.8126168732129455E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72">
+        <v>0.1025937</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="N72">
+        <v>0.12217500000000001</v>
+      </c>
+      <c r="O72">
+        <v>8.2869399999999996E-2</v>
+      </c>
+      <c r="P72" s="5">
+        <f t="shared" si="8"/>
+        <v>0.19225644459650057</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73">
+        <v>0.60131109999999999</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="N73">
+        <v>0.61718419999999996</v>
+      </c>
+      <c r="O73">
+        <v>0.59969519999999998</v>
+      </c>
+      <c r="P73" s="5">
+        <f t="shared" si="8"/>
+        <v>2.6872944803447061E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74">
+        <v>0.75203169999999997</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="N74">
+        <v>0.76254909999999998</v>
+      </c>
+      <c r="O74">
+        <v>0.75087110000000001</v>
+      </c>
+      <c r="P74" s="5">
+        <f t="shared" si="8"/>
+        <v>1.5432860077573274E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75">
+        <v>0.60331820000000003</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="N75">
+        <v>0.61981339999999996</v>
+      </c>
+      <c r="O75">
+        <v>0.60080409999999995</v>
+      </c>
+      <c r="P75" s="5">
+        <f t="shared" si="8"/>
+        <v>4.1671210979547348E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76">
+        <v>0.59891159999999999</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="N76">
+        <v>0.61717659999999996</v>
+      </c>
+      <c r="O76">
+        <v>0.59666819999999998</v>
+      </c>
+      <c r="P76" s="5">
+        <f t="shared" si="8"/>
+        <v>3.7457948718976333E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K77">
+        <v>0.70071729999999999</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="N77">
+        <v>0.71469819999999995</v>
+      </c>
+      <c r="O77">
+        <v>0.69813230000000004</v>
+      </c>
+      <c r="P77" s="5">
+        <f t="shared" si="8"/>
+        <v>3.6890768930636485E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K78">
+        <v>0.63677879999999998</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="N78">
+        <v>0.65507230000000005</v>
+      </c>
+      <c r="O78">
+        <v>0.63043470000000001</v>
+      </c>
+      <c r="P78" s="5">
+        <f t="shared" si="8"/>
+        <v>9.9628002691043802E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K79">
+        <v>0.20566110000000001</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N79">
+        <v>0.2353585</v>
+      </c>
+      <c r="O79">
+        <v>0.16055659999999999</v>
+      </c>
+      <c r="P79" s="5">
+        <f t="shared" si="8"/>
+        <v>0.21931468809609603</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="K80">
+        <v>0.26224969999999997</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="N80">
+        <v>0.29840640000000002</v>
+      </c>
+      <c r="O80">
+        <v>0.22233</v>
+      </c>
+      <c r="P80" s="5">
+        <f t="shared" si="8"/>
+        <v>0.15222019319755173</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81">
+        <v>0.5050211</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="N81">
+        <v>0.5552994</v>
+      </c>
+      <c r="O81">
+        <v>0.4981236</v>
+      </c>
+      <c r="P81" s="5">
+        <f t="shared" si="8"/>
+        <v>1.3657845187062484E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>50</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J82" s="3"/>
+      <c r="K82">
+        <v>0.55525820000000004</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="N82">
+        <v>0.58434549999999996</v>
+      </c>
+      <c r="O82">
+        <v>0.53012970000000004</v>
+      </c>
+      <c r="P82" s="5">
+        <f t="shared" si="8"/>
+        <v>4.5255522565898168E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J83" s="3"/>
+      <c r="K83">
+        <v>0.48944029999999999</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="N83">
+        <v>0.52805279999999999</v>
+      </c>
+      <c r="O83">
+        <v>0.46270620000000001</v>
+      </c>
+      <c r="P83" s="5">
+        <f t="shared" si="8"/>
+        <v>5.4621779203714901E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>46</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K84">
+        <v>0.73614829999999998</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="N84">
+        <v>0.76608790000000004</v>
+      </c>
+      <c r="O84">
+        <v>0.73319400000000001</v>
+      </c>
+      <c r="P84" s="5">
+        <f t="shared" si="8"/>
+        <v>4.0131859300632294E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K85">
+        <v>0.73376359999999996</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="N85">
+        <v>0.76699320000000004</v>
+      </c>
+      <c r="O85">
+        <v>0.72237479999999998</v>
+      </c>
+      <c r="P85" s="5">
+        <f t="shared" si="8"/>
+        <v>1.5521075180071588E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>53</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K86">
+        <v>0.83560100000000004</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="N86">
+        <v>0.86551370000000005</v>
+      </c>
+      <c r="O86">
+        <v>0.83366169999999995</v>
+      </c>
+      <c r="P86" s="5">
+        <f t="shared" si="8"/>
+        <v>2.3208445178980017E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="31"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" s="44"/>
+      <c r="E89" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F89" s="45"/>
+      <c r="G89" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="H89" s="46"/>
+      <c r="I89" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="J89" s="51"/>
+      <c r="K89" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="L89" s="48"/>
+      <c r="M89" s="58" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E90" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F90" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H90" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K90" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L90" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="M90" s="58"/>
+      <c r="N90" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="O90" t="s">
+        <v>122</v>
+      </c>
+      <c r="P90" s="2"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91">
+        <v>221</v>
+      </c>
+      <c r="C91">
+        <f>N69</f>
+        <v>0.48632120000000001</v>
+      </c>
+      <c r="D91">
+        <f>O69</f>
+        <v>0.46441080000000001</v>
+      </c>
+      <c r="E91">
+        <v>0.42868440000000002</v>
+      </c>
+      <c r="F91">
+        <v>0.41266617999999999</v>
+      </c>
+      <c r="G91">
+        <v>0.33269620999999999</v>
+      </c>
+      <c r="H91">
+        <v>0.32347081</v>
+      </c>
+      <c r="I91">
+        <v>0.34112587</v>
+      </c>
+      <c r="J91">
+        <v>0.33201701</v>
+      </c>
+      <c r="K91">
+        <v>0.39900400000000003</v>
+      </c>
+      <c r="L91">
+        <v>0.39069533000000001</v>
+      </c>
+      <c r="M91">
+        <f>MAX(D91,F91,H91,J91,L91)</f>
+        <v>0.46441080000000001</v>
+      </c>
+      <c r="N91">
+        <f>LARGE((D91,F91,H91,J91,L91),2)</f>
+        <v>0.41266617999999999</v>
+      </c>
+      <c r="O91" s="40">
+        <f>(M91-N91)/M91</f>
+        <v>0.1114199325252557</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92">
+        <v>219</v>
+      </c>
+      <c r="C92">
+        <f t="shared" ref="C92:D92" si="9">N70</f>
+        <v>0.38446710000000001</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="9"/>
+        <v>0.35796090000000003</v>
+      </c>
+      <c r="E92">
+        <v>0.37153829999999999</v>
+      </c>
+      <c r="F92">
+        <v>0.35375162999999998</v>
+      </c>
+      <c r="G92">
+        <v>0.25565580999999998</v>
+      </c>
+      <c r="H92">
+        <v>0.24526961</v>
+      </c>
+      <c r="I92">
+        <v>0.26458098000000002</v>
+      </c>
+      <c r="J92">
+        <v>0.25431932000000002</v>
+      </c>
+      <c r="K92">
+        <v>0.26804149999999999</v>
+      </c>
+      <c r="L92">
+        <v>0.25782817000000002</v>
+      </c>
+      <c r="M92">
+        <f t="shared" ref="M92:M108" si="10">MAX(D92,F92,H92,J92,L92)</f>
+        <v>0.35796090000000003</v>
+      </c>
+      <c r="N92">
+        <f>LARGE((D92,F92,H92,J92,L92),2)</f>
+        <v>0.35375162999999998</v>
+      </c>
+      <c r="O92" s="40">
+        <f t="shared" ref="O92:O108" si="11">(M92-N92)/M92</f>
+        <v>1.1759021725557295E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93">
+        <v>217</v>
+      </c>
+      <c r="C93">
+        <f t="shared" ref="C93:D93" si="12">N71</f>
+        <v>0.16082080000000001</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="12"/>
+        <v>0.1243348</v>
+      </c>
+      <c r="E93">
+        <v>0.151592</v>
+      </c>
+      <c r="F93">
+        <v>0.12735175000000001</v>
+      </c>
+      <c r="G93">
+        <v>8.2844329999999994E-2</v>
+      </c>
+      <c r="H93">
+        <v>6.9926639999999998E-2</v>
+      </c>
+      <c r="I93">
+        <v>0.11627782</v>
+      </c>
+      <c r="J93">
+        <v>0.10383103</v>
+      </c>
+      <c r="K93">
+        <v>0.1146687</v>
+      </c>
+      <c r="L93">
+        <v>0.10219928</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="10"/>
+        <v>0.12735175000000001</v>
+      </c>
+      <c r="N93">
+        <f>LARGE((D93,F93,H93,J93,L93),2)</f>
+        <v>0.1243348</v>
+      </c>
+      <c r="O93" s="40">
+        <f t="shared" si="11"/>
+        <v>2.3689898254244782E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94">
+        <v>211</v>
+      </c>
+      <c r="C94">
+        <f t="shared" ref="C94:D94" si="13">N72</f>
+        <v>0.12217500000000001</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="13"/>
+        <v>8.2869399999999996E-2</v>
+      </c>
+      <c r="E94">
+        <v>0.1204264</v>
+      </c>
+      <c r="F94">
+        <v>9.4556580000000001E-2</v>
+      </c>
+      <c r="G94">
+        <v>0.10967414</v>
+      </c>
+      <c r="H94">
+        <v>9.677086E-2</v>
+      </c>
+      <c r="I94">
+        <v>7.1952669999999996E-2</v>
+      </c>
+      <c r="J94">
+        <v>5.8502709999999999E-2</v>
+      </c>
+      <c r="K94">
+        <v>0.10220360000000001</v>
+      </c>
+      <c r="L94">
+        <v>8.9192019999999997E-2</v>
+      </c>
+      <c r="M94">
+        <f t="shared" si="10"/>
+        <v>9.677086E-2</v>
+      </c>
+      <c r="N94">
+        <f>LARGE((D94,F94,H94,J94,L94),2)</f>
+        <v>9.4556580000000001E-2</v>
+      </c>
+      <c r="O94" s="40">
+        <f t="shared" si="11"/>
+        <v>2.2881681530989795E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95">
+        <v>207</v>
+      </c>
+      <c r="C95">
+        <f t="shared" ref="C95:D95" si="14">N73</f>
+        <v>0.61718419999999996</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="14"/>
+        <v>0.59969519999999998</v>
+      </c>
+      <c r="E95">
+        <v>0.59521329999999995</v>
+      </c>
+      <c r="F95">
+        <v>0.58306968999999997</v>
+      </c>
+      <c r="G95">
+        <v>0.56159143</v>
+      </c>
+      <c r="H95">
+        <v>0.55511248999999996</v>
+      </c>
+      <c r="I95">
+        <v>0.51957317000000003</v>
+      </c>
+      <c r="J95">
+        <v>0.51247326999999998</v>
+      </c>
+      <c r="K95">
+        <v>0.56815760000000004</v>
+      </c>
+      <c r="L95">
+        <v>0.56177569000000005</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="10"/>
+        <v>0.59969519999999998</v>
+      </c>
+      <c r="N95">
+        <f>LARGE((D95,F95,H95,J95,L95),2)</f>
+        <v>0.58306968999999997</v>
+      </c>
+      <c r="O95" s="40">
+        <f t="shared" si="11"/>
+        <v>2.7723266752843794E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96">
+        <v>193</v>
+      </c>
+      <c r="C96">
+        <f t="shared" ref="C96:D96" si="15">N74</f>
+        <v>0.76254909999999998</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="15"/>
+        <v>0.75087110000000001</v>
+      </c>
+      <c r="E96">
+        <v>0.72381839999999997</v>
+      </c>
+      <c r="F96">
+        <v>0.71490936000000005</v>
+      </c>
+      <c r="G96">
+        <v>0.70571985000000004</v>
+      </c>
+      <c r="H96">
+        <v>0.70104873000000001</v>
+      </c>
+      <c r="I96">
+        <v>0.47619928</v>
+      </c>
+      <c r="J96">
+        <v>0.46788498000000001</v>
+      </c>
+      <c r="K96">
+        <v>0.51590639999999999</v>
+      </c>
+      <c r="L96">
+        <v>0.50822235999999998</v>
+      </c>
+      <c r="M96">
+        <f t="shared" si="10"/>
+        <v>0.75087110000000001</v>
+      </c>
+      <c r="N96">
+        <f>LARGE((D96,F96,H96,J96,L96),2)</f>
+        <v>0.71490936000000005</v>
+      </c>
+      <c r="O96" s="40">
+        <f t="shared" si="11"/>
+        <v>4.7893360125326391E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97">
+        <v>190</v>
+      </c>
+      <c r="C97">
+        <f t="shared" ref="C97:D97" si="16">N75</f>
+        <v>0.61981339999999996</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="16"/>
+        <v>0.60080409999999995</v>
+      </c>
+      <c r="E97">
+        <v>0.61245490000000002</v>
+      </c>
+      <c r="F97">
+        <v>0.59974850000000002</v>
+      </c>
+      <c r="G97">
+        <v>0.39891268000000002</v>
+      </c>
+      <c r="H97">
+        <v>0.38921771999999999</v>
+      </c>
+      <c r="I97">
+        <v>0.52564348000000005</v>
+      </c>
+      <c r="J97">
+        <v>0.51799256999999999</v>
+      </c>
+      <c r="K97">
+        <v>0.53271469999999999</v>
+      </c>
+      <c r="L97">
+        <v>0.52517784000000001</v>
+      </c>
+      <c r="M97">
+        <f t="shared" si="10"/>
+        <v>0.60080409999999995</v>
+      </c>
+      <c r="N97">
+        <f>LARGE((D97,F97,H97,J97,L97),2)</f>
+        <v>0.59974850000000002</v>
+      </c>
+      <c r="O97" s="40">
+        <f t="shared" si="11"/>
+        <v>1.7569786890601021E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98">
+        <v>178</v>
+      </c>
+      <c r="C98">
+        <f t="shared" ref="C98:D98" si="17">N76</f>
+        <v>0.61717659999999996</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="17"/>
+        <v>0.59666819999999998</v>
+      </c>
+      <c r="E98">
+        <v>0.6087342</v>
+      </c>
+      <c r="F98">
+        <v>0.59500558999999997</v>
+      </c>
+      <c r="G98">
+        <v>0.33779864999999998</v>
+      </c>
+      <c r="H98">
+        <v>0.32638138999999999</v>
+      </c>
+      <c r="I98">
+        <v>0.47851841000000001</v>
+      </c>
+      <c r="J98">
+        <v>0.46952735000000001</v>
+      </c>
+      <c r="K98">
+        <v>0.50586359999999997</v>
+      </c>
+      <c r="L98">
+        <v>0.49734395999999997</v>
+      </c>
+      <c r="M98">
+        <f t="shared" si="10"/>
+        <v>0.59666819999999998</v>
+      </c>
+      <c r="N98">
+        <f>LARGE((D98,F98,H98,J98,L98),2)</f>
+        <v>0.59500558999999997</v>
+      </c>
+      <c r="O98" s="40">
+        <f t="shared" si="11"/>
+        <v>2.7864900458915171E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99">
+        <v>165</v>
+      </c>
+      <c r="C99">
+        <f t="shared" ref="C99:D99" si="18">N77</f>
+        <v>0.71469819999999995</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="18"/>
+        <v>0.69813230000000004</v>
+      </c>
+      <c r="E99">
+        <v>0.70621979999999995</v>
+      </c>
+      <c r="F99">
+        <v>0.69506354999999997</v>
+      </c>
+      <c r="G99">
+        <v>0.61443353999999994</v>
+      </c>
+      <c r="H99">
+        <v>0.60724906999999995</v>
+      </c>
+      <c r="I99">
+        <v>0.66164445000000005</v>
+      </c>
+      <c r="J99">
+        <v>0.65533969000000003</v>
+      </c>
+      <c r="K99">
+        <v>0.68345929999999999</v>
+      </c>
+      <c r="L99">
+        <v>0.67756106999999999</v>
+      </c>
+      <c r="M99">
+        <f t="shared" si="10"/>
+        <v>0.69813230000000004</v>
+      </c>
+      <c r="N99">
+        <f>LARGE((D99,F99,H99,J99,L99),2)</f>
+        <v>0.69506354999999997</v>
+      </c>
+      <c r="O99" s="40">
+        <f t="shared" si="11"/>
+        <v>4.3956568117533941E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100">
+        <v>136</v>
+      </c>
+      <c r="C100">
+        <f t="shared" ref="C100:D100" si="19">N78</f>
+        <v>0.65507230000000005</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="19"/>
+        <v>0.63043470000000001</v>
+      </c>
+      <c r="E100">
+        <v>0.60880559999999995</v>
+      </c>
+      <c r="F100">
+        <v>0.59061054999999996</v>
+      </c>
+      <c r="G100">
+        <v>0.41884480000000002</v>
+      </c>
+      <c r="H100">
+        <v>0.40563673</v>
+      </c>
+      <c r="I100">
+        <v>0.51386726999999999</v>
+      </c>
+      <c r="J100">
+        <v>0.50281880000000001</v>
+      </c>
+      <c r="K100">
+        <v>0.57802350000000002</v>
+      </c>
+      <c r="L100">
+        <v>0.56843312999999995</v>
+      </c>
+      <c r="M100">
+        <f t="shared" si="10"/>
+        <v>0.63043470000000001</v>
+      </c>
+      <c r="N100">
+        <f>LARGE((D100,F100,H100,J100,L100),2)</f>
+        <v>0.59061054999999996</v>
+      </c>
+      <c r="O100" s="40">
+        <f t="shared" si="11"/>
+        <v>6.3169349656673493E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>38</v>
+      </c>
+      <c r="B101">
+        <v>102</v>
+      </c>
+      <c r="C101">
+        <f t="shared" ref="C101:D101" si="20">N79</f>
+        <v>0.2353585</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="20"/>
+        <v>0.16055659999999999</v>
+      </c>
+      <c r="E101">
+        <v>0.22927210000000001</v>
+      </c>
+      <c r="F101">
+        <v>0.18059458</v>
+      </c>
+      <c r="G101">
+        <v>0.18394779999999999</v>
+      </c>
+      <c r="H101">
+        <v>0.15896661000000001</v>
+      </c>
+      <c r="I101">
+        <v>0.16232949999999999</v>
+      </c>
+      <c r="J101">
+        <v>0.13668652000000001</v>
+      </c>
+      <c r="K101">
+        <v>0.2260992</v>
+      </c>
+      <c r="L101">
+        <v>0.20240837</v>
+      </c>
+      <c r="M101">
+        <f t="shared" si="10"/>
+        <v>0.20240837</v>
+      </c>
+      <c r="N101">
+        <f>LARGE((D101,F101,H101,J101,L101),2)</f>
+        <v>0.18059458</v>
+      </c>
+      <c r="O101" s="40">
+        <f t="shared" si="11"/>
+        <v>0.10777118554929324</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>41</v>
+      </c>
+      <c r="B102">
+        <v>93</v>
+      </c>
+      <c r="C102">
+        <f t="shared" ref="C102:D102" si="21">N80</f>
+        <v>0.29840640000000002</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="21"/>
+        <v>0.22233</v>
+      </c>
+      <c r="E102">
+        <v>0.29475709999999999</v>
+      </c>
+      <c r="F102">
+        <v>0.24555410999999999</v>
+      </c>
+      <c r="G102">
+        <v>0.2919062</v>
+      </c>
+      <c r="H102">
+        <v>0.26803787000000001</v>
+      </c>
+      <c r="I102">
+        <v>0.17589284999999999</v>
+      </c>
+      <c r="J102">
+        <v>0.14811394999999999</v>
+      </c>
+      <c r="K102">
+        <v>0.2383702</v>
+      </c>
+      <c r="L102">
+        <v>0.21269724000000001</v>
+      </c>
+      <c r="M102">
+        <f t="shared" si="10"/>
+        <v>0.26803787000000001</v>
+      </c>
+      <c r="N102">
+        <f>LARGE((D102,F102,H102,J102,L102),2)</f>
+        <v>0.24555410999999999</v>
+      </c>
+      <c r="O102" s="40">
+        <f t="shared" si="11"/>
+        <v>8.3882773728951129E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103">
+        <v>80</v>
+      </c>
+      <c r="C103">
+        <f t="shared" ref="C103:D103" si="22">N81</f>
+        <v>0.5552994</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="22"/>
+        <v>0.4981236</v>
+      </c>
+      <c r="E103">
+        <v>0.52621890000000004</v>
+      </c>
+      <c r="F103">
+        <v>0.48727797</v>
+      </c>
+      <c r="G103">
+        <v>0.47320899</v>
+      </c>
+      <c r="H103">
+        <v>0.4524146</v>
+      </c>
+      <c r="I103">
+        <v>0.35653908000000001</v>
+      </c>
+      <c r="J103">
+        <v>0.33113931000000002</v>
+      </c>
+      <c r="K103">
+        <v>0.46598850000000003</v>
+      </c>
+      <c r="L103">
+        <v>0.44490911</v>
+      </c>
+      <c r="M103">
+        <f t="shared" si="10"/>
+        <v>0.4981236</v>
+      </c>
+      <c r="N103">
+        <f>LARGE((D103,F103,H103,J103,L103),2)</f>
+        <v>0.48727797</v>
+      </c>
+      <c r="O103" s="40">
+        <f t="shared" si="11"/>
+        <v>2.1772969600316057E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>50</v>
+      </c>
+      <c r="B104">
+        <v>79</v>
+      </c>
+      <c r="C104">
+        <f t="shared" ref="C104:D104" si="23">N82</f>
+        <v>0.58434549999999996</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="23"/>
+        <v>0.53012970000000004</v>
+      </c>
+      <c r="E104">
+        <v>0.57430910000000002</v>
+      </c>
+      <c r="F104">
+        <v>0.53883481</v>
+      </c>
+      <c r="G104">
+        <v>0.50413388999999997</v>
+      </c>
+      <c r="H104">
+        <v>0.48429925000000001</v>
+      </c>
+      <c r="I104">
+        <v>0.35086834</v>
+      </c>
+      <c r="J104">
+        <v>0.32490308000000001</v>
+      </c>
+      <c r="K104">
+        <v>0.4005803</v>
+      </c>
+      <c r="L104">
+        <v>0.37660356</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="10"/>
+        <v>0.53883481</v>
+      </c>
+      <c r="N104">
+        <f>LARGE((D104,F104,H104,J104,L104),2)</f>
+        <v>0.53012970000000004</v>
+      </c>
+      <c r="O104" s="40">
+        <f t="shared" si="11"/>
+        <v>1.6155433610534481E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105">
+        <v>75</v>
+      </c>
+      <c r="C105">
+        <f t="shared" ref="C105:D105" si="24">N83</f>
+        <v>0.52805279999999999</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="24"/>
+        <v>0.46270620000000001</v>
+      </c>
+      <c r="E105">
+        <v>0.3861868</v>
+      </c>
+      <c r="F105">
+        <v>0.33202683999999999</v>
+      </c>
+      <c r="G105">
+        <v>0.22079744000000001</v>
+      </c>
+      <c r="H105">
+        <v>0.18787339</v>
+      </c>
+      <c r="I105">
+        <v>0.35257322000000002</v>
+      </c>
+      <c r="J105">
+        <v>0.32521716000000001</v>
+      </c>
+      <c r="K105">
+        <v>0.35216819999999999</v>
+      </c>
+      <c r="L105">
+        <v>0.32479503999999998</v>
+      </c>
+      <c r="M105">
+        <f t="shared" si="10"/>
+        <v>0.46270620000000001</v>
+      </c>
+      <c r="N105">
+        <f>LARGE((D105,F105,H105,J105,L105),2)</f>
+        <v>0.33202683999999999</v>
+      </c>
+      <c r="O105" s="40">
+        <f t="shared" si="11"/>
+        <v>0.2824240522387641</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>46</v>
+      </c>
+      <c r="B106">
+        <v>74</v>
+      </c>
+      <c r="C106">
+        <f t="shared" ref="C106:D106" si="25">N84</f>
+        <v>0.76608790000000004</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="25"/>
+        <v>0.73319400000000001</v>
+      </c>
+      <c r="E106">
+        <v>0.72064340000000005</v>
+      </c>
+      <c r="F106">
+        <v>0.69562639000000004</v>
+      </c>
+      <c r="G106">
+        <v>0.68424359999999995</v>
+      </c>
+      <c r="H106">
+        <v>0.67071117999999996</v>
+      </c>
+      <c r="I106">
+        <v>0.51675791000000004</v>
+      </c>
+      <c r="J106">
+        <v>0.49604754000000001</v>
+      </c>
+      <c r="K106">
+        <v>0.53033819999999998</v>
+      </c>
+      <c r="L106">
+        <v>0.51020980999999999</v>
+      </c>
+      <c r="M106">
+        <f t="shared" si="10"/>
+        <v>0.73319400000000001</v>
+      </c>
+      <c r="N106">
+        <f>LARGE((D106,F106,H106,J106,L106),2)</f>
+        <v>0.69562639000000004</v>
+      </c>
+      <c r="O106" s="40">
+        <f t="shared" si="11"/>
+        <v>5.1238294366838751E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>52</v>
+      </c>
+      <c r="B107">
+        <v>57</v>
+      </c>
+      <c r="C107">
+        <f t="shared" ref="C107:D107" si="26">N85</f>
+        <v>0.76699320000000004</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="26"/>
+        <v>0.72237479999999998</v>
+      </c>
+      <c r="E107">
+        <v>0.64183800000000002</v>
+      </c>
+      <c r="F107">
+        <v>0.59885854000000005</v>
+      </c>
+      <c r="G107">
+        <v>0.50363696999999996</v>
+      </c>
+      <c r="H107">
+        <v>0.47554095000000002</v>
+      </c>
+      <c r="I107">
+        <v>0.17766941999999999</v>
+      </c>
+      <c r="J107">
+        <v>0.13112240999999999</v>
+      </c>
+      <c r="K107">
+        <v>0.61411119999999997</v>
+      </c>
+      <c r="L107">
+        <v>0.59226842000000002</v>
+      </c>
+      <c r="M107">
+        <f t="shared" si="10"/>
+        <v>0.72237479999999998</v>
+      </c>
+      <c r="N107">
+        <f>LARGE((D107,F107,H107,J107,L107),2)</f>
+        <v>0.59885854000000005</v>
+      </c>
+      <c r="O107" s="40">
+        <f t="shared" si="11"/>
+        <v>0.17098639099813551</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>53</v>
+      </c>
+      <c r="B108">
+        <v>48</v>
+      </c>
+      <c r="C108">
+        <f t="shared" ref="C108:D108" si="27">N86</f>
+        <v>0.86551370000000005</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="27"/>
+        <v>0.83366169999999995</v>
+      </c>
+      <c r="E108">
+        <v>0.81750409999999996</v>
+      </c>
+      <c r="F108">
+        <v>0.79079741999999997</v>
+      </c>
+      <c r="G108">
+        <v>0.75396145999999997</v>
+      </c>
+      <c r="H108">
+        <v>0.73718609999999996</v>
+      </c>
+      <c r="I108">
+        <v>0.60362523999999995</v>
+      </c>
+      <c r="J108">
+        <v>0.57659969</v>
+      </c>
+      <c r="K108">
+        <v>0.53683630000000004</v>
+      </c>
+      <c r="L108">
+        <v>0.50525695999999998</v>
+      </c>
+      <c r="M108">
+        <f t="shared" si="10"/>
+        <v>0.83366169999999995</v>
+      </c>
+      <c r="N108">
+        <f>LARGE((D108,F108,H108,J108,L108),2)</f>
+        <v>0.79079741999999997</v>
+      </c>
+      <c r="O108" s="40">
+        <f t="shared" si="11"/>
+        <v>5.1416875694301395E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="M89:M90"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="O45:Q45"/>
+    <mergeCell ref="A67:L67"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C91:L108">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>$N91</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>$M91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N91:N108">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="7" tint="0.79998168889431442"/>
+        <color theme="5"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:K42">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="4Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47:K64">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="4Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:R146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -1903,19 +5902,19 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -2933,19 +6932,19 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="32" t="s">
+      <c r="A53" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
@@ -3963,25 +7962,25 @@
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A85" s="27" t="s">
+      <c r="A85" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="27"/>
-      <c r="J85" s="27"/>
-      <c r="K85" s="27"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="43"/>
+      <c r="D85" s="43"/>
+      <c r="E85" s="43"/>
+      <c r="F85" s="43"/>
+      <c r="G85" s="43"/>
+      <c r="H85" s="43"/>
+      <c r="I85" s="43"/>
+      <c r="J85" s="43"/>
+      <c r="K85" s="43"/>
       <c r="L85" s="4"/>
       <c r="N85" s="22" t="s">
         <v>94</v>
       </c>
       <c r="O85" s="22"/>
-      <c r="P85" s="33"/>
+      <c r="P85" s="27"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -4005,13 +8004,13 @@
       <c r="G86" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H86" s="35" t="s">
+      <c r="H86" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J86" s="35" t="s">
+      <c r="J86" s="29" t="s">
         <v>79</v>
       </c>
       <c r="K86" t="s">
@@ -4026,7 +8025,7 @@
       <c r="O86" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="P86" s="34" t="s">
+      <c r="P86" s="28" t="s">
         <v>82</v>
       </c>
     </row>
@@ -5126,7 +9125,7 @@
         <v>3.2475846785061848</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -5167,7 +9166,7 @@
         <v>3.4430937212957244E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>38</v>
       </c>
@@ -5204,37 +9203,37 @@
         <v>0.21931486424708138</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="37"/>
-      <c r="B117" s="39" t="s">
+    <row r="117" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="31"/>
+      <c r="B117" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="C117" s="39"/>
-      <c r="D117" s="40" t="s">
+      <c r="C117" s="44"/>
+      <c r="D117" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="E117" s="40"/>
-      <c r="F117" s="42" t="s">
+      <c r="E117" s="45"/>
+      <c r="F117" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="G117" s="42"/>
-      <c r="H117" s="44" t="s">
+      <c r="G117" s="46"/>
+      <c r="H117" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="I117" s="44"/>
-      <c r="J117" s="46" t="s">
+      <c r="I117" s="47"/>
+      <c r="J117" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="K117" s="46"/>
-      <c r="L117" s="38" t="s">
+      <c r="K117" s="48"/>
+      <c r="L117" s="42" t="s">
         <v>121</v>
       </c>
       <c r="O117" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A118" s="36" t="s">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A118" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B118" s="23" t="s">
@@ -5243,31 +9242,31 @@
       <c r="C118" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D118" s="41" t="s">
+      <c r="D118" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="E118" s="41" t="s">
+      <c r="E118" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="F118" s="43" t="s">
+      <c r="F118" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G118" s="43" t="s">
+      <c r="G118" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H118" s="45" t="s">
+      <c r="H118" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="I118" s="45" t="s">
+      <c r="I118" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="J118" s="47" t="s">
+      <c r="J118" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="K118" s="47" t="s">
+      <c r="K118" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="L118" s="38"/>
+      <c r="L118" s="42"/>
       <c r="M118" t="s">
         <v>119</v>
       </c>
@@ -5277,8 +9276,11 @@
       <c r="O118" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P118" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -5312,15 +9314,15 @@
       <c r="K119">
         <v>0.39069533169999998</v>
       </c>
-      <c r="L119" s="50">
+      <c r="L119" s="38">
         <f>MAX(C119,E119,G119,I119,K119)</f>
         <v>0.46441076799999997</v>
       </c>
-      <c r="M119" s="48">
+      <c r="M119" s="36">
         <f>LARGE((C119,E119,G119,I119,K119),2)</f>
         <v>0.41266618300000002</v>
       </c>
-      <c r="N119" s="52">
+      <c r="N119" s="40">
         <f>(L119-M119)/L119</f>
         <v>0.11141986483827601</v>
       </c>
@@ -5328,7 +9330,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -5362,15 +9364,15 @@
       <c r="K120">
         <v>0.2578281738</v>
       </c>
-      <c r="L120" s="50">
+      <c r="L120" s="38">
         <f t="shared" ref="L120:L146" si="2">MAX(C120,E120,G120,I120,K120)</f>
         <v>0.35796089199999997</v>
       </c>
-      <c r="M120" s="48">
+      <c r="M120" s="36">
         <f>LARGE((C120,E120,G120,I120,K120),2)</f>
         <v>0.35375162700000001</v>
       </c>
-      <c r="N120" s="52">
+      <c r="N120" s="40">
         <f t="shared" ref="N120:N146" si="3">(L120-M120)/L120</f>
         <v>1.1759008020350899E-2</v>
       </c>
@@ -5378,7 +9380,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>18</v>
       </c>
@@ -5412,21 +9414,24 @@
       <c r="K121">
         <v>6.6330281599999999E-2</v>
       </c>
-      <c r="L121" s="51">
+      <c r="L121" s="39">
         <f t="shared" si="2"/>
         <v>7.8309699999999996E-2</v>
       </c>
-      <c r="M121" s="49">
+      <c r="M121" s="37">
         <f>LARGE((C121,E121,G121,I121,K121),2)</f>
         <v>6.9627941999999998E-2</v>
       </c>
-      <c r="N121" s="53">
+      <c r="N121" s="41">
         <f t="shared" si="3"/>
         <v>0.11086440121721827</v>
       </c>
       <c r="O121" s="3"/>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R121" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -5460,23 +9465,26 @@
       <c r="K122">
         <v>0.1021992808</v>
       </c>
-      <c r="L122" s="50">
+      <c r="L122" s="38">
         <f t="shared" si="2"/>
         <v>0.12735175300000001</v>
       </c>
-      <c r="M122" s="48">
+      <c r="M122" s="36">
         <f>LARGE((C122,E122,G122,I122,K122),2)</f>
         <v>0.124334789</v>
       </c>
-      <c r="N122" s="52">
+      <c r="N122" s="40">
         <f t="shared" si="3"/>
         <v>2.3690007627928063E-2</v>
       </c>
       <c r="O122" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R122" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>19</v>
       </c>
@@ -5510,21 +9518,21 @@
       <c r="K123">
         <v>8.9192018200000001E-2</v>
       </c>
-      <c r="L123" s="51">
+      <c r="L123" s="39">
         <f t="shared" si="2"/>
         <v>9.6770861999999999E-2</v>
       </c>
-      <c r="M123" s="49">
+      <c r="M123" s="37">
         <f>LARGE((C123,E123,G123,I123,K123),2)</f>
         <v>9.4556583999999999E-2</v>
       </c>
-      <c r="N123" s="53">
+      <c r="N123" s="41">
         <f t="shared" si="3"/>
         <v>2.2881660390707277E-2</v>
       </c>
       <c r="O123" s="3"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>14</v>
       </c>
@@ -5558,15 +9566,15 @@
       <c r="K124">
         <v>0.56177568830000002</v>
       </c>
-      <c r="L124" s="50">
+      <c r="L124" s="38">
         <f t="shared" si="2"/>
         <v>0.59969515399999995</v>
       </c>
-      <c r="M124" s="48">
+      <c r="M124" s="36">
         <f>LARGE((C124,E124,G124,I124,K124),2)</f>
         <v>0.58306969399999997</v>
       </c>
-      <c r="N124" s="52">
+      <c r="N124" s="40">
         <f t="shared" si="3"/>
         <v>2.772318550368006E-2</v>
       </c>
@@ -5574,7 +9582,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>20</v>
       </c>
@@ -5608,21 +9616,21 @@
       <c r="K125">
         <v>1.30327494E-2</v>
       </c>
-      <c r="L125" s="51">
+      <c r="L125" s="39">
         <f t="shared" si="2"/>
         <v>1.7759153999999999E-2</v>
       </c>
-      <c r="M125" s="49">
+      <c r="M125" s="37">
         <f>LARGE((C125,E125,G125,I125,K125),2)</f>
         <v>1.30327494E-2</v>
       </c>
-      <c r="N125" s="53">
+      <c r="N125" s="41">
         <f t="shared" si="3"/>
         <v>0.26613906270535181</v>
       </c>
       <c r="O125" s="3"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>21</v>
       </c>
@@ -5656,15 +9664,15 @@
       <c r="K126">
         <v>0.44662750839999998</v>
       </c>
-      <c r="L126" s="50">
+      <c r="L126" s="38">
         <f t="shared" si="2"/>
         <v>0.48212026400000002</v>
       </c>
-      <c r="M126" s="48">
+      <c r="M126" s="36">
         <f>LARGE((C126,E126,G126,I126,K126),2)</f>
         <v>0.47616857800000001</v>
       </c>
-      <c r="N126" s="52">
+      <c r="N126" s="40">
         <f t="shared" si="3"/>
         <v>1.2344816105883514E-2</v>
       </c>
@@ -5672,7 +9680,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>22</v>
       </c>
@@ -5706,15 +9714,15 @@
       <c r="K127">
         <v>0.50822235770000002</v>
       </c>
-      <c r="L127" s="50">
+      <c r="L127" s="38">
         <f t="shared" si="2"/>
         <v>0.75087114200000005</v>
       </c>
-      <c r="M127" s="48">
+      <c r="M127" s="36">
         <f>LARGE((C127,E127,G127,I127,K127),2)</f>
         <v>0.71490936100000002</v>
       </c>
-      <c r="N127" s="52">
+      <c r="N127" s="40">
         <f t="shared" si="3"/>
         <v>4.7893412049653687E-2</v>
       </c>
@@ -5722,7 +9730,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>23</v>
       </c>
@@ -5756,15 +9764,15 @@
       <c r="K128">
         <v>0.5251778412</v>
       </c>
-      <c r="L128" s="50">
+      <c r="L128" s="38">
         <f t="shared" si="2"/>
         <v>0.60080411300000003</v>
       </c>
-      <c r="M128" s="48">
+      <c r="M128" s="36">
         <f>LARGE((C128,E128,G128,I128,K128),2)</f>
         <v>0.59974849900000005</v>
       </c>
-      <c r="N128" s="52">
+      <c r="N128" s="40">
         <f t="shared" si="3"/>
         <v>1.7570019531473855E-3</v>
       </c>
@@ -5806,15 +9814,15 @@
       <c r="K129">
         <v>0.79586976549999999</v>
       </c>
-      <c r="L129" s="50">
+      <c r="L129" s="38">
         <f t="shared" si="2"/>
         <v>0.83190030800000003</v>
       </c>
-      <c r="M129" s="48">
+      <c r="M129" s="36">
         <f>LARGE((C129,E129,G129,I129,K129),2)</f>
         <v>0.82019393500000004</v>
       </c>
-      <c r="N129" s="52">
+      <c r="N129" s="40">
         <f t="shared" si="3"/>
         <v>1.4071845974121207E-2</v>
       </c>
@@ -5856,15 +9864,15 @@
       <c r="K130">
         <v>0.30610777420000002</v>
       </c>
-      <c r="L130" s="50">
+      <c r="L130" s="38">
         <f t="shared" si="2"/>
         <v>0.33028222899999998</v>
       </c>
-      <c r="M130" s="48">
+      <c r="M130" s="36">
         <f>LARGE((C130,E130,G130,I130,K130),2)</f>
         <v>0.31710780599999999</v>
       </c>
-      <c r="N130" s="52">
+      <c r="N130" s="40">
         <f t="shared" si="3"/>
         <v>3.988837982560664E-2</v>
       </c>
@@ -5906,15 +9914,15 @@
       <c r="K131">
         <v>0.65377653840000005</v>
       </c>
-      <c r="L131" s="50">
+      <c r="L131" s="38">
         <f t="shared" si="2"/>
         <v>0.70259912599999996</v>
       </c>
-      <c r="M131" s="48">
+      <c r="M131" s="36">
         <f>LARGE((C131,E131,G131,I131,K131),2)</f>
         <v>0.68587769600000004</v>
       </c>
-      <c r="N131" s="52">
+      <c r="N131" s="40">
         <f t="shared" si="3"/>
         <v>2.3799389127050988E-2</v>
       </c>
@@ -5956,15 +9964,15 @@
       <c r="K132">
         <v>0.4757420054</v>
       </c>
-      <c r="L132" s="50">
+      <c r="L132" s="38">
         <f t="shared" si="2"/>
         <v>0.528086893</v>
       </c>
-      <c r="M132" s="48">
+      <c r="M132" s="36">
         <f>LARGE((C132,E132,G132,I132,K132),2)</f>
         <v>0.51247436599999996</v>
       </c>
-      <c r="N132" s="52">
+      <c r="N132" s="40">
         <f t="shared" si="3"/>
         <v>2.9564314522761773E-2</v>
       </c>
@@ -6006,15 +10014,15 @@
       <c r="K133">
         <v>0.497343959</v>
       </c>
-      <c r="L133" s="50">
+      <c r="L133" s="38">
         <f t="shared" si="2"/>
         <v>0.59666824600000001</v>
       </c>
-      <c r="M133" s="48">
+      <c r="M133" s="36">
         <f>LARGE((C133,E133,G133,I133,K133),2)</f>
         <v>0.59500559099999994</v>
       </c>
-      <c r="N133" s="52">
+      <c r="N133" s="40">
         <f t="shared" si="3"/>
         <v>2.7865652498625985E-3</v>
       </c>
@@ -6056,15 +10064,15 @@
       <c r="K134">
         <v>0.28688881960000001</v>
       </c>
-      <c r="L134" s="50">
+      <c r="L134" s="38">
         <f t="shared" si="2"/>
         <v>0.37826667200000003</v>
       </c>
-      <c r="M134" s="48">
+      <c r="M134" s="36">
         <f>LARGE((C134,E134,G134,I134,K134),2)</f>
         <v>0.33993789400000002</v>
       </c>
-      <c r="N134" s="52">
+      <c r="N134" s="40">
         <f t="shared" si="3"/>
         <v>0.10132739899432643</v>
       </c>
@@ -6106,15 +10114,15 @@
       <c r="K135">
         <v>0.29337272479999998</v>
       </c>
-      <c r="L135" s="50">
+      <c r="L135" s="38">
         <f t="shared" si="2"/>
         <v>0.40468619300000003</v>
       </c>
-      <c r="M135" s="48">
+      <c r="M135" s="36">
         <f>LARGE((C135,E135,G135,I135,K135),2)</f>
         <v>0.38517905899999999</v>
       </c>
-      <c r="N135" s="52">
+      <c r="N135" s="40">
         <f t="shared" si="3"/>
         <v>4.8203112281619241E-2</v>
       </c>
@@ -6156,15 +10164,15 @@
       <c r="K136">
         <v>0.66136024869999999</v>
       </c>
-      <c r="L136" s="50">
+      <c r="L136" s="38">
         <f t="shared" si="2"/>
         <v>0.69802616500000003</v>
       </c>
-      <c r="M136" s="48">
+      <c r="M136" s="36">
         <f>LARGE((C136,E136,G136,I136,K136),2)</f>
         <v>0.673503089</v>
       </c>
-      <c r="N136" s="52">
+      <c r="N136" s="40">
         <f t="shared" si="3"/>
         <v>3.5132029757079422E-2</v>
       </c>
@@ -6206,15 +10214,15 @@
       <c r="K137">
         <v>0.67756106920000003</v>
       </c>
-      <c r="L137" s="50">
+      <c r="L137" s="38">
         <f t="shared" si="2"/>
         <v>0.69813231099999995</v>
       </c>
-      <c r="M137" s="48">
+      <c r="M137" s="36">
         <f>LARGE((C137,E137,G137,I137,K137),2)</f>
         <v>0.69506355200000003</v>
       </c>
-      <c r="N137" s="52">
+      <c r="N137" s="40">
         <f t="shared" si="3"/>
         <v>4.3956696340329117E-3</v>
       </c>
@@ -6256,15 +10264,15 @@
       <c r="K138">
         <v>0.68363464689999998</v>
       </c>
-      <c r="L138" s="50">
+      <c r="L138" s="38">
         <f t="shared" si="2"/>
         <v>0.69845201099999998</v>
       </c>
-      <c r="M138" s="48">
+      <c r="M138" s="36">
         <f>LARGE((C138,E138,G138,I138,K138),2)</f>
         <v>0.69367525200000002</v>
       </c>
-      <c r="N138" s="52">
+      <c r="N138" s="40">
         <f t="shared" si="3"/>
         <v>6.839065425784799E-3</v>
       </c>
@@ -6306,15 +10314,15 @@
       <c r="K139">
         <v>3.7742985600000001E-2</v>
       </c>
-      <c r="L139" s="51">
+      <c r="L139" s="39">
         <f t="shared" si="2"/>
         <v>3.7742985600000001E-2</v>
       </c>
-      <c r="M139" s="49">
+      <c r="M139" s="37">
         <f>LARGE((C139,E139,G139,I139,K139),2)</f>
         <v>2.9670994999999999E-2</v>
       </c>
-      <c r="N139" s="53">
+      <c r="N139" s="41">
         <f t="shared" si="3"/>
         <v>0.2138673046575309</v>
       </c>
@@ -6354,15 +10362,15 @@
       <c r="K140">
         <v>-3.9232681000000002E-3</v>
       </c>
-      <c r="L140" s="51">
+      <c r="L140" s="39">
         <f t="shared" si="2"/>
         <v>1.9423513999999999E-2</v>
       </c>
-      <c r="M140" s="49">
+      <c r="M140" s="37">
         <f>LARGE((C140,E140,G140,I140,K140),2)</f>
         <v>9.3164089999999995E-3</v>
       </c>
-      <c r="N140" s="53">
+      <c r="N140" s="41">
         <f t="shared" si="3"/>
         <v>0.5203540924675113</v>
       </c>
@@ -6402,15 +10410,15 @@
       <c r="K141">
         <v>0.14729318450000001</v>
       </c>
-      <c r="L141" s="50">
+      <c r="L141" s="38">
         <f t="shared" si="2"/>
         <v>0.283651553</v>
       </c>
-      <c r="M141" s="48">
+      <c r="M141" s="36">
         <f>LARGE((C141,E141,G141,I141,K141),2)</f>
         <v>0.27553867799999998</v>
       </c>
-      <c r="N141" s="52">
+      <c r="N141" s="40">
         <f t="shared" si="3"/>
         <v>2.8601553258550357E-2</v>
       </c>
@@ -6452,15 +10460,15 @@
       <c r="K142">
         <v>0.56843313360000003</v>
       </c>
-      <c r="L142" s="50">
+      <c r="L142" s="38">
         <f t="shared" si="2"/>
         <v>0.63043465700000001</v>
       </c>
-      <c r="M142" s="48">
+      <c r="M142" s="36">
         <f>LARGE((C142,E142,G142,I142,K142),2)</f>
         <v>0.59061055399999995</v>
       </c>
-      <c r="N142" s="52">
+      <c r="N142" s="40">
         <f t="shared" si="3"/>
         <v>6.3169279413520657E-2</v>
       </c>
@@ -6502,15 +10510,15 @@
       <c r="K143">
         <v>0.42653943480000001</v>
       </c>
-      <c r="L143" s="50">
+      <c r="L143" s="38">
         <f t="shared" si="2"/>
         <v>0.42653943480000001</v>
       </c>
-      <c r="M143" s="48">
+      <c r="M143" s="36">
         <f>LARGE((C143,E143,G143,I143,K143),2)</f>
         <v>0.424901588</v>
       </c>
-      <c r="N143" s="52">
+      <c r="N143" s="40">
         <f t="shared" si="3"/>
         <v>3.839848479116541E-3</v>
       </c>
@@ -6552,15 +10560,15 @@
       <c r="K144">
         <v>4.246664E-4</v>
       </c>
-      <c r="L144" s="51">
+      <c r="L144" s="39">
         <f t="shared" si="2"/>
         <v>4.246664E-4</v>
       </c>
-      <c r="M144" s="49">
+      <c r="M144" s="37">
         <f>LARGE((C144,E144,G144,I144,K144),2)</f>
         <v>-7.1020980000000003E-3</v>
       </c>
-      <c r="N144" s="53">
+      <c r="N144" s="41">
         <f t="shared" si="3"/>
         <v>17.7239461374858</v>
       </c>
@@ -6600,15 +10608,15 @@
       <c r="K145">
         <v>0.21985822839999999</v>
       </c>
-      <c r="L145" s="50">
+      <c r="L145" s="38">
         <f t="shared" si="2"/>
         <v>0.33403035199999997</v>
       </c>
-      <c r="M145" s="48">
+      <c r="M145" s="36">
         <f>LARGE((C145,E145,G145,I145,K145),2)</f>
         <v>0.30406079899999999</v>
       </c>
-      <c r="N145" s="52">
+      <c r="N145" s="40">
         <f t="shared" si="3"/>
         <v>8.9721047265788542E-2</v>
       </c>
@@ -6650,15 +10658,15 @@
       <c r="K146">
         <v>0.20240836940000001</v>
       </c>
-      <c r="L146" s="50">
+      <c r="L146" s="38">
         <f t="shared" si="2"/>
         <v>0.20240836940000001</v>
       </c>
-      <c r="M146" s="48">
+      <c r="M146" s="36">
         <f>LARGE((C146,E146,G146,I146,K146),2)</f>
         <v>0.18059457800000001</v>
       </c>
-      <c r="N146" s="52">
+      <c r="N146" s="40">
         <f t="shared" si="3"/>
         <v>0.10777119278546989</v>
       </c>
@@ -6701,7 +10709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:S122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7090,19 +11098,19 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="N19" s="22" t="s">
         <v>94</v>
       </c>
@@ -7997,19 +12005,19 @@
       <c r="P41" s="14"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -8775,19 +12783,19 @@
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -9553,24 +13561,24 @@
       </c>
     </row>
     <row r="91" spans="1:13" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="28" t="s">
+      <c r="A91" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="28"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="29" t="s">
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="52"/>
+      <c r="E91" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="F91" s="29"/>
-      <c r="G91" s="29"/>
-      <c r="H91" s="29"/>
-      <c r="I91" s="30" t="s">
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="53"/>
+      <c r="I91" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="J91" s="30"/>
-      <c r="K91" s="30"/>
-      <c r="L91" s="30"/>
+      <c r="J91" s="54"/>
+      <c r="K91" s="54"/>
+      <c r="L91" s="54"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
@@ -10370,22 +14378,22 @@
       </c>
     </row>
     <row r="114" spans="1:19" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="25" t="s">
+      <c r="A114" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
+      <c r="B114" s="50"/>
+      <c r="C114" s="50"/>
       <c r="D114" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E114" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H114" s="26" t="s">
+      <c r="H114" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="I114" s="26"/>
-      <c r="J114" s="26"/>
+      <c r="I114" s="51"/>
+      <c r="J114" s="51"/>
       <c r="K114" s="10" t="s">
         <v>32</v>
       </c>
@@ -10393,11 +14401,11 @@
         <v>28</v>
       </c>
       <c r="N114" s="9"/>
-      <c r="O114" s="24" t="s">
+      <c r="O114" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="P114" s="24"/>
-      <c r="Q114" s="24"/>
+      <c r="P114" s="49"/>
+      <c r="Q114" s="49"/>
       <c r="R114" s="20" t="s">
         <v>32</v>
       </c>
@@ -10662,7 +14670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:Q69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12659,21 +16667,1142 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:M74"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1">
+        <f>COUNTA(B2:B26)</f>
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(B2,K$3:K$25,1,FALSE),"FALTA")</f>
+        <v>341/17</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3">
+        <v>221</v>
+      </c>
+      <c r="H2" t="str">
+        <f>VLOOKUP(F2,B$2:B$26,1,FALSE)</f>
+        <v>418/15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>134</v>
+      </c>
+      <c r="L2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C26" si="0">_xlfn.IFNA(VLOOKUP(B3,K$3:K$25,1,FALSE),"FALTA")</f>
+        <v>342/97</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3">
+        <v>219</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="1">VLOOKUP(F3,B$2:B$26,1,FALSE)</f>
+        <v>391/33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3">
+        <v>18</v>
+      </c>
+      <c r="M3" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(K3,B$2:B$26,1,FALSE),"")</f>
+        <v>329/6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>377/86</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3">
+        <v>218</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4">
+        <v>235</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" ref="M4:M25" si="2">_xlfn.IFNA(VLOOKUP(K4,B$2:B$26,1,FALSE),"")</f>
+        <v>330/183</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>391/243</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3">
+        <v>217</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>377/94</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5">
+        <v>85</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="2"/>
+        <v>331/2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>329/6</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="3">
+        <v>211</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>330/183</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6">
+        <v>211</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="2"/>
+        <v>341/17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>330/183</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3">
+        <v>207</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>405/17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7">
+        <v>97</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="2"/>
+        <v>342/78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>331/2</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3">
+        <v>207</v>
+      </c>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8">
+        <v>64</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="2"/>
+        <v>342/97</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>378/129</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3">
+        <v>201</v>
+      </c>
+      <c r="K9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9">
+        <v>29</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="2"/>
+        <v>353/346</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>FALTA</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3">
+        <v>193</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="1"/>
+        <v>377/86</v>
+      </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10">
+        <v>9</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="2"/>
+        <v>353/353</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>342/78</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3">
+        <v>190</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="1"/>
+        <v>341/17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11">
+        <v>80</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="2"/>
+        <v>377/54</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>FALTA</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3">
+        <v>187</v>
+      </c>
+      <c r="K12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12">
+        <v>36</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="2"/>
+        <v>377/59</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>390/208</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="3">
+        <v>186</v>
+      </c>
+      <c r="K13" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13">
+        <v>51</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="2"/>
+        <v>377/84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>377/54</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="3">
+        <v>184</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14">
+        <v>214</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="2"/>
+        <v>377/86</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>377/59</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3">
+        <v>179</v>
+      </c>
+      <c r="K15" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15">
+        <v>354</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="2"/>
+        <v>377/94</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>377/84</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
+        <v>178</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>418/4</v>
+      </c>
+      <c r="K16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16">
+        <v>8</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="2"/>
+        <v>378/129</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>391/437</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="3">
+        <v>176</v>
+      </c>
+      <c r="K17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17">
+        <v>81</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="2"/>
+        <v>390/208</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>353/346</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="3">
+        <v>169</v>
+      </c>
+      <c r="K18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18">
+        <v>109</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="2"/>
+        <v>391/243</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>353/353</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="3">
+        <v>168</v>
+      </c>
+      <c r="K19" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19">
+        <v>358</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="2"/>
+        <v>391/33</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>377/94</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="3">
+        <v>165</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v>391/437</v>
+      </c>
+      <c r="K20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20">
+        <v>185</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="2"/>
+        <v>391/437</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>391/33</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3">
+        <v>164</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21">
+        <v>267</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="2"/>
+        <v>404/69</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>404/69</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="3">
+        <v>164</v>
+      </c>
+      <c r="K22" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22">
+        <v>275</v>
+      </c>
+      <c r="M22" t="str">
+        <f t="shared" si="2"/>
+        <v>405/17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>405/17</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="3">
+        <v>153</v>
+      </c>
+      <c r="K23" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23">
+        <v>131</v>
+      </c>
+      <c r="M23" t="str">
+        <f t="shared" si="2"/>
+        <v>405/34</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>405/34</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="3">
+        <v>141</v>
+      </c>
+      <c r="K24" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24">
+        <v>371</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="shared" si="2"/>
+        <v>418/15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>418/15</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="3">
+        <v>136</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>404/69</v>
+      </c>
+      <c r="K25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25">
+        <v>311</v>
+      </c>
+      <c r="M25" t="str">
+        <f t="shared" si="2"/>
+        <v>418/4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>418/4</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="3">
+        <v>102</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>391/243</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="3">
+        <v>93</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>342/78</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="3">
+        <v>80</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v>331/2</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="3">
+        <v>79</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="1"/>
+        <v>405/34</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="3">
+        <v>75</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="1"/>
+        <v>390/208</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" s="3">
+        <v>74</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="1"/>
+        <v>377/54</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G38" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="3">
+        <v>57</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="1"/>
+        <v>342/97</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E42" s="4"/>
+      <c r="F42" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="24">
+        <v>48</v>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>377/84</v>
+      </c>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G43" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G45" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="3">
+        <v>34</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="1"/>
+        <v>377/59</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" s="3">
+        <v>26</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="1"/>
+        <v>353/346</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G48" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="3">
+        <v>15</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="1"/>
+        <v>329/6</v>
+      </c>
+    </row>
+    <row r="52" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G52" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G53" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G54" s="3">
+        <v>9</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="1"/>
+        <v>353/353</v>
+      </c>
+    </row>
+    <row r="55" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F55" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G55" s="3">
+        <v>5</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="1"/>
+        <v>378/129</v>
+      </c>
+    </row>
+    <row r="56" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G56" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F59" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F60" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F61" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F62" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F63" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F64" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F66" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F67" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F68" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F69" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F70" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F71" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F72" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F73" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F74" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="F1:H74"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7b5dc55a-e723-417d-bbd9-2b7384a51092" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7b5dc55a-e723-417d-bbd9-2b7384a51092" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12930,26 +18059,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98708EEF-3554-4A3F-B1A7-CCD4F989B1B5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8394E3-3502-4278-897E-CA609F09FC7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="53b96b38-2798-47b2-a685-55ac0f3a25a3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8394E3-3502-4278-897E-CA609F09FC7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98708EEF-3554-4A3F-B1A7-CCD4F989B1B5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7b5dc55a-e723-417d-bbd9-2b7384a51092"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="53b96b38-2798-47b2-a685-55ac0f3a25a3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
